--- a/Hoadon/HDVao/9/HDDienTuDaCapMa.xlsx
+++ b/Hoadon/HDVao/9/HDDienTuDaCapMa.xlsx
@@ -325,56 +325,56 @@
       </c>
       <c r="C7" s="6" t="inlineStr">
         <is>
-          <t>C25TBR</t>
+          <t>C25TAA</t>
         </is>
       </c>
       <c r="D7" s="7" t="inlineStr">
         <is>
-          <t>7058</t>
+          <t>406408</t>
         </is>
       </c>
       <c r="E7" s="7" t="inlineStr">
         <is>
-          <t>11/09/2025</t>
+          <t>24/09/2025</t>
         </is>
       </c>
       <c r="F7" s="7" t="inlineStr">
         <is>
-          <t>0316158113</t>
+          <t>0108930466</t>
         </is>
       </c>
       <c r="G7" s="6" t="inlineStr">
         <is>
-          <t>CÔNG TY TNHH KHÍ HÓA LỎNG VIỆT NAM - VT GAS</t>
+          <t>CÔNG TY TNHH ĐẦU TƯ VÀ PHÁT TRIỂN HỆ THỐNG ĐẤU THẦU QUA MẠNG QUỐC GIA</t>
         </is>
       </c>
       <c r="H7" s="6" t="inlineStr">
         <is>
-          <t>Phòng 606, tầng 6, Tòa nhà Waseco, số 10 Phổ Quang, Phường Tân Sơn Hòa, TP. Hồ Chí Minh, Việt Nam</t>
+          <t>Tầng 8, Tòa tháp VIT TOWER, số 519, Phố Kim Mã, Phường Giảng Võ, Thành phố Hà Nội, Việt Nam.</t>
         </is>
       </c>
       <c r="I7" s="7" t="inlineStr">
         <is>
-          <t>3502469834</t>
+          <t>3502245376</t>
         </is>
       </c>
       <c r="J7" s="6" t="inlineStr">
         <is>
-          <t>CÔNG TY TNHH MỘT THÀNH VIÊN VƯỜN PHỐ VŨNG TÀU</t>
+          <t>CÔNG TY CỔ PHẦN ĐẦU TƯ XÂY DỰNG THƯƠNG MẠI DỊCH VỤ KỸ THUẬT H &amp; V</t>
         </is>
       </c>
       <c r="K7" s="13" t="n">
-        <v>4423022.0</v>
+        <v>305556.0</v>
       </c>
       <c r="L7" s="13" t="n">
-        <v>353842.0</v>
+        <v>24444.0</v>
       </c>
       <c r="M7" s="13" t="n">
         <v>0.0</v>
       </c>
       <c r="N7" s="13"/>
       <c r="O7" s="13" t="n">
-        <v>4776864.0</v>
+        <v>330000.0</v>
       </c>
       <c r="P7" s="7" t="inlineStr">
         <is>
@@ -408,56 +408,54 @@
       </c>
       <c r="C8" s="6" t="inlineStr">
         <is>
-          <t>C25TVH</t>
+          <t>C25TVF</t>
         </is>
       </c>
       <c r="D8" s="7" t="inlineStr">
         <is>
-          <t>128</t>
+          <t>43388</t>
         </is>
       </c>
       <c r="E8" s="7" t="inlineStr">
         <is>
-          <t>09/09/2025</t>
+          <t>10/09/2025</t>
         </is>
       </c>
       <c r="F8" s="7" t="inlineStr">
         <is>
-          <t>3501381915</t>
+          <t>0303490096</t>
         </is>
       </c>
       <c r="G8" s="6" t="inlineStr">
         <is>
-          <t>CÔNG TY TRÁCH NHIỆM HỮU HẠN IN VĂN HÓA</t>
+          <t>CÔNG TY CỔ PHẦN TẬP ĐOÀN VNG</t>
         </is>
       </c>
       <c r="H8" s="6" t="inlineStr">
         <is>
-          <t>Số 360/19 Lê Hồng Phong, Phường Vũng Tàu, Thành phố Hồ Chí Minh, Việt Nam</t>
+          <t>Z06, Đường số 13, Phường Tân Thuận, Thành phố Hồ Chí Minh, Việt Nam</t>
         </is>
       </c>
       <c r="I8" s="7" t="inlineStr">
         <is>
-          <t>3502469834</t>
+          <t>3502245376</t>
         </is>
       </c>
       <c r="J8" s="6" t="inlineStr">
         <is>
-          <t>CÔNG TY TNHH MỘT THÀNH VIÊN VƯỜN PHỐ VŨNG TÀU</t>
+          <t>Công ty Cổ phần đầu tư thương mại dịch vụ kỹ thuật H&amp;V</t>
         </is>
       </c>
       <c r="K8" s="13" t="n">
-        <v>1800000.0</v>
+        <v>445455.0</v>
       </c>
       <c r="L8" s="13" t="n">
-        <v>144000.0</v>
-      </c>
-      <c r="M8" s="13" t="n">
-        <v>0.0</v>
-      </c>
+        <v>44545.0</v>
+      </c>
+      <c r="M8" s="13"/>
       <c r="N8" s="13"/>
       <c r="O8" s="13" t="n">
-        <v>1944000.0</v>
+        <v>490000.0</v>
       </c>
       <c r="P8" s="7" t="inlineStr">
         <is>
@@ -491,56 +489,56 @@
       </c>
       <c r="C9" s="6" t="inlineStr">
         <is>
-          <t>C25TLP</t>
+          <t>C25TSP</t>
         </is>
       </c>
       <c r="D9" s="7" t="inlineStr">
         <is>
-          <t>2063</t>
+          <t>31589</t>
         </is>
       </c>
       <c r="E9" s="7" t="inlineStr">
         <is>
-          <t>09/09/2025</t>
+          <t>03/09/2025</t>
         </is>
       </c>
       <c r="F9" s="7" t="inlineStr">
         <is>
-          <t>3502376562</t>
+          <t>0304667885</t>
         </is>
       </c>
       <c r="G9" s="6" t="inlineStr">
         <is>
-          <t>CÔNG TY TNHH THỰC PHẨM HƯNG LỘC PHÁT</t>
+          <t>CÔNG TY CỔ PHẦN DẦU KHÍ MIỀN NAM</t>
         </is>
       </c>
       <c r="H9" s="6" t="inlineStr">
         <is>
-          <t>Số 542/13 Bình Giã, Phường Tam Thắng, Thành Phố Hồ Chí Minh, Việt Nam</t>
+          <t>86 Nguyễn Cửu Vân, Phường Gia Định, Thành phố Hồ Chí Minh, Việt Nam</t>
         </is>
       </c>
       <c r="I9" s="7" t="inlineStr">
         <is>
-          <t>3502469834</t>
+          <t>3502245376</t>
         </is>
       </c>
       <c r="J9" s="6" t="inlineStr">
         <is>
-          <t>CÔNG TY TNHH MỘT THÀNH VIÊN VƯỜN PHỐ VŨNG TÀU</t>
+          <t>CÔNG TY CỔ PHẦN ĐẦU TƯ XÂY DỰNG THƯƠNG MẠI DỊCH VỤ KỸ THUẬT H &amp; V</t>
         </is>
       </c>
       <c r="K9" s="13" t="n">
-        <v>4547588.0</v>
+        <v>566667.0</v>
       </c>
       <c r="L9" s="13" t="n">
-        <v>363807.0</v>
+        <v>45333.0</v>
       </c>
       <c r="M9" s="13" t="n">
         <v>0.0</v>
       </c>
       <c r="N9" s="13"/>
       <c r="O9" s="13" t="n">
-        <v>4911395.0</v>
+        <v>612000.0</v>
       </c>
       <c r="P9" s="7" t="inlineStr">
         <is>
@@ -574,56 +572,56 @@
       </c>
       <c r="C10" s="6" t="inlineStr">
         <is>
-          <t>C25THP</t>
+          <t>C25TSP</t>
         </is>
       </c>
       <c r="D10" s="7" t="inlineStr">
         <is>
-          <t>8734</t>
+          <t>35298</t>
         </is>
       </c>
       <c r="E10" s="7" t="inlineStr">
         <is>
-          <t>11/09/2025</t>
+          <t>14/09/2025</t>
         </is>
       </c>
       <c r="F10" s="7" t="inlineStr">
         <is>
-          <t>3502420437</t>
+          <t>0304667885</t>
         </is>
       </c>
       <c r="G10" s="6" t="inlineStr">
         <is>
-          <t>CÔNG TY TNHH TMDV PHƯƠNG HOÀNG</t>
+          <t>CÔNG TY CỔ PHẦN DẦU KHÍ MIỀN NAM</t>
         </is>
       </c>
       <c r="H10" s="6" t="inlineStr">
         <is>
-          <t>Số 42D đường 30/4, Phường Tam Thắng, Thành Phố Hồ Chí Minh, Việt Nam</t>
+          <t>86 Nguyễn Cửu Vân, Phường Gia Định, Thành phố Hồ Chí Minh, Việt Nam</t>
         </is>
       </c>
       <c r="I10" s="7" t="inlineStr">
         <is>
-          <t>3502469834</t>
+          <t>3502245376</t>
         </is>
       </c>
       <c r="J10" s="6" t="inlineStr">
         <is>
-          <t>CÔNG TY TNHH MỘT THÀNH VIÊN VƯỜN PHỐ VŨNG TÀU</t>
+          <t>CÔNG TY CỔ PHẦN ĐẦU TƯ XÂY DỰNG THƯƠNG MẠI DỊCH VỤ KỸ THUẬT H &amp; V</t>
         </is>
       </c>
       <c r="K10" s="13" t="n">
-        <v>1712963.0</v>
+        <v>283333.0</v>
       </c>
       <c r="L10" s="13" t="n">
-        <v>137037.0</v>
+        <v>22667.0</v>
       </c>
       <c r="M10" s="13" t="n">
         <v>0.0</v>
       </c>
       <c r="N10" s="13"/>
       <c r="O10" s="13" t="n">
-        <v>1850000.0</v>
+        <v>306000.0</v>
       </c>
       <c r="P10" s="7" t="inlineStr">
         <is>
@@ -657,56 +655,54 @@
       </c>
       <c r="C11" s="6" t="inlineStr">
         <is>
-          <t>C25TBP</t>
+          <t>C25TDK</t>
         </is>
       </c>
       <c r="D11" s="7" t="inlineStr">
         <is>
-          <t>305</t>
+          <t>21405</t>
         </is>
       </c>
       <c r="E11" s="7" t="inlineStr">
         <is>
-          <t>03/09/2025</t>
+          <t>04/09/2025</t>
         </is>
       </c>
       <c r="F11" s="7" t="inlineStr">
         <is>
-          <t>3502431414</t>
+          <t>3500102326</t>
         </is>
       </c>
       <c r="G11" s="6" t="inlineStr">
         <is>
-          <t>CÔNG TY TNHH THƯƠNG MẠI VÀ DỊCH VỤ MINH BÁCH PHÁT</t>
+          <t>TRUNG TÂM ĐĂNG KIỂM PHƯƠNG TIỆN GIAO THÔNG VẬN TẢI</t>
         </is>
       </c>
       <c r="H11" s="6" t="inlineStr">
         <is>
-          <t>144C/20 Đô Lương, Phường Phước Thắng, Thành phố Hồ Chí Minh, Việt Nam</t>
+          <t>47B Đường 30/4 - phường Rạch Dừa - TP. Hồ Chí Minh</t>
         </is>
       </c>
       <c r="I11" s="7" t="inlineStr">
         <is>
-          <t>3502469834</t>
+          <t>3502245376</t>
         </is>
       </c>
       <c r="J11" s="6" t="inlineStr">
         <is>
-          <t>CÔNG TY TNHH MỘT THÀNH VIÊN VƯỜN PHỐ VŨNG TÀU</t>
+          <t>CÔNG TY CỔ PHẦN ĐẦU TƯ XÂY DỰNG THƯƠNG MẠI DỊCH VỤ KỸ THUẬT H&amp;V</t>
         </is>
       </c>
       <c r="K11" s="13" t="n">
-        <v>4750000.0</v>
+        <v>1.2E7</v>
       </c>
       <c r="L11" s="13" t="n">
-        <v>237500.0</v>
-      </c>
-      <c r="M11" s="13" t="n">
-        <v>0.0</v>
-      </c>
+        <v>1200000.0</v>
+      </c>
+      <c r="M11" s="13"/>
       <c r="N11" s="13"/>
       <c r="O11" s="13" t="n">
-        <v>4987500.0</v>
+        <v>1.32E7</v>
       </c>
       <c r="P11" s="7" t="inlineStr">
         <is>
@@ -740,56 +736,56 @@
       </c>
       <c r="C12" s="6" t="inlineStr">
         <is>
-          <t>C25TBP</t>
+          <t>C25TTT</t>
         </is>
       </c>
       <c r="D12" s="7" t="inlineStr">
         <is>
-          <t>310</t>
+          <t>7261</t>
         </is>
       </c>
       <c r="E12" s="7" t="inlineStr">
         <is>
-          <t>04/09/2025</t>
+          <t>20/09/2025</t>
         </is>
       </c>
       <c r="F12" s="7" t="inlineStr">
         <is>
-          <t>3502431414</t>
+          <t>3502252817</t>
         </is>
       </c>
       <c r="G12" s="6" t="inlineStr">
         <is>
-          <t>CÔNG TY TNHH THƯƠNG MẠI VÀ DỊCH VỤ MINH BÁCH PHÁT</t>
+          <t>CÔNG TY TNHH ĐẦU TƯ THƯƠNG MẠI DỊCH VỤ VIỆT TÍN THÀNH</t>
         </is>
       </c>
       <c r="H12" s="6" t="inlineStr">
         <is>
-          <t>144C/20 Đô Lương, Phường Phước Thắng, Thành phố Hồ Chí Minh, Việt Nam</t>
+          <t>Số 24/8 Lê Thánh Tông, Phường Rạch Dừa, Thành phố Hồ Chí Minh, Việt Nam.</t>
         </is>
       </c>
       <c r="I12" s="7" t="inlineStr">
         <is>
-          <t>3502469834</t>
+          <t>3502245376</t>
         </is>
       </c>
       <c r="J12" s="6" t="inlineStr">
         <is>
-          <t>CÔNG TY TNHH MỘT THÀNH VIÊN VƯỜN PHỐ VŨNG TÀU</t>
+          <t>CÔNG TY CỔ PHẦN ĐẦU TƯ XÂY DỰNG THƯƠNG MẠI DỊCH VỤ KỸ THUẬT H &amp; V</t>
         </is>
       </c>
       <c r="K12" s="13" t="n">
-        <v>4750000.0</v>
+        <v>1040741.0</v>
       </c>
       <c r="L12" s="13" t="n">
-        <v>237500.0</v>
+        <v>83259.0</v>
       </c>
       <c r="M12" s="13" t="n">
         <v>0.0</v>
       </c>
       <c r="N12" s="13"/>
       <c r="O12" s="13" t="n">
-        <v>4987500.0</v>
+        <v>1124000.0</v>
       </c>
       <c r="P12" s="7" t="inlineStr">
         <is>
@@ -823,56 +819,56 @@
       </c>
       <c r="C13" s="6" t="inlineStr">
         <is>
-          <t>C25TBP</t>
+          <t>C25TPA</t>
         </is>
       </c>
       <c r="D13" s="7" t="inlineStr">
         <is>
-          <t>317</t>
+          <t>78</t>
         </is>
       </c>
       <c r="E13" s="7" t="inlineStr">
         <is>
-          <t>06/09/2025</t>
+          <t>03/09/2025</t>
         </is>
       </c>
       <c r="F13" s="7" t="inlineStr">
         <is>
-          <t>3502431414</t>
+          <t>3502424618</t>
         </is>
       </c>
       <c r="G13" s="6" t="inlineStr">
         <is>
-          <t>CÔNG TY TNHH THƯƠNG MẠI VÀ DỊCH VỤ MINH BÁCH PHÁT</t>
+          <t>CÔNG TY TNHH THƯƠNG MẠI DỊCH VỤ XÂY DỰNG NGUYỄN PHÚC AN</t>
         </is>
       </c>
       <c r="H13" s="6" t="inlineStr">
         <is>
-          <t>144C/20 Đô Lương, Phường Phước Thắng, Thành phố Hồ Chí Minh, Việt Nam</t>
+          <t>Số 190 Lý Tự Trọng, Phường Vũng Tàu, TP Hồ Chí Minh, Việt Nam</t>
         </is>
       </c>
       <c r="I13" s="7" t="inlineStr">
         <is>
-          <t>3502469834</t>
+          <t>3502245376</t>
         </is>
       </c>
       <c r="J13" s="6" t="inlineStr">
         <is>
-          <t>CÔNG TY TNHH MỘT THÀNH VIÊN VƯỜN PHỐ VŨNG TÀU</t>
+          <t>CÔNG TY CỔ PHẦN ĐẦU TƯ XÂY DỰNG THƯƠNG MẠI DỊCH VỤ KỸ THUẬT H &amp; V</t>
         </is>
       </c>
       <c r="K13" s="13" t="n">
-        <v>4750000.0</v>
+        <v>2445000.0</v>
       </c>
       <c r="L13" s="13" t="n">
-        <v>237500.0</v>
+        <v>195600.0</v>
       </c>
       <c r="M13" s="13" t="n">
         <v>0.0</v>
       </c>
       <c r="N13" s="13"/>
       <c r="O13" s="13" t="n">
-        <v>4987500.0</v>
+        <v>2640600.0</v>
       </c>
       <c r="P13" s="7" t="inlineStr">
         <is>
@@ -890,417 +886,6 @@
         </is>
       </c>
       <c r="S13" s="6" t="inlineStr">
-        <is>
-          <t>Đã cấp mã hóa đơn</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" s="4" t="n">
-        <v>8.0</v>
-      </c>
-      <c r="B14" s="7" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="C14" s="6" t="inlineStr">
-        <is>
-          <t>C25TBP</t>
-        </is>
-      </c>
-      <c r="D14" s="7" t="inlineStr">
-        <is>
-          <t>323</t>
-        </is>
-      </c>
-      <c r="E14" s="7" t="inlineStr">
-        <is>
-          <t>09/09/2025</t>
-        </is>
-      </c>
-      <c r="F14" s="7" t="inlineStr">
-        <is>
-          <t>3502431414</t>
-        </is>
-      </c>
-      <c r="G14" s="6" t="inlineStr">
-        <is>
-          <t>CÔNG TY TNHH THƯƠNG MẠI VÀ DỊCH VỤ MINH BÁCH PHÁT</t>
-        </is>
-      </c>
-      <c r="H14" s="6" t="inlineStr">
-        <is>
-          <t>144C/20 Đô Lương, Phường Phước Thắng, Thành phố Hồ Chí Minh, Việt Nam</t>
-        </is>
-      </c>
-      <c r="I14" s="7" t="inlineStr">
-        <is>
-          <t>3502469834</t>
-        </is>
-      </c>
-      <c r="J14" s="6" t="inlineStr">
-        <is>
-          <t>CÔNG TY TNHH MỘT THÀNH VIÊN VƯỜN PHỐ VŨNG TÀU</t>
-        </is>
-      </c>
-      <c r="K14" s="13" t="n">
-        <v>4500000.0</v>
-      </c>
-      <c r="L14" s="13" t="n">
-        <v>225000.0</v>
-      </c>
-      <c r="M14" s="13" t="n">
-        <v>0.0</v>
-      </c>
-      <c r="N14" s="13"/>
-      <c r="O14" s="13" t="n">
-        <v>4725000.0</v>
-      </c>
-      <c r="P14" s="7" t="inlineStr">
-        <is>
-          <t>VND</t>
-        </is>
-      </c>
-      <c r="Q14" s="7" t="inlineStr">
-        <is>
-          <t>1.0</t>
-        </is>
-      </c>
-      <c r="R14" s="6" t="inlineStr">
-        <is>
-          <t>Hóa đơn mới</t>
-        </is>
-      </c>
-      <c r="S14" s="6" t="inlineStr">
-        <is>
-          <t>Đã cấp mã hóa đơn</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" s="4" t="n">
-        <v>9.0</v>
-      </c>
-      <c r="B15" s="7" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="C15" s="6" t="inlineStr">
-        <is>
-          <t>C25TBP</t>
-        </is>
-      </c>
-      <c r="D15" s="7" t="inlineStr">
-        <is>
-          <t>324</t>
-        </is>
-      </c>
-      <c r="E15" s="7" t="inlineStr">
-        <is>
-          <t>11/09/2025</t>
-        </is>
-      </c>
-      <c r="F15" s="7" t="inlineStr">
-        <is>
-          <t>3502431414</t>
-        </is>
-      </c>
-      <c r="G15" s="6" t="inlineStr">
-        <is>
-          <t>CÔNG TY TNHH THƯƠNG MẠI VÀ DỊCH VỤ MINH BÁCH PHÁT</t>
-        </is>
-      </c>
-      <c r="H15" s="6" t="inlineStr">
-        <is>
-          <t>144C/20 Đô Lương, Phường Phước Thắng, Thành phố Hồ Chí Minh, Việt Nam</t>
-        </is>
-      </c>
-      <c r="I15" s="7" t="inlineStr">
-        <is>
-          <t>3502469834</t>
-        </is>
-      </c>
-      <c r="J15" s="6" t="inlineStr">
-        <is>
-          <t>CÔNG TY TNHH MỘT THÀNH VIÊN VƯỜN PHỐ VŨNG TÀU</t>
-        </is>
-      </c>
-      <c r="K15" s="13" t="n">
-        <v>4400000.0</v>
-      </c>
-      <c r="L15" s="13" t="n">
-        <v>220000.0</v>
-      </c>
-      <c r="M15" s="13" t="n">
-        <v>0.0</v>
-      </c>
-      <c r="N15" s="13"/>
-      <c r="O15" s="13" t="n">
-        <v>4620000.0</v>
-      </c>
-      <c r="P15" s="7" t="inlineStr">
-        <is>
-          <t>VND</t>
-        </is>
-      </c>
-      <c r="Q15" s="7" t="inlineStr">
-        <is>
-          <t>1.0</t>
-        </is>
-      </c>
-      <c r="R15" s="6" t="inlineStr">
-        <is>
-          <t>Hóa đơn mới</t>
-        </is>
-      </c>
-      <c r="S15" s="6" t="inlineStr">
-        <is>
-          <t>Đã cấp mã hóa đơn</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" s="4" t="n">
-        <v>10.0</v>
-      </c>
-      <c r="B16" s="7" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="C16" s="6" t="inlineStr">
-        <is>
-          <t>C25TCH</t>
-        </is>
-      </c>
-      <c r="D16" s="7" t="inlineStr">
-        <is>
-          <t>181</t>
-        </is>
-      </c>
-      <c r="E16" s="7" t="inlineStr">
-        <is>
-          <t>05/09/2025</t>
-        </is>
-      </c>
-      <c r="F16" s="7" t="inlineStr">
-        <is>
-          <t>3502470942</t>
-        </is>
-      </c>
-      <c r="G16" s="6" t="inlineStr">
-        <is>
-          <t>CÔNG TY TNHH THỰC PHẨM CAO HÂN</t>
-        </is>
-      </c>
-      <c r="H16" s="6" t="inlineStr">
-        <is>
-          <t>142 Xô Viết Nghệ Tĩnh, Phường Vũng Tàu, Thành phố Hồ Chí Minh, Việt Nam</t>
-        </is>
-      </c>
-      <c r="I16" s="7" t="inlineStr">
-        <is>
-          <t>3502469834</t>
-        </is>
-      </c>
-      <c r="J16" s="6" t="inlineStr">
-        <is>
-          <t>CÔNG TY TNHH MỘT THÀNH VIÊN VƯỜN PHỐ VŨNG TÀU</t>
-        </is>
-      </c>
-      <c r="K16" s="13" t="n">
-        <v>4666675.0</v>
-      </c>
-      <c r="L16" s="13" t="n">
-        <v>233334.0</v>
-      </c>
-      <c r="M16" s="13"/>
-      <c r="N16" s="13"/>
-      <c r="O16" s="13" t="n">
-        <v>4900009.0</v>
-      </c>
-      <c r="P16" s="7" t="inlineStr">
-        <is>
-          <t>VND</t>
-        </is>
-      </c>
-      <c r="Q16" s="7" t="inlineStr">
-        <is>
-          <t>1.0</t>
-        </is>
-      </c>
-      <c r="R16" s="6" t="inlineStr">
-        <is>
-          <t>Hóa đơn mới</t>
-        </is>
-      </c>
-      <c r="S16" s="6" t="inlineStr">
-        <is>
-          <t>Đã cấp mã hóa đơn</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" s="4" t="n">
-        <v>11.0</v>
-      </c>
-      <c r="B17" s="7" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="C17" s="6" t="inlineStr">
-        <is>
-          <t>C25TCH</t>
-        </is>
-      </c>
-      <c r="D17" s="7" t="inlineStr">
-        <is>
-          <t>192</t>
-        </is>
-      </c>
-      <c r="E17" s="7" t="inlineStr">
-        <is>
-          <t>12/09/2025</t>
-        </is>
-      </c>
-      <c r="F17" s="7" t="inlineStr">
-        <is>
-          <t>3502470942</t>
-        </is>
-      </c>
-      <c r="G17" s="6" t="inlineStr">
-        <is>
-          <t>CÔNG TY TNHH THỰC PHẨM CAO HÂN</t>
-        </is>
-      </c>
-      <c r="H17" s="6" t="inlineStr">
-        <is>
-          <t>142 Xô Viết Nghệ Tĩnh, Phường Vũng Tàu, Thành phố Hồ Chí Minh, Việt Nam</t>
-        </is>
-      </c>
-      <c r="I17" s="7" t="inlineStr">
-        <is>
-          <t>3502469834</t>
-        </is>
-      </c>
-      <c r="J17" s="6" t="inlineStr">
-        <is>
-          <t>CÔNG TY TNHH MỘT THÀNH VIÊN VƯỜN PHỐ VŨNG TÀU</t>
-        </is>
-      </c>
-      <c r="K17" s="13" t="n">
-        <v>4571430.0</v>
-      </c>
-      <c r="L17" s="13" t="n">
-        <v>228572.0</v>
-      </c>
-      <c r="M17" s="13"/>
-      <c r="N17" s="13"/>
-      <c r="O17" s="13" t="n">
-        <v>4800002.0</v>
-      </c>
-      <c r="P17" s="7" t="inlineStr">
-        <is>
-          <t>VND</t>
-        </is>
-      </c>
-      <c r="Q17" s="7" t="inlineStr">
-        <is>
-          <t>1.0</t>
-        </is>
-      </c>
-      <c r="R17" s="6" t="inlineStr">
-        <is>
-          <t>Hóa đơn mới</t>
-        </is>
-      </c>
-      <c r="S17" s="6" t="inlineStr">
-        <is>
-          <t>Đã cấp mã hóa đơn</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" s="4" t="n">
-        <v>12.0</v>
-      </c>
-      <c r="B18" s="7" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="C18" s="6" t="inlineStr">
-        <is>
-          <t>C25TMQ</t>
-        </is>
-      </c>
-      <c r="D18" s="7" t="inlineStr">
-        <is>
-          <t>3692</t>
-        </is>
-      </c>
-      <c r="E18" s="7" t="inlineStr">
-        <is>
-          <t>05/09/2025</t>
-        </is>
-      </c>
-      <c r="F18" s="7" t="inlineStr">
-        <is>
-          <t>3502479416</t>
-        </is>
-      </c>
-      <c r="G18" s="6" t="inlineStr">
-        <is>
-          <t>CÔNG TY CỔ PHẦN THỰC PHẨM MINH QUÂN FOOD</t>
-        </is>
-      </c>
-      <c r="H18" s="6" t="inlineStr">
-        <is>
-          <t>Số 516 đường Thống Nhất ,Phường Tam Thắng ,Thành Phố Hồ Chí Minh, Việt Nam</t>
-        </is>
-      </c>
-      <c r="I18" s="7" t="inlineStr">
-        <is>
-          <t>3502469834</t>
-        </is>
-      </c>
-      <c r="J18" s="6" t="inlineStr">
-        <is>
-          <t>CÔNG TY TNHH MỘT THÀNH VIÊN VƯỜN PHỐ VŨNG TÀU</t>
-        </is>
-      </c>
-      <c r="K18" s="13" t="n">
-        <v>2280000.0</v>
-      </c>
-      <c r="L18" s="13" t="n">
-        <v>147000.0</v>
-      </c>
-      <c r="M18" s="13" t="n">
-        <v>0.0</v>
-      </c>
-      <c r="N18" s="13"/>
-      <c r="O18" s="13" t="n">
-        <v>2427000.0</v>
-      </c>
-      <c r="P18" s="7" t="inlineStr">
-        <is>
-          <t>VND</t>
-        </is>
-      </c>
-      <c r="Q18" s="7" t="inlineStr">
-        <is>
-          <t>1.0</t>
-        </is>
-      </c>
-      <c r="R18" s="6" t="inlineStr">
-        <is>
-          <t>Hóa đơn mới</t>
-        </is>
-      </c>
-      <c r="S18" s="6" t="inlineStr">
         <is>
           <t>Đã cấp mã hóa đơn</t>
         </is>

--- a/Hoadon/HDVao/9/HDDienTuDaCapMa.xlsx
+++ b/Hoadon/HDVao/9/HDDienTuDaCapMa.xlsx
@@ -325,56 +325,56 @@
       </c>
       <c r="C7" s="6" t="inlineStr">
         <is>
-          <t>C25TAA</t>
+          <t>C25TBR</t>
         </is>
       </c>
       <c r="D7" s="7" t="inlineStr">
         <is>
-          <t>406408</t>
+          <t>7058</t>
         </is>
       </c>
       <c r="E7" s="7" t="inlineStr">
         <is>
-          <t>24/09/2025</t>
+          <t>11/09/2025</t>
         </is>
       </c>
       <c r="F7" s="7" t="inlineStr">
         <is>
-          <t>0108930466</t>
+          <t>0316158113</t>
         </is>
       </c>
       <c r="G7" s="6" t="inlineStr">
         <is>
-          <t>CÔNG TY TNHH ĐẦU TƯ VÀ PHÁT TRIỂN HỆ THỐNG ĐẤU THẦU QUA MẠNG QUỐC GIA</t>
+          <t>CÔNG TY TNHH KHÍ HÓA LỎNG VIỆT NAM - VT GAS</t>
         </is>
       </c>
       <c r="H7" s="6" t="inlineStr">
         <is>
-          <t>Tầng 8, Tòa tháp VIT TOWER, số 519, Phố Kim Mã, Phường Giảng Võ, Thành phố Hà Nội, Việt Nam.</t>
+          <t>Phòng 606, tầng 6, Tòa nhà Waseco, số 10 Phổ Quang, Phường Tân Sơn Hòa, TP. Hồ Chí Minh, Việt Nam</t>
         </is>
       </c>
       <c r="I7" s="7" t="inlineStr">
         <is>
-          <t>3502245376</t>
+          <t>3502469834</t>
         </is>
       </c>
       <c r="J7" s="6" t="inlineStr">
         <is>
-          <t>CÔNG TY CỔ PHẦN ĐẦU TƯ XÂY DỰNG THƯƠNG MẠI DỊCH VỤ KỸ THUẬT H &amp; V</t>
+          <t>CÔNG TY TNHH MỘT THÀNH VIÊN VƯỜN PHỐ VŨNG TÀU</t>
         </is>
       </c>
       <c r="K7" s="13" t="n">
-        <v>305556.0</v>
+        <v>4423022.0</v>
       </c>
       <c r="L7" s="13" t="n">
-        <v>24444.0</v>
+        <v>353842.0</v>
       </c>
       <c r="M7" s="13" t="n">
         <v>0.0</v>
       </c>
       <c r="N7" s="13"/>
       <c r="O7" s="13" t="n">
-        <v>330000.0</v>
+        <v>4776864.0</v>
       </c>
       <c r="P7" s="7" t="inlineStr">
         <is>
@@ -408,54 +408,56 @@
       </c>
       <c r="C8" s="6" t="inlineStr">
         <is>
-          <t>C25TVF</t>
+          <t>C25TBR</t>
         </is>
       </c>
       <c r="D8" s="7" t="inlineStr">
         <is>
-          <t>43388</t>
+          <t>7594</t>
         </is>
       </c>
       <c r="E8" s="7" t="inlineStr">
         <is>
-          <t>10/09/2025</t>
+          <t>30/09/2025</t>
         </is>
       </c>
       <c r="F8" s="7" t="inlineStr">
         <is>
-          <t>0303490096</t>
+          <t>0316158113</t>
         </is>
       </c>
       <c r="G8" s="6" t="inlineStr">
         <is>
-          <t>CÔNG TY CỔ PHẦN TẬP ĐOÀN VNG</t>
+          <t>CÔNG TY TNHH KHÍ HÓA LỎNG VIỆT NAM - VT GAS</t>
         </is>
       </c>
       <c r="H8" s="6" t="inlineStr">
         <is>
-          <t>Z06, Đường số 13, Phường Tân Thuận, Thành phố Hồ Chí Minh, Việt Nam</t>
+          <t>Phòng 606, tầng 6, Tòa nhà Waseco, số 10 Phổ Quang, Phường Tân Sơn Hòa, TP. Hồ Chí Minh, Việt Nam</t>
         </is>
       </c>
       <c r="I8" s="7" t="inlineStr">
         <is>
-          <t>3502245376</t>
+          <t>3502469834</t>
         </is>
       </c>
       <c r="J8" s="6" t="inlineStr">
         <is>
-          <t>Công ty Cổ phần đầu tư thương mại dịch vụ kỹ thuật H&amp;V</t>
+          <t>CÔNG TY TNHH MỘT THÀNH VIÊN VƯỜN PHỐ VŨNG TÀU</t>
         </is>
       </c>
       <c r="K8" s="13" t="n">
-        <v>445455.0</v>
+        <v>4423022.0</v>
       </c>
       <c r="L8" s="13" t="n">
-        <v>44545.0</v>
-      </c>
-      <c r="M8" s="13"/>
+        <v>353842.0</v>
+      </c>
+      <c r="M8" s="13" t="n">
+        <v>0.0</v>
+      </c>
       <c r="N8" s="13"/>
       <c r="O8" s="13" t="n">
-        <v>490000.0</v>
+        <v>4776864.0</v>
       </c>
       <c r="P8" s="7" t="inlineStr">
         <is>
@@ -489,56 +491,56 @@
       </c>
       <c r="C9" s="6" t="inlineStr">
         <is>
-          <t>C25TSP</t>
+          <t>C25TVH</t>
         </is>
       </c>
       <c r="D9" s="7" t="inlineStr">
         <is>
-          <t>31589</t>
+          <t>128</t>
         </is>
       </c>
       <c r="E9" s="7" t="inlineStr">
         <is>
-          <t>03/09/2025</t>
+          <t>09/09/2025</t>
         </is>
       </c>
       <c r="F9" s="7" t="inlineStr">
         <is>
-          <t>0304667885</t>
+          <t>3501381915</t>
         </is>
       </c>
       <c r="G9" s="6" t="inlineStr">
         <is>
-          <t>CÔNG TY CỔ PHẦN DẦU KHÍ MIỀN NAM</t>
+          <t>CÔNG TY TRÁCH NHIỆM HỮU HẠN IN VĂN HÓA</t>
         </is>
       </c>
       <c r="H9" s="6" t="inlineStr">
         <is>
-          <t>86 Nguyễn Cửu Vân, Phường Gia Định, Thành phố Hồ Chí Minh, Việt Nam</t>
+          <t>Số 360/19 Lê Hồng Phong, Phường Vũng Tàu, Thành phố Hồ Chí Minh, Việt Nam</t>
         </is>
       </c>
       <c r="I9" s="7" t="inlineStr">
         <is>
-          <t>3502245376</t>
+          <t>3502469834</t>
         </is>
       </c>
       <c r="J9" s="6" t="inlineStr">
         <is>
-          <t>CÔNG TY CỔ PHẦN ĐẦU TƯ XÂY DỰNG THƯƠNG MẠI DỊCH VỤ KỸ THUẬT H &amp; V</t>
+          <t>CÔNG TY TNHH MỘT THÀNH VIÊN VƯỜN PHỐ VŨNG TÀU</t>
         </is>
       </c>
       <c r="K9" s="13" t="n">
-        <v>566667.0</v>
+        <v>1800000.0</v>
       </c>
       <c r="L9" s="13" t="n">
-        <v>45333.0</v>
+        <v>144000.0</v>
       </c>
       <c r="M9" s="13" t="n">
         <v>0.0</v>
       </c>
       <c r="N9" s="13"/>
       <c r="O9" s="13" t="n">
-        <v>612000.0</v>
+        <v>1944000.0</v>
       </c>
       <c r="P9" s="7" t="inlineStr">
         <is>
@@ -572,56 +574,56 @@
       </c>
       <c r="C10" s="6" t="inlineStr">
         <is>
-          <t>C25TSP</t>
+          <t>C25TDL</t>
         </is>
       </c>
       <c r="D10" s="7" t="inlineStr">
         <is>
-          <t>35298</t>
+          <t>34859</t>
         </is>
       </c>
       <c r="E10" s="7" t="inlineStr">
         <is>
-          <t>14/09/2025</t>
+          <t>19/09/2025</t>
         </is>
       </c>
       <c r="F10" s="7" t="inlineStr">
         <is>
-          <t>0304667885</t>
+          <t>3501970854</t>
         </is>
       </c>
       <c r="G10" s="6" t="inlineStr">
         <is>
-          <t>CÔNG TY CỔ PHẦN DẦU KHÍ MIỀN NAM</t>
+          <t>CÔNG TY TNHH THƯƠNG MẠI HỮU LINH</t>
         </is>
       </c>
       <c r="H10" s="6" t="inlineStr">
         <is>
-          <t>86 Nguyễn Cửu Vân, Phường Gia Định, Thành phố Hồ Chí Minh, Việt Nam</t>
+          <t>Số 58/23C Nguyễn Gia Thiều, Phường Phước Thắng, Thành Phố Hồ Chí Minh, Việt Nam</t>
         </is>
       </c>
       <c r="I10" s="7" t="inlineStr">
         <is>
-          <t>3502245376</t>
+          <t>3502469834</t>
         </is>
       </c>
       <c r="J10" s="6" t="inlineStr">
         <is>
-          <t>CÔNG TY CỔ PHẦN ĐẦU TƯ XÂY DỰNG THƯƠNG MẠI DỊCH VỤ KỸ THUẬT H &amp; V</t>
+          <t>CÔNG TY TNHH MỘT THÀNH VIÊN VƯỜN PHỐ VŨNG TÀU</t>
         </is>
       </c>
       <c r="K10" s="13" t="n">
-        <v>283333.0</v>
+        <v>4319444.0</v>
       </c>
       <c r="L10" s="13" t="n">
-        <v>22667.0</v>
+        <v>345556.0</v>
       </c>
       <c r="M10" s="13" t="n">
         <v>0.0</v>
       </c>
       <c r="N10" s="13"/>
       <c r="O10" s="13" t="n">
-        <v>306000.0</v>
+        <v>4665000.0</v>
       </c>
       <c r="P10" s="7" t="inlineStr">
         <is>
@@ -655,54 +657,56 @@
       </c>
       <c r="C11" s="6" t="inlineStr">
         <is>
-          <t>C25TDK</t>
+          <t>C25TLP</t>
         </is>
       </c>
       <c r="D11" s="7" t="inlineStr">
         <is>
-          <t>21405</t>
+          <t>2063</t>
         </is>
       </c>
       <c r="E11" s="7" t="inlineStr">
         <is>
-          <t>04/09/2025</t>
+          <t>09/09/2025</t>
         </is>
       </c>
       <c r="F11" s="7" t="inlineStr">
         <is>
-          <t>3500102326</t>
+          <t>3502376562</t>
         </is>
       </c>
       <c r="G11" s="6" t="inlineStr">
         <is>
-          <t>TRUNG TÂM ĐĂNG KIỂM PHƯƠNG TIỆN GIAO THÔNG VẬN TẢI</t>
+          <t>CÔNG TY TNHH THỰC PHẨM HƯNG LỘC PHÁT</t>
         </is>
       </c>
       <c r="H11" s="6" t="inlineStr">
         <is>
-          <t>47B Đường 30/4 - phường Rạch Dừa - TP. Hồ Chí Minh</t>
+          <t>Số 542/13 Bình Giã, Phường Tam Thắng, Thành Phố Hồ Chí Minh, Việt Nam</t>
         </is>
       </c>
       <c r="I11" s="7" t="inlineStr">
         <is>
-          <t>3502245376</t>
+          <t>3502469834</t>
         </is>
       </c>
       <c r="J11" s="6" t="inlineStr">
         <is>
-          <t>CÔNG TY CỔ PHẦN ĐẦU TƯ XÂY DỰNG THƯƠNG MẠI DỊCH VỤ KỸ THUẬT H&amp;V</t>
+          <t>CÔNG TY TNHH MỘT THÀNH VIÊN VƯỜN PHỐ VŨNG TÀU</t>
         </is>
       </c>
       <c r="K11" s="13" t="n">
-        <v>1.2E7</v>
+        <v>4547588.0</v>
       </c>
       <c r="L11" s="13" t="n">
-        <v>1200000.0</v>
-      </c>
-      <c r="M11" s="13"/>
+        <v>363807.0</v>
+      </c>
+      <c r="M11" s="13" t="n">
+        <v>0.0</v>
+      </c>
       <c r="N11" s="13"/>
       <c r="O11" s="13" t="n">
-        <v>1.32E7</v>
+        <v>4911395.0</v>
       </c>
       <c r="P11" s="7" t="inlineStr">
         <is>
@@ -736,56 +740,56 @@
       </c>
       <c r="C12" s="6" t="inlineStr">
         <is>
-          <t>C25TTT</t>
+          <t>C25TLP</t>
         </is>
       </c>
       <c r="D12" s="7" t="inlineStr">
         <is>
-          <t>7261</t>
+          <t>2505</t>
         </is>
       </c>
       <c r="E12" s="7" t="inlineStr">
         <is>
-          <t>20/09/2025</t>
+          <t>24/09/2025</t>
         </is>
       </c>
       <c r="F12" s="7" t="inlineStr">
         <is>
-          <t>3502252817</t>
+          <t>3502376562</t>
         </is>
       </c>
       <c r="G12" s="6" t="inlineStr">
         <is>
-          <t>CÔNG TY TNHH ĐẦU TƯ THƯƠNG MẠI DỊCH VỤ VIỆT TÍN THÀNH</t>
+          <t>CÔNG TY TNHH THỰC PHẨM HƯNG LỘC PHÁT</t>
         </is>
       </c>
       <c r="H12" s="6" t="inlineStr">
         <is>
-          <t>Số 24/8 Lê Thánh Tông, Phường Rạch Dừa, Thành phố Hồ Chí Minh, Việt Nam.</t>
+          <t>Số 542/13 Bình Giã, Phường Tam Thắng, Thành Phố Hồ Chí Minh, Việt Nam</t>
         </is>
       </c>
       <c r="I12" s="7" t="inlineStr">
         <is>
-          <t>3502245376</t>
+          <t>3502469834</t>
         </is>
       </c>
       <c r="J12" s="6" t="inlineStr">
         <is>
-          <t>CÔNG TY CỔ PHẦN ĐẦU TƯ XÂY DỰNG THƯƠNG MẠI DỊCH VỤ KỸ THUẬT H &amp; V</t>
+          <t>CÔNG TY TNHH MỘT THÀNH VIÊN VƯỜN PHỐ VŨNG TÀU</t>
         </is>
       </c>
       <c r="K12" s="13" t="n">
-        <v>1040741.0</v>
+        <v>4547588.0</v>
       </c>
       <c r="L12" s="13" t="n">
-        <v>83259.0</v>
+        <v>363807.0</v>
       </c>
       <c r="M12" s="13" t="n">
         <v>0.0</v>
       </c>
       <c r="N12" s="13"/>
       <c r="O12" s="13" t="n">
-        <v>1124000.0</v>
+        <v>4911395.0</v>
       </c>
       <c r="P12" s="7" t="inlineStr">
         <is>
@@ -819,56 +823,56 @@
       </c>
       <c r="C13" s="6" t="inlineStr">
         <is>
-          <t>C25TPA</t>
+          <t>C25TAB</t>
         </is>
       </c>
       <c r="D13" s="7" t="inlineStr">
         <is>
-          <t>78</t>
+          <t>1333</t>
         </is>
       </c>
       <c r="E13" s="7" t="inlineStr">
         <is>
-          <t>03/09/2025</t>
+          <t>24/09/2025</t>
         </is>
       </c>
       <c r="F13" s="7" t="inlineStr">
         <is>
-          <t>3502424618</t>
+          <t>3502397869</t>
         </is>
       </c>
       <c r="G13" s="6" t="inlineStr">
         <is>
-          <t>CÔNG TY TNHH THƯƠNG MẠI DỊCH VỤ XÂY DỰNG NGUYỄN PHÚC AN</t>
+          <t>CÔNG TY TNHH MỘT THÀNH VIÊN THƯƠNG MẠI DỊCH VỤ XUẤT NHẬP KHẨU PHÚ MỸ</t>
         </is>
       </c>
       <c r="H13" s="6" t="inlineStr">
         <is>
-          <t>Số 190 Lý Tự Trọng, Phường Vũng Tàu, TP Hồ Chí Minh, Việt Nam</t>
+          <t>Ấp 4B, Xã Hoà Hội, Thành Phố Hồ Chí Minh</t>
         </is>
       </c>
       <c r="I13" s="7" t="inlineStr">
         <is>
-          <t>3502245376</t>
+          <t>3502469834</t>
         </is>
       </c>
       <c r="J13" s="6" t="inlineStr">
         <is>
-          <t>CÔNG TY CỔ PHẦN ĐẦU TƯ XÂY DỰNG THƯƠNG MẠI DỊCH VỤ KỸ THUẬT H &amp; V</t>
+          <t>CÔNG TY TNHH MỘT THÀNH VIÊN VƯỜN PHỐ VŨNG TÀU</t>
         </is>
       </c>
       <c r="K13" s="13" t="n">
-        <v>2445000.0</v>
+        <v>931000.0</v>
       </c>
       <c r="L13" s="13" t="n">
-        <v>195600.0</v>
+        <v>46550.0</v>
       </c>
       <c r="M13" s="13" t="n">
         <v>0.0</v>
       </c>
       <c r="N13" s="13"/>
       <c r="O13" s="13" t="n">
-        <v>2640600.0</v>
+        <v>977550.0</v>
       </c>
       <c r="P13" s="7" t="inlineStr">
         <is>
@@ -886,6 +890,1905 @@
         </is>
       </c>
       <c r="S13" s="6" t="inlineStr">
+        <is>
+          <t>Đã cấp mã hóa đơn</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="4" t="n">
+        <v>8.0</v>
+      </c>
+      <c r="B14" s="7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C14" s="6" t="inlineStr">
+        <is>
+          <t>C25THP</t>
+        </is>
+      </c>
+      <c r="D14" s="7" t="inlineStr">
+        <is>
+          <t>10419</t>
+        </is>
+      </c>
+      <c r="E14" s="7" t="inlineStr">
+        <is>
+          <t>30/09/2025</t>
+        </is>
+      </c>
+      <c r="F14" s="7" t="inlineStr">
+        <is>
+          <t>3502420437</t>
+        </is>
+      </c>
+      <c r="G14" s="6" t="inlineStr">
+        <is>
+          <t>CÔNG TY TNHH TMDV PHƯƠNG HOÀNG</t>
+        </is>
+      </c>
+      <c r="H14" s="6" t="inlineStr">
+        <is>
+          <t>Số 42D đường 30/4, Phường Tam Thắng, Thành Phố Hồ Chí Minh, Việt Nam</t>
+        </is>
+      </c>
+      <c r="I14" s="7" t="inlineStr">
+        <is>
+          <t>3502469834</t>
+        </is>
+      </c>
+      <c r="J14" s="6" t="inlineStr">
+        <is>
+          <t>CÔNG TY TNHH MỘT THÀNH VIÊN VƯỜN PHỐ VŨNG TÀU</t>
+        </is>
+      </c>
+      <c r="K14" s="13" t="n">
+        <v>3041667.0</v>
+      </c>
+      <c r="L14" s="13" t="n">
+        <v>243333.0</v>
+      </c>
+      <c r="M14" s="13" t="n">
+        <v>74074.0</v>
+      </c>
+      <c r="N14" s="13"/>
+      <c r="O14" s="13" t="n">
+        <v>3285000.0</v>
+      </c>
+      <c r="P14" s="7" t="inlineStr">
+        <is>
+          <t>VND</t>
+        </is>
+      </c>
+      <c r="Q14" s="7" t="inlineStr">
+        <is>
+          <t>1.0</t>
+        </is>
+      </c>
+      <c r="R14" s="6" t="inlineStr">
+        <is>
+          <t>Hóa đơn mới</t>
+        </is>
+      </c>
+      <c r="S14" s="6" t="inlineStr">
+        <is>
+          <t>Đã cấp mã hóa đơn</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="4" t="n">
+        <v>9.0</v>
+      </c>
+      <c r="B15" s="7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C15" s="6" t="inlineStr">
+        <is>
+          <t>C25THP</t>
+        </is>
+      </c>
+      <c r="D15" s="7" t="inlineStr">
+        <is>
+          <t>8734</t>
+        </is>
+      </c>
+      <c r="E15" s="7" t="inlineStr">
+        <is>
+          <t>11/09/2025</t>
+        </is>
+      </c>
+      <c r="F15" s="7" t="inlineStr">
+        <is>
+          <t>3502420437</t>
+        </is>
+      </c>
+      <c r="G15" s="6" t="inlineStr">
+        <is>
+          <t>CÔNG TY TNHH TMDV PHƯƠNG HOÀNG</t>
+        </is>
+      </c>
+      <c r="H15" s="6" t="inlineStr">
+        <is>
+          <t>Số 42D đường 30/4, Phường Tam Thắng, Thành Phố Hồ Chí Minh, Việt Nam</t>
+        </is>
+      </c>
+      <c r="I15" s="7" t="inlineStr">
+        <is>
+          <t>3502469834</t>
+        </is>
+      </c>
+      <c r="J15" s="6" t="inlineStr">
+        <is>
+          <t>CÔNG TY TNHH MỘT THÀNH VIÊN VƯỜN PHỐ VŨNG TÀU</t>
+        </is>
+      </c>
+      <c r="K15" s="13" t="n">
+        <v>1712963.0</v>
+      </c>
+      <c r="L15" s="13" t="n">
+        <v>137037.0</v>
+      </c>
+      <c r="M15" s="13" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="N15" s="13"/>
+      <c r="O15" s="13" t="n">
+        <v>1850000.0</v>
+      </c>
+      <c r="P15" s="7" t="inlineStr">
+        <is>
+          <t>VND</t>
+        </is>
+      </c>
+      <c r="Q15" s="7" t="inlineStr">
+        <is>
+          <t>1.0</t>
+        </is>
+      </c>
+      <c r="R15" s="6" t="inlineStr">
+        <is>
+          <t>Hóa đơn mới</t>
+        </is>
+      </c>
+      <c r="S15" s="6" t="inlineStr">
+        <is>
+          <t>Đã cấp mã hóa đơn</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="4" t="n">
+        <v>10.0</v>
+      </c>
+      <c r="B16" s="7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C16" s="6" t="inlineStr">
+        <is>
+          <t>C25THP</t>
+        </is>
+      </c>
+      <c r="D16" s="7" t="inlineStr">
+        <is>
+          <t>9613</t>
+        </is>
+      </c>
+      <c r="E16" s="7" t="inlineStr">
+        <is>
+          <t>20/09/2025</t>
+        </is>
+      </c>
+      <c r="F16" s="7" t="inlineStr">
+        <is>
+          <t>3502420437</t>
+        </is>
+      </c>
+      <c r="G16" s="6" t="inlineStr">
+        <is>
+          <t>CÔNG TY TNHH TMDV PHƯƠNG HOÀNG</t>
+        </is>
+      </c>
+      <c r="H16" s="6" t="inlineStr">
+        <is>
+          <t>Số 42D đường 30/4, Phường Tam Thắng, Thành Phố Hồ Chí Minh, Việt Nam</t>
+        </is>
+      </c>
+      <c r="I16" s="7" t="inlineStr">
+        <is>
+          <t>3502469834</t>
+        </is>
+      </c>
+      <c r="J16" s="6" t="inlineStr">
+        <is>
+          <t>CÔNG TY TNHH MỘT THÀNH VIÊN VƯỜN PHỐ VŨNG TÀU</t>
+        </is>
+      </c>
+      <c r="K16" s="13" t="n">
+        <v>3435185.0</v>
+      </c>
+      <c r="L16" s="13" t="n">
+        <v>274815.0</v>
+      </c>
+      <c r="M16" s="13" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="N16" s="13"/>
+      <c r="O16" s="13" t="n">
+        <v>3710000.0</v>
+      </c>
+      <c r="P16" s="7" t="inlineStr">
+        <is>
+          <t>VND</t>
+        </is>
+      </c>
+      <c r="Q16" s="7" t="inlineStr">
+        <is>
+          <t>1.0</t>
+        </is>
+      </c>
+      <c r="R16" s="6" t="inlineStr">
+        <is>
+          <t>Hóa đơn mới</t>
+        </is>
+      </c>
+      <c r="S16" s="6" t="inlineStr">
+        <is>
+          <t>Đã cấp mã hóa đơn</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="4" t="n">
+        <v>11.0</v>
+      </c>
+      <c r="B17" s="7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C17" s="6" t="inlineStr">
+        <is>
+          <t>C25TBP</t>
+        </is>
+      </c>
+      <c r="D17" s="7" t="inlineStr">
+        <is>
+          <t>305</t>
+        </is>
+      </c>
+      <c r="E17" s="7" t="inlineStr">
+        <is>
+          <t>03/09/2025</t>
+        </is>
+      </c>
+      <c r="F17" s="7" t="inlineStr">
+        <is>
+          <t>3502431414</t>
+        </is>
+      </c>
+      <c r="G17" s="6" t="inlineStr">
+        <is>
+          <t>CÔNG TY TNHH THƯƠNG MẠI VÀ DỊCH VỤ MINH BÁCH PHÁT</t>
+        </is>
+      </c>
+      <c r="H17" s="6" t="inlineStr">
+        <is>
+          <t>144C/20 Đô Lương, Phường Phước Thắng, Thành phố Hồ Chí Minh, Việt Nam</t>
+        </is>
+      </c>
+      <c r="I17" s="7" t="inlineStr">
+        <is>
+          <t>3502469834</t>
+        </is>
+      </c>
+      <c r="J17" s="6" t="inlineStr">
+        <is>
+          <t>CÔNG TY TNHH MỘT THÀNH VIÊN VƯỜN PHỐ VŨNG TÀU</t>
+        </is>
+      </c>
+      <c r="K17" s="13" t="n">
+        <v>4750000.0</v>
+      </c>
+      <c r="L17" s="13" t="n">
+        <v>237500.0</v>
+      </c>
+      <c r="M17" s="13" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="N17" s="13"/>
+      <c r="O17" s="13" t="n">
+        <v>4987500.0</v>
+      </c>
+      <c r="P17" s="7" t="inlineStr">
+        <is>
+          <t>VND</t>
+        </is>
+      </c>
+      <c r="Q17" s="7" t="inlineStr">
+        <is>
+          <t>1.0</t>
+        </is>
+      </c>
+      <c r="R17" s="6" t="inlineStr">
+        <is>
+          <t>Hóa đơn mới</t>
+        </is>
+      </c>
+      <c r="S17" s="6" t="inlineStr">
+        <is>
+          <t>Đã cấp mã hóa đơn</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="4" t="n">
+        <v>12.0</v>
+      </c>
+      <c r="B18" s="7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C18" s="6" t="inlineStr">
+        <is>
+          <t>C25TBP</t>
+        </is>
+      </c>
+      <c r="D18" s="7" t="inlineStr">
+        <is>
+          <t>310</t>
+        </is>
+      </c>
+      <c r="E18" s="7" t="inlineStr">
+        <is>
+          <t>04/09/2025</t>
+        </is>
+      </c>
+      <c r="F18" s="7" t="inlineStr">
+        <is>
+          <t>3502431414</t>
+        </is>
+      </c>
+      <c r="G18" s="6" t="inlineStr">
+        <is>
+          <t>CÔNG TY TNHH THƯƠNG MẠI VÀ DỊCH VỤ MINH BÁCH PHÁT</t>
+        </is>
+      </c>
+      <c r="H18" s="6" t="inlineStr">
+        <is>
+          <t>144C/20 Đô Lương, Phường Phước Thắng, Thành phố Hồ Chí Minh, Việt Nam</t>
+        </is>
+      </c>
+      <c r="I18" s="7" t="inlineStr">
+        <is>
+          <t>3502469834</t>
+        </is>
+      </c>
+      <c r="J18" s="6" t="inlineStr">
+        <is>
+          <t>CÔNG TY TNHH MỘT THÀNH VIÊN VƯỜN PHỐ VŨNG TÀU</t>
+        </is>
+      </c>
+      <c r="K18" s="13" t="n">
+        <v>4750000.0</v>
+      </c>
+      <c r="L18" s="13" t="n">
+        <v>237500.0</v>
+      </c>
+      <c r="M18" s="13" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="N18" s="13"/>
+      <c r="O18" s="13" t="n">
+        <v>4987500.0</v>
+      </c>
+      <c r="P18" s="7" t="inlineStr">
+        <is>
+          <t>VND</t>
+        </is>
+      </c>
+      <c r="Q18" s="7" t="inlineStr">
+        <is>
+          <t>1.0</t>
+        </is>
+      </c>
+      <c r="R18" s="6" t="inlineStr">
+        <is>
+          <t>Hóa đơn mới</t>
+        </is>
+      </c>
+      <c r="S18" s="6" t="inlineStr">
+        <is>
+          <t>Đã cấp mã hóa đơn</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="4" t="n">
+        <v>13.0</v>
+      </c>
+      <c r="B19" s="7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C19" s="6" t="inlineStr">
+        <is>
+          <t>C25TBP</t>
+        </is>
+      </c>
+      <c r="D19" s="7" t="inlineStr">
+        <is>
+          <t>317</t>
+        </is>
+      </c>
+      <c r="E19" s="7" t="inlineStr">
+        <is>
+          <t>06/09/2025</t>
+        </is>
+      </c>
+      <c r="F19" s="7" t="inlineStr">
+        <is>
+          <t>3502431414</t>
+        </is>
+      </c>
+      <c r="G19" s="6" t="inlineStr">
+        <is>
+          <t>CÔNG TY TNHH THƯƠNG MẠI VÀ DỊCH VỤ MINH BÁCH PHÁT</t>
+        </is>
+      </c>
+      <c r="H19" s="6" t="inlineStr">
+        <is>
+          <t>144C/20 Đô Lương, Phường Phước Thắng, Thành phố Hồ Chí Minh, Việt Nam</t>
+        </is>
+      </c>
+      <c r="I19" s="7" t="inlineStr">
+        <is>
+          <t>3502469834</t>
+        </is>
+      </c>
+      <c r="J19" s="6" t="inlineStr">
+        <is>
+          <t>CÔNG TY TNHH MỘT THÀNH VIÊN VƯỜN PHỐ VŨNG TÀU</t>
+        </is>
+      </c>
+      <c r="K19" s="13" t="n">
+        <v>4750000.0</v>
+      </c>
+      <c r="L19" s="13" t="n">
+        <v>237500.0</v>
+      </c>
+      <c r="M19" s="13" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="N19" s="13"/>
+      <c r="O19" s="13" t="n">
+        <v>4987500.0</v>
+      </c>
+      <c r="P19" s="7" t="inlineStr">
+        <is>
+          <t>VND</t>
+        </is>
+      </c>
+      <c r="Q19" s="7" t="inlineStr">
+        <is>
+          <t>1.0</t>
+        </is>
+      </c>
+      <c r="R19" s="6" t="inlineStr">
+        <is>
+          <t>Hóa đơn mới</t>
+        </is>
+      </c>
+      <c r="S19" s="6" t="inlineStr">
+        <is>
+          <t>Đã cấp mã hóa đơn</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="4" t="n">
+        <v>14.0</v>
+      </c>
+      <c r="B20" s="7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C20" s="6" t="inlineStr">
+        <is>
+          <t>C25TBP</t>
+        </is>
+      </c>
+      <c r="D20" s="7" t="inlineStr">
+        <is>
+          <t>323</t>
+        </is>
+      </c>
+      <c r="E20" s="7" t="inlineStr">
+        <is>
+          <t>09/09/2025</t>
+        </is>
+      </c>
+      <c r="F20" s="7" t="inlineStr">
+        <is>
+          <t>3502431414</t>
+        </is>
+      </c>
+      <c r="G20" s="6" t="inlineStr">
+        <is>
+          <t>CÔNG TY TNHH THƯƠNG MẠI VÀ DỊCH VỤ MINH BÁCH PHÁT</t>
+        </is>
+      </c>
+      <c r="H20" s="6" t="inlineStr">
+        <is>
+          <t>144C/20 Đô Lương, Phường Phước Thắng, Thành phố Hồ Chí Minh, Việt Nam</t>
+        </is>
+      </c>
+      <c r="I20" s="7" t="inlineStr">
+        <is>
+          <t>3502469834</t>
+        </is>
+      </c>
+      <c r="J20" s="6" t="inlineStr">
+        <is>
+          <t>CÔNG TY TNHH MỘT THÀNH VIÊN VƯỜN PHỐ VŨNG TÀU</t>
+        </is>
+      </c>
+      <c r="K20" s="13" t="n">
+        <v>4500000.0</v>
+      </c>
+      <c r="L20" s="13" t="n">
+        <v>225000.0</v>
+      </c>
+      <c r="M20" s="13" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="N20" s="13"/>
+      <c r="O20" s="13" t="n">
+        <v>4725000.0</v>
+      </c>
+      <c r="P20" s="7" t="inlineStr">
+        <is>
+          <t>VND</t>
+        </is>
+      </c>
+      <c r="Q20" s="7" t="inlineStr">
+        <is>
+          <t>1.0</t>
+        </is>
+      </c>
+      <c r="R20" s="6" t="inlineStr">
+        <is>
+          <t>Hóa đơn mới</t>
+        </is>
+      </c>
+      <c r="S20" s="6" t="inlineStr">
+        <is>
+          <t>Đã cấp mã hóa đơn</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="4" t="n">
+        <v>15.0</v>
+      </c>
+      <c r="B21" s="7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C21" s="6" t="inlineStr">
+        <is>
+          <t>C25TBP</t>
+        </is>
+      </c>
+      <c r="D21" s="7" t="inlineStr">
+        <is>
+          <t>324</t>
+        </is>
+      </c>
+      <c r="E21" s="7" t="inlineStr">
+        <is>
+          <t>11/09/2025</t>
+        </is>
+      </c>
+      <c r="F21" s="7" t="inlineStr">
+        <is>
+          <t>3502431414</t>
+        </is>
+      </c>
+      <c r="G21" s="6" t="inlineStr">
+        <is>
+          <t>CÔNG TY TNHH THƯƠNG MẠI VÀ DỊCH VỤ MINH BÁCH PHÁT</t>
+        </is>
+      </c>
+      <c r="H21" s="6" t="inlineStr">
+        <is>
+          <t>144C/20 Đô Lương, Phường Phước Thắng, Thành phố Hồ Chí Minh, Việt Nam</t>
+        </is>
+      </c>
+      <c r="I21" s="7" t="inlineStr">
+        <is>
+          <t>3502469834</t>
+        </is>
+      </c>
+      <c r="J21" s="6" t="inlineStr">
+        <is>
+          <t>CÔNG TY TNHH MỘT THÀNH VIÊN VƯỜN PHỐ VŨNG TÀU</t>
+        </is>
+      </c>
+      <c r="K21" s="13" t="n">
+        <v>4400000.0</v>
+      </c>
+      <c r="L21" s="13" t="n">
+        <v>220000.0</v>
+      </c>
+      <c r="M21" s="13" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="N21" s="13"/>
+      <c r="O21" s="13" t="n">
+        <v>4620000.0</v>
+      </c>
+      <c r="P21" s="7" t="inlineStr">
+        <is>
+          <t>VND</t>
+        </is>
+      </c>
+      <c r="Q21" s="7" t="inlineStr">
+        <is>
+          <t>1.0</t>
+        </is>
+      </c>
+      <c r="R21" s="6" t="inlineStr">
+        <is>
+          <t>Hóa đơn mới</t>
+        </is>
+      </c>
+      <c r="S21" s="6" t="inlineStr">
+        <is>
+          <t>Đã cấp mã hóa đơn</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="4" t="n">
+        <v>16.0</v>
+      </c>
+      <c r="B22" s="7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C22" s="6" t="inlineStr">
+        <is>
+          <t>C25TBP</t>
+        </is>
+      </c>
+      <c r="D22" s="7" t="inlineStr">
+        <is>
+          <t>328</t>
+        </is>
+      </c>
+      <c r="E22" s="7" t="inlineStr">
+        <is>
+          <t>15/09/2025</t>
+        </is>
+      </c>
+      <c r="F22" s="7" t="inlineStr">
+        <is>
+          <t>3502431414</t>
+        </is>
+      </c>
+      <c r="G22" s="6" t="inlineStr">
+        <is>
+          <t>CÔNG TY TNHH THƯƠNG MẠI VÀ DỊCH VỤ MINH BÁCH PHÁT</t>
+        </is>
+      </c>
+      <c r="H22" s="6" t="inlineStr">
+        <is>
+          <t>144C/20 Đô Lương, Phường Phước Thắng, Thành phố Hồ Chí Minh, Việt Nam</t>
+        </is>
+      </c>
+      <c r="I22" s="7" t="inlineStr">
+        <is>
+          <t>3502469834</t>
+        </is>
+      </c>
+      <c r="J22" s="6" t="inlineStr">
+        <is>
+          <t>CÔNG TY TNHH MỘT THÀNH VIÊN VƯỜN PHỐ VŨNG TÀU</t>
+        </is>
+      </c>
+      <c r="K22" s="13" t="n">
+        <v>4600000.0</v>
+      </c>
+      <c r="L22" s="13" t="n">
+        <v>230000.0</v>
+      </c>
+      <c r="M22" s="13" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="N22" s="13"/>
+      <c r="O22" s="13" t="n">
+        <v>4830000.0</v>
+      </c>
+      <c r="P22" s="7" t="inlineStr">
+        <is>
+          <t>VND</t>
+        </is>
+      </c>
+      <c r="Q22" s="7" t="inlineStr">
+        <is>
+          <t>1.0</t>
+        </is>
+      </c>
+      <c r="R22" s="6" t="inlineStr">
+        <is>
+          <t>Hóa đơn mới</t>
+        </is>
+      </c>
+      <c r="S22" s="6" t="inlineStr">
+        <is>
+          <t>Đã cấp mã hóa đơn</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="4" t="n">
+        <v>17.0</v>
+      </c>
+      <c r="B23" s="7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C23" s="6" t="inlineStr">
+        <is>
+          <t>C25TBP</t>
+        </is>
+      </c>
+      <c r="D23" s="7" t="inlineStr">
+        <is>
+          <t>330</t>
+        </is>
+      </c>
+      <c r="E23" s="7" t="inlineStr">
+        <is>
+          <t>16/09/2025</t>
+        </is>
+      </c>
+      <c r="F23" s="7" t="inlineStr">
+        <is>
+          <t>3502431414</t>
+        </is>
+      </c>
+      <c r="G23" s="6" t="inlineStr">
+        <is>
+          <t>CÔNG TY TNHH THƯƠNG MẠI VÀ DỊCH VỤ MINH BÁCH PHÁT</t>
+        </is>
+      </c>
+      <c r="H23" s="6" t="inlineStr">
+        <is>
+          <t>144C/20 Đô Lương, Phường Phước Thắng, Thành phố Hồ Chí Minh, Việt Nam</t>
+        </is>
+      </c>
+      <c r="I23" s="7" t="inlineStr">
+        <is>
+          <t>3502469834</t>
+        </is>
+      </c>
+      <c r="J23" s="6" t="inlineStr">
+        <is>
+          <t>CÔNG TY TNHH MỘT THÀNH VIÊN VƯỜN PHỐ VŨNG TÀU</t>
+        </is>
+      </c>
+      <c r="K23" s="13" t="n">
+        <v>4490000.0</v>
+      </c>
+      <c r="L23" s="13" t="n">
+        <v>224500.0</v>
+      </c>
+      <c r="M23" s="13" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="N23" s="13"/>
+      <c r="O23" s="13" t="n">
+        <v>4714500.0</v>
+      </c>
+      <c r="P23" s="7" t="inlineStr">
+        <is>
+          <t>VND</t>
+        </is>
+      </c>
+      <c r="Q23" s="7" t="inlineStr">
+        <is>
+          <t>1.0</t>
+        </is>
+      </c>
+      <c r="R23" s="6" t="inlineStr">
+        <is>
+          <t>Hóa đơn mới</t>
+        </is>
+      </c>
+      <c r="S23" s="6" t="inlineStr">
+        <is>
+          <t>Đã cấp mã hóa đơn</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="4" t="n">
+        <v>18.0</v>
+      </c>
+      <c r="B24" s="7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C24" s="6" t="inlineStr">
+        <is>
+          <t>C25TBP</t>
+        </is>
+      </c>
+      <c r="D24" s="7" t="inlineStr">
+        <is>
+          <t>331</t>
+        </is>
+      </c>
+      <c r="E24" s="7" t="inlineStr">
+        <is>
+          <t>17/09/2025</t>
+        </is>
+      </c>
+      <c r="F24" s="7" t="inlineStr">
+        <is>
+          <t>3502431414</t>
+        </is>
+      </c>
+      <c r="G24" s="6" t="inlineStr">
+        <is>
+          <t>CÔNG TY TNHH THƯƠNG MẠI VÀ DỊCH VỤ MINH BÁCH PHÁT</t>
+        </is>
+      </c>
+      <c r="H24" s="6" t="inlineStr">
+        <is>
+          <t>144C/20 Đô Lương, Phường Phước Thắng, Thành phố Hồ Chí Minh, Việt Nam</t>
+        </is>
+      </c>
+      <c r="I24" s="7" t="inlineStr">
+        <is>
+          <t>3502469834</t>
+        </is>
+      </c>
+      <c r="J24" s="6" t="inlineStr">
+        <is>
+          <t>CÔNG TY TNHH MỘT THÀNH VIÊN VƯỜN PHỐ VŨNG TÀU</t>
+        </is>
+      </c>
+      <c r="K24" s="13" t="n">
+        <v>4600000.0</v>
+      </c>
+      <c r="L24" s="13" t="n">
+        <v>230000.0</v>
+      </c>
+      <c r="M24" s="13" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="N24" s="13"/>
+      <c r="O24" s="13" t="n">
+        <v>4830000.0</v>
+      </c>
+      <c r="P24" s="7" t="inlineStr">
+        <is>
+          <t>VND</t>
+        </is>
+      </c>
+      <c r="Q24" s="7" t="inlineStr">
+        <is>
+          <t>1.0</t>
+        </is>
+      </c>
+      <c r="R24" s="6" t="inlineStr">
+        <is>
+          <t>Hóa đơn mới</t>
+        </is>
+      </c>
+      <c r="S24" s="6" t="inlineStr">
+        <is>
+          <t>Đã cấp mã hóa đơn</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="4" t="n">
+        <v>19.0</v>
+      </c>
+      <c r="B25" s="7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C25" s="6" t="inlineStr">
+        <is>
+          <t>C25TBP</t>
+        </is>
+      </c>
+      <c r="D25" s="7" t="inlineStr">
+        <is>
+          <t>335</t>
+        </is>
+      </c>
+      <c r="E25" s="7" t="inlineStr">
+        <is>
+          <t>18/09/2025</t>
+        </is>
+      </c>
+      <c r="F25" s="7" t="inlineStr">
+        <is>
+          <t>3502431414</t>
+        </is>
+      </c>
+      <c r="G25" s="6" t="inlineStr">
+        <is>
+          <t>CÔNG TY TNHH THƯƠNG MẠI VÀ DỊCH VỤ MINH BÁCH PHÁT</t>
+        </is>
+      </c>
+      <c r="H25" s="6" t="inlineStr">
+        <is>
+          <t>144C/20 Đô Lương, Phường Phước Thắng, Thành phố Hồ Chí Minh, Việt Nam</t>
+        </is>
+      </c>
+      <c r="I25" s="7" t="inlineStr">
+        <is>
+          <t>3502469834</t>
+        </is>
+      </c>
+      <c r="J25" s="6" t="inlineStr">
+        <is>
+          <t>CÔNG TY TNHH MỘT THÀNH VIÊN VƯỜN PHỐ VŨNG TÀU</t>
+        </is>
+      </c>
+      <c r="K25" s="13" t="n">
+        <v>4700000.0</v>
+      </c>
+      <c r="L25" s="13" t="n">
+        <v>235000.0</v>
+      </c>
+      <c r="M25" s="13" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="N25" s="13"/>
+      <c r="O25" s="13" t="n">
+        <v>4935000.0</v>
+      </c>
+      <c r="P25" s="7" t="inlineStr">
+        <is>
+          <t>VND</t>
+        </is>
+      </c>
+      <c r="Q25" s="7" t="inlineStr">
+        <is>
+          <t>1.0</t>
+        </is>
+      </c>
+      <c r="R25" s="6" t="inlineStr">
+        <is>
+          <t>Hóa đơn mới</t>
+        </is>
+      </c>
+      <c r="S25" s="6" t="inlineStr">
+        <is>
+          <t>Đã cấp mã hóa đơn</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="4" t="n">
+        <v>20.0</v>
+      </c>
+      <c r="B26" s="7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C26" s="6" t="inlineStr">
+        <is>
+          <t>C25TBP</t>
+        </is>
+      </c>
+      <c r="D26" s="7" t="inlineStr">
+        <is>
+          <t>338</t>
+        </is>
+      </c>
+      <c r="E26" s="7" t="inlineStr">
+        <is>
+          <t>19/09/2025</t>
+        </is>
+      </c>
+      <c r="F26" s="7" t="inlineStr">
+        <is>
+          <t>3502431414</t>
+        </is>
+      </c>
+      <c r="G26" s="6" t="inlineStr">
+        <is>
+          <t>CÔNG TY TNHH THƯƠNG MẠI VÀ DỊCH VỤ MINH BÁCH PHÁT</t>
+        </is>
+      </c>
+      <c r="H26" s="6" t="inlineStr">
+        <is>
+          <t>144C/20 Đô Lương, Phường Phước Thắng, Thành phố Hồ Chí Minh, Việt Nam</t>
+        </is>
+      </c>
+      <c r="I26" s="7" t="inlineStr">
+        <is>
+          <t>3502469834</t>
+        </is>
+      </c>
+      <c r="J26" s="6" t="inlineStr">
+        <is>
+          <t>CÔNG TY TNHH MỘT THÀNH VIÊN VƯỜN PHỐ VŨNG TÀU</t>
+        </is>
+      </c>
+      <c r="K26" s="13" t="n">
+        <v>4660000.0</v>
+      </c>
+      <c r="L26" s="13" t="n">
+        <v>233000.0</v>
+      </c>
+      <c r="M26" s="13" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="N26" s="13"/>
+      <c r="O26" s="13" t="n">
+        <v>4893000.0</v>
+      </c>
+      <c r="P26" s="7" t="inlineStr">
+        <is>
+          <t>VND</t>
+        </is>
+      </c>
+      <c r="Q26" s="7" t="inlineStr">
+        <is>
+          <t>1.0</t>
+        </is>
+      </c>
+      <c r="R26" s="6" t="inlineStr">
+        <is>
+          <t>Hóa đơn mới</t>
+        </is>
+      </c>
+      <c r="S26" s="6" t="inlineStr">
+        <is>
+          <t>Đã cấp mã hóa đơn</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="4" t="n">
+        <v>21.0</v>
+      </c>
+      <c r="B27" s="7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C27" s="6" t="inlineStr">
+        <is>
+          <t>C25TBP</t>
+        </is>
+      </c>
+      <c r="D27" s="7" t="inlineStr">
+        <is>
+          <t>339</t>
+        </is>
+      </c>
+      <c r="E27" s="7" t="inlineStr">
+        <is>
+          <t>20/09/2025</t>
+        </is>
+      </c>
+      <c r="F27" s="7" t="inlineStr">
+        <is>
+          <t>3502431414</t>
+        </is>
+      </c>
+      <c r="G27" s="6" t="inlineStr">
+        <is>
+          <t>CÔNG TY TNHH THƯƠNG MẠI VÀ DỊCH VỤ MINH BÁCH PHÁT</t>
+        </is>
+      </c>
+      <c r="H27" s="6" t="inlineStr">
+        <is>
+          <t>144C/20 Đô Lương, Phường Phước Thắng, Thành phố Hồ Chí Minh, Việt Nam</t>
+        </is>
+      </c>
+      <c r="I27" s="7" t="inlineStr">
+        <is>
+          <t>3502469834</t>
+        </is>
+      </c>
+      <c r="J27" s="6" t="inlineStr">
+        <is>
+          <t>CÔNG TY TNHH MỘT THÀNH VIÊN VƯỜN PHỐ VŨNG TÀU</t>
+        </is>
+      </c>
+      <c r="K27" s="13" t="n">
+        <v>4760000.0</v>
+      </c>
+      <c r="L27" s="13" t="n">
+        <v>238000.0</v>
+      </c>
+      <c r="M27" s="13" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="N27" s="13"/>
+      <c r="O27" s="13" t="n">
+        <v>4998000.0</v>
+      </c>
+      <c r="P27" s="7" t="inlineStr">
+        <is>
+          <t>VND</t>
+        </is>
+      </c>
+      <c r="Q27" s="7" t="inlineStr">
+        <is>
+          <t>1.0</t>
+        </is>
+      </c>
+      <c r="R27" s="6" t="inlineStr">
+        <is>
+          <t>Hóa đơn mới</t>
+        </is>
+      </c>
+      <c r="S27" s="6" t="inlineStr">
+        <is>
+          <t>Đã cấp mã hóa đơn</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="4" t="n">
+        <v>22.0</v>
+      </c>
+      <c r="B28" s="7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C28" s="6" t="inlineStr">
+        <is>
+          <t>C25TBP</t>
+        </is>
+      </c>
+      <c r="D28" s="7" t="inlineStr">
+        <is>
+          <t>343</t>
+        </is>
+      </c>
+      <c r="E28" s="7" t="inlineStr">
+        <is>
+          <t>22/09/2025</t>
+        </is>
+      </c>
+      <c r="F28" s="7" t="inlineStr">
+        <is>
+          <t>3502431414</t>
+        </is>
+      </c>
+      <c r="G28" s="6" t="inlineStr">
+        <is>
+          <t>CÔNG TY TNHH THƯƠNG MẠI VÀ DỊCH VỤ MINH BÁCH PHÁT</t>
+        </is>
+      </c>
+      <c r="H28" s="6" t="inlineStr">
+        <is>
+          <t>144C/20 Đô Lương, Phường Phước Thắng, Thành phố Hồ Chí Minh, Việt Nam</t>
+        </is>
+      </c>
+      <c r="I28" s="7" t="inlineStr">
+        <is>
+          <t>3502469834</t>
+        </is>
+      </c>
+      <c r="J28" s="6" t="inlineStr">
+        <is>
+          <t>CÔNG TY TNHH MỘT THÀNH VIÊN VƯỜN PHỐ VŨNG TÀU</t>
+        </is>
+      </c>
+      <c r="K28" s="13" t="n">
+        <v>4750000.0</v>
+      </c>
+      <c r="L28" s="13" t="n">
+        <v>237500.0</v>
+      </c>
+      <c r="M28" s="13" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="N28" s="13"/>
+      <c r="O28" s="13" t="n">
+        <v>4987500.0</v>
+      </c>
+      <c r="P28" s="7" t="inlineStr">
+        <is>
+          <t>VND</t>
+        </is>
+      </c>
+      <c r="Q28" s="7" t="inlineStr">
+        <is>
+          <t>1.0</t>
+        </is>
+      </c>
+      <c r="R28" s="6" t="inlineStr">
+        <is>
+          <t>Hóa đơn mới</t>
+        </is>
+      </c>
+      <c r="S28" s="6" t="inlineStr">
+        <is>
+          <t>Đã cấp mã hóa đơn</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="4" t="n">
+        <v>23.0</v>
+      </c>
+      <c r="B29" s="7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C29" s="6" t="inlineStr">
+        <is>
+          <t>C25TBP</t>
+        </is>
+      </c>
+      <c r="D29" s="7" t="inlineStr">
+        <is>
+          <t>347</t>
+        </is>
+      </c>
+      <c r="E29" s="7" t="inlineStr">
+        <is>
+          <t>23/09/2025</t>
+        </is>
+      </c>
+      <c r="F29" s="7" t="inlineStr">
+        <is>
+          <t>3502431414</t>
+        </is>
+      </c>
+      <c r="G29" s="6" t="inlineStr">
+        <is>
+          <t>CÔNG TY TNHH THƯƠNG MẠI VÀ DỊCH VỤ MINH BÁCH PHÁT</t>
+        </is>
+      </c>
+      <c r="H29" s="6" t="inlineStr">
+        <is>
+          <t>144C/20 Đô Lương, Phường Phước Thắng, Thành phố Hồ Chí Minh, Việt Nam</t>
+        </is>
+      </c>
+      <c r="I29" s="7" t="inlineStr">
+        <is>
+          <t>3502469834</t>
+        </is>
+      </c>
+      <c r="J29" s="6" t="inlineStr">
+        <is>
+          <t>CÔNG TY TNHH MỘT THÀNH VIÊN VƯỜN PHỐ VŨNG TÀU</t>
+        </is>
+      </c>
+      <c r="K29" s="13" t="n">
+        <v>4710000.0</v>
+      </c>
+      <c r="L29" s="13" t="n">
+        <v>235500.0</v>
+      </c>
+      <c r="M29" s="13" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="N29" s="13"/>
+      <c r="O29" s="13" t="n">
+        <v>4945500.0</v>
+      </c>
+      <c r="P29" s="7" t="inlineStr">
+        <is>
+          <t>VND</t>
+        </is>
+      </c>
+      <c r="Q29" s="7" t="inlineStr">
+        <is>
+          <t>1.0</t>
+        </is>
+      </c>
+      <c r="R29" s="6" t="inlineStr">
+        <is>
+          <t>Hóa đơn mới</t>
+        </is>
+      </c>
+      <c r="S29" s="6" t="inlineStr">
+        <is>
+          <t>Đã cấp mã hóa đơn</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="4" t="n">
+        <v>24.0</v>
+      </c>
+      <c r="B30" s="7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C30" s="6" t="inlineStr">
+        <is>
+          <t>C25TCH</t>
+        </is>
+      </c>
+      <c r="D30" s="7" t="inlineStr">
+        <is>
+          <t>181</t>
+        </is>
+      </c>
+      <c r="E30" s="7" t="inlineStr">
+        <is>
+          <t>05/09/2025</t>
+        </is>
+      </c>
+      <c r="F30" s="7" t="inlineStr">
+        <is>
+          <t>3502470942</t>
+        </is>
+      </c>
+      <c r="G30" s="6" t="inlineStr">
+        <is>
+          <t>CÔNG TY TNHH THỰC PHẨM CAO HÂN</t>
+        </is>
+      </c>
+      <c r="H30" s="6" t="inlineStr">
+        <is>
+          <t>142 Xô Viết Nghệ Tĩnh, Phường Vũng Tàu, Thành phố Hồ Chí Minh, Việt Nam</t>
+        </is>
+      </c>
+      <c r="I30" s="7" t="inlineStr">
+        <is>
+          <t>3502469834</t>
+        </is>
+      </c>
+      <c r="J30" s="6" t="inlineStr">
+        <is>
+          <t>CÔNG TY TNHH MỘT THÀNH VIÊN VƯỜN PHỐ VŨNG TÀU</t>
+        </is>
+      </c>
+      <c r="K30" s="13" t="n">
+        <v>4666675.0</v>
+      </c>
+      <c r="L30" s="13" t="n">
+        <v>233334.0</v>
+      </c>
+      <c r="M30" s="13"/>
+      <c r="N30" s="13"/>
+      <c r="O30" s="13" t="n">
+        <v>4900009.0</v>
+      </c>
+      <c r="P30" s="7" t="inlineStr">
+        <is>
+          <t>VND</t>
+        </is>
+      </c>
+      <c r="Q30" s="7" t="inlineStr">
+        <is>
+          <t>1.0</t>
+        </is>
+      </c>
+      <c r="R30" s="6" t="inlineStr">
+        <is>
+          <t>Hóa đơn mới</t>
+        </is>
+      </c>
+      <c r="S30" s="6" t="inlineStr">
+        <is>
+          <t>Đã cấp mã hóa đơn</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="4" t="n">
+        <v>25.0</v>
+      </c>
+      <c r="B31" s="7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C31" s="6" t="inlineStr">
+        <is>
+          <t>C25TCH</t>
+        </is>
+      </c>
+      <c r="D31" s="7" t="inlineStr">
+        <is>
+          <t>192</t>
+        </is>
+      </c>
+      <c r="E31" s="7" t="inlineStr">
+        <is>
+          <t>12/09/2025</t>
+        </is>
+      </c>
+      <c r="F31" s="7" t="inlineStr">
+        <is>
+          <t>3502470942</t>
+        </is>
+      </c>
+      <c r="G31" s="6" t="inlineStr">
+        <is>
+          <t>CÔNG TY TNHH THỰC PHẨM CAO HÂN</t>
+        </is>
+      </c>
+      <c r="H31" s="6" t="inlineStr">
+        <is>
+          <t>142 Xô Viết Nghệ Tĩnh, Phường Vũng Tàu, Thành phố Hồ Chí Minh, Việt Nam</t>
+        </is>
+      </c>
+      <c r="I31" s="7" t="inlineStr">
+        <is>
+          <t>3502469834</t>
+        </is>
+      </c>
+      <c r="J31" s="6" t="inlineStr">
+        <is>
+          <t>CÔNG TY TNHH MỘT THÀNH VIÊN VƯỜN PHỐ VŨNG TÀU</t>
+        </is>
+      </c>
+      <c r="K31" s="13" t="n">
+        <v>4571430.0</v>
+      </c>
+      <c r="L31" s="13" t="n">
+        <v>228572.0</v>
+      </c>
+      <c r="M31" s="13"/>
+      <c r="N31" s="13"/>
+      <c r="O31" s="13" t="n">
+        <v>4800002.0</v>
+      </c>
+      <c r="P31" s="7" t="inlineStr">
+        <is>
+          <t>VND</t>
+        </is>
+      </c>
+      <c r="Q31" s="7" t="inlineStr">
+        <is>
+          <t>1.0</t>
+        </is>
+      </c>
+      <c r="R31" s="6" t="inlineStr">
+        <is>
+          <t>Hóa đơn mới</t>
+        </is>
+      </c>
+      <c r="S31" s="6" t="inlineStr">
+        <is>
+          <t>Đã cấp mã hóa đơn</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="4" t="n">
+        <v>26.0</v>
+      </c>
+      <c r="B32" s="7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C32" s="6" t="inlineStr">
+        <is>
+          <t>C25TCH</t>
+        </is>
+      </c>
+      <c r="D32" s="7" t="inlineStr">
+        <is>
+          <t>216</t>
+        </is>
+      </c>
+      <c r="E32" s="7" t="inlineStr">
+        <is>
+          <t>29/09/2025</t>
+        </is>
+      </c>
+      <c r="F32" s="7" t="inlineStr">
+        <is>
+          <t>3502470942</t>
+        </is>
+      </c>
+      <c r="G32" s="6" t="inlineStr">
+        <is>
+          <t>CÔNG TY TNHH THỰC PHẨM CAO HÂN</t>
+        </is>
+      </c>
+      <c r="H32" s="6" t="inlineStr">
+        <is>
+          <t>142 Xô Viết Nghệ Tĩnh, Phường Vũng Tàu, Thành phố Hồ Chí Minh, Việt Nam</t>
+        </is>
+      </c>
+      <c r="I32" s="7" t="inlineStr">
+        <is>
+          <t>3502469834</t>
+        </is>
+      </c>
+      <c r="J32" s="6" t="inlineStr">
+        <is>
+          <t>CÔNG TY TNHH MỘT THÀNH VIÊN VƯỜN PHỐ VŨNG TÀU</t>
+        </is>
+      </c>
+      <c r="K32" s="13" t="n">
+        <v>4381260.0</v>
+      </c>
+      <c r="L32" s="13" t="n">
+        <v>219063.0</v>
+      </c>
+      <c r="M32" s="13"/>
+      <c r="N32" s="13"/>
+      <c r="O32" s="13" t="n">
+        <v>4600323.0</v>
+      </c>
+      <c r="P32" s="7" t="inlineStr">
+        <is>
+          <t>VND</t>
+        </is>
+      </c>
+      <c r="Q32" s="7" t="inlineStr">
+        <is>
+          <t>1.0</t>
+        </is>
+      </c>
+      <c r="R32" s="6" t="inlineStr">
+        <is>
+          <t>Hóa đơn mới</t>
+        </is>
+      </c>
+      <c r="S32" s="6" t="inlineStr">
+        <is>
+          <t>Đã cấp mã hóa đơn</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="4" t="n">
+        <v>27.0</v>
+      </c>
+      <c r="B33" s="7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C33" s="6" t="inlineStr">
+        <is>
+          <t>C25TCH</t>
+        </is>
+      </c>
+      <c r="D33" s="7" t="inlineStr">
+        <is>
+          <t>221</t>
+        </is>
+      </c>
+      <c r="E33" s="7" t="inlineStr">
+        <is>
+          <t>30/09/2025</t>
+        </is>
+      </c>
+      <c r="F33" s="7" t="inlineStr">
+        <is>
+          <t>3502470942</t>
+        </is>
+      </c>
+      <c r="G33" s="6" t="inlineStr">
+        <is>
+          <t>CÔNG TY TNHH THỰC PHẨM CAO HÂN</t>
+        </is>
+      </c>
+      <c r="H33" s="6" t="inlineStr">
+        <is>
+          <t>142 Xô Viết Nghệ Tĩnh, Phường Vũng Tàu, Thành phố Hồ Chí Minh, Việt Nam</t>
+        </is>
+      </c>
+      <c r="I33" s="7" t="inlineStr">
+        <is>
+          <t>3502469834</t>
+        </is>
+      </c>
+      <c r="J33" s="6" t="inlineStr">
+        <is>
+          <t>CÔNG TY TNHH MỘT THÀNH VIÊN VƯỜN PHỐ VŨNG TÀU</t>
+        </is>
+      </c>
+      <c r="K33" s="13" t="n">
+        <v>4667440.0</v>
+      </c>
+      <c r="L33" s="13" t="n">
+        <v>233372.0</v>
+      </c>
+      <c r="M33" s="13"/>
+      <c r="N33" s="13"/>
+      <c r="O33" s="13" t="n">
+        <v>4900812.0</v>
+      </c>
+      <c r="P33" s="7" t="inlineStr">
+        <is>
+          <t>VND</t>
+        </is>
+      </c>
+      <c r="Q33" s="7" t="inlineStr">
+        <is>
+          <t>1.0</t>
+        </is>
+      </c>
+      <c r="R33" s="6" t="inlineStr">
+        <is>
+          <t>Hóa đơn mới</t>
+        </is>
+      </c>
+      <c r="S33" s="6" t="inlineStr">
+        <is>
+          <t>Đã cấp mã hóa đơn</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="4" t="n">
+        <v>28.0</v>
+      </c>
+      <c r="B34" s="7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C34" s="6" t="inlineStr">
+        <is>
+          <t>C25TMQ</t>
+        </is>
+      </c>
+      <c r="D34" s="7" t="inlineStr">
+        <is>
+          <t>3692</t>
+        </is>
+      </c>
+      <c r="E34" s="7" t="inlineStr">
+        <is>
+          <t>05/09/2025</t>
+        </is>
+      </c>
+      <c r="F34" s="7" t="inlineStr">
+        <is>
+          <t>3502479416</t>
+        </is>
+      </c>
+      <c r="G34" s="6" t="inlineStr">
+        <is>
+          <t>CÔNG TY CỔ PHẦN THỰC PHẨM MINH QUÂN FOOD</t>
+        </is>
+      </c>
+      <c r="H34" s="6" t="inlineStr">
+        <is>
+          <t>Số 516 đường Thống Nhất ,Phường Tam Thắng ,Thành Phố Hồ Chí Minh, Việt Nam</t>
+        </is>
+      </c>
+      <c r="I34" s="7" t="inlineStr">
+        <is>
+          <t>3502469834</t>
+        </is>
+      </c>
+      <c r="J34" s="6" t="inlineStr">
+        <is>
+          <t>CÔNG TY TNHH MỘT THÀNH VIÊN VƯỜN PHỐ VŨNG TÀU</t>
+        </is>
+      </c>
+      <c r="K34" s="13" t="n">
+        <v>2280000.0</v>
+      </c>
+      <c r="L34" s="13" t="n">
+        <v>147000.0</v>
+      </c>
+      <c r="M34" s="13" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="N34" s="13"/>
+      <c r="O34" s="13" t="n">
+        <v>2427000.0</v>
+      </c>
+      <c r="P34" s="7" t="inlineStr">
+        <is>
+          <t>VND</t>
+        </is>
+      </c>
+      <c r="Q34" s="7" t="inlineStr">
+        <is>
+          <t>1.0</t>
+        </is>
+      </c>
+      <c r="R34" s="6" t="inlineStr">
+        <is>
+          <t>Hóa đơn mới</t>
+        </is>
+      </c>
+      <c r="S34" s="6" t="inlineStr">
+        <is>
+          <t>Đã cấp mã hóa đơn</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="4" t="n">
+        <v>29.0</v>
+      </c>
+      <c r="B35" s="7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C35" s="6" t="inlineStr">
+        <is>
+          <t>C25THP</t>
+        </is>
+      </c>
+      <c r="D35" s="7" t="inlineStr">
+        <is>
+          <t>70</t>
+        </is>
+      </c>
+      <c r="E35" s="7" t="inlineStr">
+        <is>
+          <t>16/09/2025</t>
+        </is>
+      </c>
+      <c r="F35" s="7" t="inlineStr">
+        <is>
+          <t>3502550066</t>
+        </is>
+      </c>
+      <c r="G35" s="6" t="inlineStr">
+        <is>
+          <t>CÔNG TY TNHH HỒNG PHÁT VŨNG TÀU</t>
+        </is>
+      </c>
+      <c r="H35" s="6" t="inlineStr">
+        <is>
+          <t>20, Tô Hiến Thành, Phường Vũng Tàu, Thành phố Hồ Chí Minh</t>
+        </is>
+      </c>
+      <c r="I35" s="7" t="inlineStr">
+        <is>
+          <t>3502469834</t>
+        </is>
+      </c>
+      <c r="J35" s="6" t="inlineStr">
+        <is>
+          <t>CÔNG TY TNHH MỘT THÀNH VIÊN VƯỜN PHỐ VŨNG TÀU</t>
+        </is>
+      </c>
+      <c r="K35" s="13" t="n">
+        <v>2422574.0</v>
+      </c>
+      <c r="L35" s="13" t="n">
+        <v>193806.0</v>
+      </c>
+      <c r="M35" s="13" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="N35" s="13"/>
+      <c r="O35" s="13" t="n">
+        <v>2616380.0</v>
+      </c>
+      <c r="P35" s="7" t="inlineStr">
+        <is>
+          <t>VND</t>
+        </is>
+      </c>
+      <c r="Q35" s="7" t="inlineStr">
+        <is>
+          <t>1.0</t>
+        </is>
+      </c>
+      <c r="R35" s="6" t="inlineStr">
+        <is>
+          <t>Hóa đơn mới</t>
+        </is>
+      </c>
+      <c r="S35" s="6" t="inlineStr">
+        <is>
+          <t>Đã cấp mã hóa đơn</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="4" t="n">
+        <v>30.0</v>
+      </c>
+      <c r="B36" s="7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C36" s="6" t="inlineStr">
+        <is>
+          <t>C25TLN</t>
+        </is>
+      </c>
+      <c r="D36" s="7" t="inlineStr">
+        <is>
+          <t>807</t>
+        </is>
+      </c>
+      <c r="E36" s="7" t="inlineStr">
+        <is>
+          <t>27/09/2025</t>
+        </is>
+      </c>
+      <c r="F36" s="7" t="inlineStr">
+        <is>
+          <t>3602750365</t>
+        </is>
+      </c>
+      <c r="G36" s="6" t="inlineStr">
+        <is>
+          <t>CÔNG TY TNHH MỘT THÀNH VIÊN CỒN - LÊ NGUYỄN</t>
+        </is>
+      </c>
+      <c r="H36" s="6" t="inlineStr">
+        <is>
+          <t>A2/189 B, KP 2, Phường Biên Hòa, Tỉnh Đồng Nai, Việt Nam</t>
+        </is>
+      </c>
+      <c r="I36" s="7" t="inlineStr">
+        <is>
+          <t>3502469834</t>
+        </is>
+      </c>
+      <c r="J36" s="6" t="inlineStr">
+        <is>
+          <t>CÔNG TY TNHH MỘT THÀNH VIÊN VƯỜN PHỐ VŨNG TÀU</t>
+        </is>
+      </c>
+      <c r="K36" s="13" t="n">
+        <v>4254640.0</v>
+      </c>
+      <c r="L36" s="13" t="n">
+        <v>340371.0</v>
+      </c>
+      <c r="M36" s="13"/>
+      <c r="N36" s="13"/>
+      <c r="O36" s="13" t="n">
+        <v>4595011.0</v>
+      </c>
+      <c r="P36" s="7" t="inlineStr">
+        <is>
+          <t>VND</t>
+        </is>
+      </c>
+      <c r="Q36" s="7" t="inlineStr">
+        <is>
+          <t>1.0</t>
+        </is>
+      </c>
+      <c r="R36" s="6" t="inlineStr">
+        <is>
+          <t>Hóa đơn mới</t>
+        </is>
+      </c>
+      <c r="S36" s="6" t="inlineStr">
         <is>
           <t>Đã cấp mã hóa đơn</t>
         </is>

--- a/Hoadon/HDVao/9/HDDienTuDaCapMa.xlsx
+++ b/Hoadon/HDVao/9/HDDienTuDaCapMa.xlsx
@@ -325,56 +325,56 @@
       </c>
       <c r="C7" s="6" t="inlineStr">
         <is>
-          <t>C25TAA</t>
+          <t>C25TEM</t>
         </is>
       </c>
       <c r="D7" s="7" t="inlineStr">
         <is>
-          <t>406408</t>
+          <t>6923246</t>
         </is>
       </c>
       <c r="E7" s="7" t="inlineStr">
         <is>
-          <t>24/09/2025</t>
+          <t>30/09/2025</t>
         </is>
       </c>
       <c r="F7" s="7" t="inlineStr">
         <is>
-          <t>0108930466</t>
+          <t>0109266456</t>
         </is>
       </c>
       <c r="G7" s="6" t="inlineStr">
         <is>
-          <t>CÔNG TY TNHH ĐẦU TƯ VÀ PHÁT TRIỂN HỆ THỐNG ĐẤU THẦU QUA MẠNG QUỐC GIA</t>
+          <t>CÔNG TY CỔ PHẦN GIAO THÔNG SỐ VIỆT NAM</t>
         </is>
       </c>
       <c r="H7" s="6" t="inlineStr">
         <is>
-          <t>Tầng 8, Tòa tháp VIT TOWER, số 519, Phố Kim Mã, Phường Giảng Võ, Thành phố Hà Nội, Việt Nam.</t>
+          <t>Số 01 đường Trần Hữu Dực, Phường Từ Liêm, Thành phố Hà Nội, Việt Nam</t>
         </is>
       </c>
       <c r="I7" s="7" t="inlineStr">
         <is>
-          <t>3502245376</t>
+          <t>3502217971</t>
         </is>
       </c>
       <c r="J7" s="6" t="inlineStr">
         <is>
-          <t>CÔNG TY CỔ PHẦN ĐẦU TƯ XÂY DỰNG THƯƠNG MẠI DỊCH VỤ KỸ THUẬT H &amp; V</t>
+          <t>Công Ty Trách nhiệm hữu hạn đại lý tàu biển vũng tàu</t>
         </is>
       </c>
       <c r="K7" s="13" t="n">
-        <v>305556.0</v>
+        <v>63889.0</v>
       </c>
       <c r="L7" s="13" t="n">
-        <v>24444.0</v>
+        <v>5111.0</v>
       </c>
       <c r="M7" s="13" t="n">
         <v>0.0</v>
       </c>
       <c r="N7" s="13"/>
       <c r="O7" s="13" t="n">
-        <v>330000.0</v>
+        <v>69000.0</v>
       </c>
       <c r="P7" s="7" t="inlineStr">
         <is>
@@ -408,54 +408,56 @@
       </c>
       <c r="C8" s="6" t="inlineStr">
         <is>
-          <t>C25TVF</t>
+          <t>C25TDH</t>
         </is>
       </c>
       <c r="D8" s="7" t="inlineStr">
         <is>
-          <t>43388</t>
+          <t>1263</t>
         </is>
       </c>
       <c r="E8" s="7" t="inlineStr">
         <is>
-          <t>10/09/2025</t>
+          <t>23/09/2025</t>
         </is>
       </c>
       <c r="F8" s="7" t="inlineStr">
         <is>
-          <t>0303490096</t>
+          <t>0200429325</t>
         </is>
       </c>
       <c r="G8" s="6" t="inlineStr">
         <is>
-          <t>CÔNG TY CỔ PHẦN TẬP ĐOÀN VNG</t>
+          <t>TRƯỜNG CAO ĐẲNG KINH TẾ KỸ THUẬT CÔNG NGHIỆP</t>
         </is>
       </c>
       <c r="H8" s="6" t="inlineStr">
         <is>
-          <t>Z06, Đường số 13, Phường Tân Thuận, Thành phố Hồ Chí Minh, Việt Nam</t>
+          <t>Số 156/109 Đường Trường Chinh, Cụm Công nghiệp Đồng Hòa, Phường Kiến An, Thành phố Hải Phòng, Việt Nam.</t>
         </is>
       </c>
       <c r="I8" s="7" t="inlineStr">
         <is>
-          <t>3502245376</t>
+          <t>3502217971</t>
         </is>
       </c>
       <c r="J8" s="6" t="inlineStr">
         <is>
-          <t>Công ty Cổ phần đầu tư thương mại dịch vụ kỹ thuật H&amp;V</t>
+          <t>CÔNG TY TRÁCH NHIỆM HỮU HẠN ĐẠI LÝ TÀU BIỂN VŨNG TÀU</t>
         </is>
       </c>
       <c r="K8" s="13" t="n">
-        <v>445455.0</v>
+        <v>9400000.0</v>
       </c>
       <c r="L8" s="13" t="n">
-        <v>44545.0</v>
-      </c>
-      <c r="M8" s="13"/>
+        <v>0.0</v>
+      </c>
+      <c r="M8" s="13" t="n">
+        <v>0.0</v>
+      </c>
       <c r="N8" s="13"/>
       <c r="O8" s="13" t="n">
-        <v>490000.0</v>
+        <v>9400000.0</v>
       </c>
       <c r="P8" s="7" t="inlineStr">
         <is>
@@ -489,56 +491,56 @@
       </c>
       <c r="C9" s="6" t="inlineStr">
         <is>
-          <t>C25TSP</t>
+          <t>C25TBV</t>
         </is>
       </c>
       <c r="D9" s="7" t="inlineStr">
         <is>
-          <t>31589</t>
+          <t>11808</t>
         </is>
       </c>
       <c r="E9" s="7" t="inlineStr">
         <is>
-          <t>03/09/2025</t>
+          <t>25/09/2025</t>
         </is>
       </c>
       <c r="F9" s="7" t="inlineStr">
         <is>
-          <t>0304667885</t>
+          <t>0304998358-056</t>
         </is>
       </c>
       <c r="G9" s="6" t="inlineStr">
         <is>
-          <t>CÔNG TY CỔ PHẦN DẦU KHÍ MIỀN NAM</t>
+          <t>CHI NHÁNH 34 - CÔNG TY CỔ PHẦN THƯƠNG MẠI - DỊCH VỤ PHONG VŨ</t>
         </is>
       </c>
       <c r="H9" s="6" t="inlineStr">
         <is>
-          <t>86 Nguyễn Cửu Vân, Phường Gia Định, Thành phố Hồ Chí Minh, Việt Nam</t>
+          <t>L11 G2 Đường Nguyễn Thái Học,phường Tam Thắng, Thành phố Hồ Chí Minh, Việt Nam</t>
         </is>
       </c>
       <c r="I9" s="7" t="inlineStr">
         <is>
-          <t>3502245376</t>
+          <t>3502217971</t>
         </is>
       </c>
       <c r="J9" s="6" t="inlineStr">
         <is>
-          <t>CÔNG TY CỔ PHẦN ĐẦU TƯ XÂY DỰNG THƯƠNG MẠI DỊCH VỤ KỸ THUẬT H &amp; V</t>
+          <t>CÔNG TY TRÁCH NHIỆM HỮU HẠN ĐẠI LÝ TÀU BIỂN VŨNG TÀU</t>
         </is>
       </c>
       <c r="K9" s="13" t="n">
-        <v>566667.0</v>
+        <v>9874814.82</v>
       </c>
       <c r="L9" s="13" t="n">
-        <v>45333.0</v>
+        <v>789985.18</v>
       </c>
       <c r="M9" s="13" t="n">
         <v>0.0</v>
       </c>
       <c r="N9" s="13"/>
       <c r="O9" s="13" t="n">
-        <v>612000.0</v>
+        <v>1.06648E7</v>
       </c>
       <c r="P9" s="7" t="inlineStr">
         <is>
@@ -572,56 +574,56 @@
       </c>
       <c r="C10" s="6" t="inlineStr">
         <is>
-          <t>C25TSP</t>
+          <t>C25TCO</t>
         </is>
       </c>
       <c r="D10" s="7" t="inlineStr">
         <is>
-          <t>35298</t>
+          <t>6940</t>
         </is>
       </c>
       <c r="E10" s="7" t="inlineStr">
         <is>
-          <t>14/09/2025</t>
+          <t>18/09/2025</t>
         </is>
       </c>
       <c r="F10" s="7" t="inlineStr">
         <is>
-          <t>0304667885</t>
+          <t>0315360616</t>
         </is>
       </c>
       <c r="G10" s="6" t="inlineStr">
         <is>
-          <t>CÔNG TY CỔ PHẦN DẦU KHÍ MIỀN NAM</t>
+          <t>CÔNG TY TNHH SẢN XUẤT VÀ THƯƠNG MẠI DỊCH VỤ BICOM</t>
         </is>
       </c>
       <c r="H10" s="6" t="inlineStr">
         <is>
-          <t>86 Nguyễn Cửu Vân, Phường Gia Định, Thành phố Hồ Chí Minh, Việt Nam</t>
+          <t>Toà nha Sabay, 99 Cộng Hoà, Phường Tân Sơn Nhất, Thành phố Hồ Chí Minh, Việt Nam</t>
         </is>
       </c>
       <c r="I10" s="7" t="inlineStr">
         <is>
-          <t>3502245376</t>
+          <t>3502217971</t>
         </is>
       </c>
       <c r="J10" s="6" t="inlineStr">
         <is>
-          <t>CÔNG TY CỔ PHẦN ĐẦU TƯ XÂY DỰNG THƯƠNG MẠI DỊCH VỤ KỸ THUẬT H &amp; V</t>
+          <t>CTY TNHH ĐẠI LÝ TÀU BIỂN VŨNG TÀU</t>
         </is>
       </c>
       <c r="K10" s="13" t="n">
-        <v>283333.0</v>
+        <v>32407.0</v>
       </c>
       <c r="L10" s="13" t="n">
-        <v>22667.0</v>
+        <v>2593.0</v>
       </c>
       <c r="M10" s="13" t="n">
         <v>0.0</v>
       </c>
       <c r="N10" s="13"/>
       <c r="O10" s="13" t="n">
-        <v>306000.0</v>
+        <v>35000.0</v>
       </c>
       <c r="P10" s="7" t="inlineStr">
         <is>
@@ -660,12 +662,12 @@
       </c>
       <c r="D11" s="7" t="inlineStr">
         <is>
-          <t>21405</t>
+          <t>22308</t>
         </is>
       </c>
       <c r="E11" s="7" t="inlineStr">
         <is>
-          <t>04/09/2025</t>
+          <t>15/09/2025</t>
         </is>
       </c>
       <c r="F11" s="7" t="inlineStr">
@@ -685,24 +687,24 @@
       </c>
       <c r="I11" s="7" t="inlineStr">
         <is>
-          <t>3502245376</t>
+          <t>3502217971</t>
         </is>
       </c>
       <c r="J11" s="6" t="inlineStr">
         <is>
-          <t>CÔNG TY CỔ PHẦN ĐẦU TƯ XÂY DỰNG THƯƠNG MẠI DỊCH VỤ KỸ THUẬT H&amp;V</t>
+          <t>CÔNG TY TRÁCH NHIỆM HỮU HẠN ĐẠI LÝ TÀU BIỂN VŨNG TÀU</t>
         </is>
       </c>
       <c r="K11" s="13" t="n">
-        <v>1.2E7</v>
+        <v>263636.0</v>
       </c>
       <c r="L11" s="13" t="n">
-        <v>1200000.0</v>
+        <v>21091.0</v>
       </c>
       <c r="M11" s="13"/>
       <c r="N11" s="13"/>
       <c r="O11" s="13" t="n">
-        <v>1.32E7</v>
+        <v>284727.0</v>
       </c>
       <c r="P11" s="7" t="inlineStr">
         <is>
@@ -736,56 +738,56 @@
       </c>
       <c r="C12" s="6" t="inlineStr">
         <is>
-          <t>C25TTT</t>
+          <t>C25TDK</t>
         </is>
       </c>
       <c r="D12" s="7" t="inlineStr">
         <is>
-          <t>7261</t>
+          <t>22342</t>
         </is>
       </c>
       <c r="E12" s="7" t="inlineStr">
         <is>
-          <t>20/09/2025</t>
+          <t>16/09/2025</t>
         </is>
       </c>
       <c r="F12" s="7" t="inlineStr">
         <is>
-          <t>3502252817</t>
+          <t>3500102326</t>
         </is>
       </c>
       <c r="G12" s="6" t="inlineStr">
         <is>
-          <t>CÔNG TY TNHH ĐẦU TƯ THƯƠNG MẠI DỊCH VỤ VIỆT TÍN THÀNH</t>
+          <t>TRUNG TÂM ĐĂNG KIỂM PHƯƠNG TIỆN GIAO THÔNG VẬN TẢI</t>
         </is>
       </c>
       <c r="H12" s="6" t="inlineStr">
         <is>
-          <t>Số 24/8 Lê Thánh Tông, Phường Rạch Dừa, Thành phố Hồ Chí Minh, Việt Nam.</t>
+          <t>47B Đường 30/4 - phường Rạch Dừa - TP. Hồ Chí Minh</t>
         </is>
       </c>
       <c r="I12" s="7" t="inlineStr">
         <is>
-          <t>3502245376</t>
+          <t>3502217971</t>
         </is>
       </c>
       <c r="J12" s="6" t="inlineStr">
         <is>
-          <t>CÔNG TY CỔ PHẦN ĐẦU TƯ XÂY DỰNG THƯƠNG MẠI DỊCH VỤ KỸ THUẬT H &amp; V</t>
+          <t>CÔNG TY TRÁCH NHIỆM HỮU HẠN ĐẠI LÝ TÀU BIỂN VŨNG TÀU</t>
         </is>
       </c>
       <c r="K12" s="13" t="n">
-        <v>1040741.0</v>
+        <v>131819.0</v>
       </c>
       <c r="L12" s="13" t="n">
-        <v>83259.0</v>
-      </c>
-      <c r="M12" s="13" t="n">
-        <v>0.0</v>
-      </c>
-      <c r="N12" s="13"/>
+        <v>10545.0</v>
+      </c>
+      <c r="M12" s="13"/>
+      <c r="N12" s="13" t="n">
+        <v>20000.0</v>
+      </c>
       <c r="O12" s="13" t="n">
-        <v>1124000.0</v>
+        <v>162364.0</v>
       </c>
       <c r="P12" s="7" t="inlineStr">
         <is>
@@ -819,56 +821,56 @@
       </c>
       <c r="C13" s="6" t="inlineStr">
         <is>
-          <t>C25TPA</t>
+          <t>C25TVR</t>
         </is>
       </c>
       <c r="D13" s="7" t="inlineStr">
         <is>
-          <t>78</t>
+          <t>49754</t>
         </is>
       </c>
       <c r="E13" s="7" t="inlineStr">
         <is>
-          <t>03/09/2025</t>
+          <t>05/09/2025</t>
         </is>
       </c>
       <c r="F13" s="7" t="inlineStr">
         <is>
-          <t>3502424618</t>
+          <t>3500704465</t>
         </is>
       </c>
       <c r="G13" s="6" t="inlineStr">
         <is>
-          <t>CÔNG TY TNHH THƯƠNG MẠI DỊCH VỤ XÂY DỰNG NGUYỄN PHÚC AN</t>
+          <t>CÔNG TY TNHH RỒNG VIỆT</t>
         </is>
       </c>
       <c r="H13" s="6" t="inlineStr">
         <is>
-          <t>Số 190 Lý Tự Trọng, Phường Vũng Tàu, TP Hồ Chí Minh, Việt Nam</t>
+          <t>Số 863 Đường 30/4, Phường Phước Thắng, Thành Phố Hồ Chí Minh, Việt Nam</t>
         </is>
       </c>
       <c r="I13" s="7" t="inlineStr">
         <is>
-          <t>3502245376</t>
+          <t>3502217971</t>
         </is>
       </c>
       <c r="J13" s="6" t="inlineStr">
         <is>
-          <t>CÔNG TY CỔ PHẦN ĐẦU TƯ XÂY DỰNG THƯƠNG MẠI DỊCH VỤ KỸ THUẬT H &amp; V</t>
+          <t>CÔNG TY TRÁCH NHIỆM HỮU HẠN ĐẠI LÝ TÀU BIỂN VŨNG TÀU</t>
         </is>
       </c>
       <c r="K13" s="13" t="n">
-        <v>2445000.0</v>
+        <v>3270000.0</v>
       </c>
       <c r="L13" s="13" t="n">
-        <v>195600.0</v>
+        <v>261600.0</v>
       </c>
       <c r="M13" s="13" t="n">
         <v>0.0</v>
       </c>
       <c r="N13" s="13"/>
       <c r="O13" s="13" t="n">
-        <v>2640600.0</v>
+        <v>3531600.0</v>
       </c>
       <c r="P13" s="7" t="inlineStr">
         <is>
@@ -886,6 +888,255 @@
         </is>
       </c>
       <c r="S13" s="6" t="inlineStr">
+        <is>
+          <t>Đã cấp mã hóa đơn</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="4" t="n">
+        <v>8.0</v>
+      </c>
+      <c r="B14" s="7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C14" s="6" t="inlineStr">
+        <is>
+          <t>C25TSV</t>
+        </is>
+      </c>
+      <c r="D14" s="7" t="inlineStr">
+        <is>
+          <t>150</t>
+        </is>
+      </c>
+      <c r="E14" s="7" t="inlineStr">
+        <is>
+          <t>19/09/2025</t>
+        </is>
+      </c>
+      <c r="F14" s="7" t="inlineStr">
+        <is>
+          <t>3500898348</t>
+        </is>
+      </c>
+      <c r="G14" s="6" t="inlineStr">
+        <is>
+          <t>CÔNG TY TNHH DỊCH VỤ THUẾ SAO VIỆT</t>
+        </is>
+      </c>
+      <c r="H14" s="6" t="inlineStr">
+        <is>
+          <t>Số 640 Trương Công Định, Phường Tam Thắng, TP. Hồ Chí Minh, Việt Nam</t>
+        </is>
+      </c>
+      <c r="I14" s="7" t="inlineStr">
+        <is>
+          <t>3502217971</t>
+        </is>
+      </c>
+      <c r="J14" s="6" t="inlineStr">
+        <is>
+          <t>CÔNG TY TRÁCH NHIỆM HỮU HẠN ĐẠI LÝ TÀU BIỂN VŨNG TÀU</t>
+        </is>
+      </c>
+      <c r="K14" s="13" t="n">
+        <v>9000000.0</v>
+      </c>
+      <c r="L14" s="13" t="n">
+        <v>720000.0</v>
+      </c>
+      <c r="M14" s="13" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="N14" s="13"/>
+      <c r="O14" s="13" t="n">
+        <v>9720000.0</v>
+      </c>
+      <c r="P14" s="7" t="inlineStr">
+        <is>
+          <t>VND</t>
+        </is>
+      </c>
+      <c r="Q14" s="7" t="inlineStr">
+        <is>
+          <t>1.0</t>
+        </is>
+      </c>
+      <c r="R14" s="6" t="inlineStr">
+        <is>
+          <t>Hóa đơn mới</t>
+        </is>
+      </c>
+      <c r="S14" s="6" t="inlineStr">
+        <is>
+          <t>Đã cấp mã hóa đơn</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="4" t="n">
+        <v>9.0</v>
+      </c>
+      <c r="B15" s="7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C15" s="6" t="inlineStr">
+        <is>
+          <t>C25TTT</t>
+        </is>
+      </c>
+      <c r="D15" s="7" t="inlineStr">
+        <is>
+          <t>106</t>
+        </is>
+      </c>
+      <c r="E15" s="7" t="inlineStr">
+        <is>
+          <t>03/09/2025</t>
+        </is>
+      </c>
+      <c r="F15" s="7" t="inlineStr">
+        <is>
+          <t>3502297046</t>
+        </is>
+      </c>
+      <c r="G15" s="6" t="inlineStr">
+        <is>
+          <t>CÔNG TY TNHH THƯƠNG MẠI DỊCH VỤ ĐIỆN LẠNH TÂN TIẾN VŨNG TÀU</t>
+        </is>
+      </c>
+      <c r="H15" s="6" t="inlineStr">
+        <is>
+          <t>Số 514 Nguyễn An Ninh, Phường Tam Thắng, Thành phố Hồ Chí Minh, Việt Nam</t>
+        </is>
+      </c>
+      <c r="I15" s="7" t="inlineStr">
+        <is>
+          <t>3502217971</t>
+        </is>
+      </c>
+      <c r="J15" s="6" t="inlineStr">
+        <is>
+          <t>CÔNG TY TNHH ĐẠI LÝ TÀU  BIỂN VŨNG TÀU</t>
+        </is>
+      </c>
+      <c r="K15" s="13" t="n">
+        <v>1.085818182E7</v>
+      </c>
+      <c r="L15" s="13" t="n">
+        <v>1085818.18</v>
+      </c>
+      <c r="M15" s="13" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="N15" s="13"/>
+      <c r="O15" s="13" t="n">
+        <v>1.1944E7</v>
+      </c>
+      <c r="P15" s="7" t="inlineStr">
+        <is>
+          <t>VND</t>
+        </is>
+      </c>
+      <c r="Q15" s="7" t="inlineStr">
+        <is>
+          <t>1.0</t>
+        </is>
+      </c>
+      <c r="R15" s="6" t="inlineStr">
+        <is>
+          <t>Hóa đơn mới</t>
+        </is>
+      </c>
+      <c r="S15" s="6" t="inlineStr">
+        <is>
+          <t>Đã cấp mã hóa đơn</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="4" t="n">
+        <v>10.0</v>
+      </c>
+      <c r="B16" s="7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C16" s="6" t="inlineStr">
+        <is>
+          <t>C25TAH</t>
+        </is>
+      </c>
+      <c r="D16" s="7" t="inlineStr">
+        <is>
+          <t>347</t>
+        </is>
+      </c>
+      <c r="E16" s="7" t="inlineStr">
+        <is>
+          <t>24/09/2025</t>
+        </is>
+      </c>
+      <c r="F16" s="7" t="inlineStr">
+        <is>
+          <t>3502496732</t>
+        </is>
+      </c>
+      <c r="G16" s="6" t="inlineStr">
+        <is>
+          <t>CÔNG TY TNHH HÀNG HẢI VÀ THƯƠNG MẠI AN HẢI</t>
+        </is>
+      </c>
+      <c r="H16" s="6" t="inlineStr">
+        <is>
+          <t>14/20 Kha Vạn Cân, Phường Tam Thắng, Thành phố Hồ Chí Minh, Việt Nam</t>
+        </is>
+      </c>
+      <c r="I16" s="7" t="inlineStr">
+        <is>
+          <t>3502217971</t>
+        </is>
+      </c>
+      <c r="J16" s="6" t="inlineStr">
+        <is>
+          <t>CÔNG TY TNHH ĐẠI LÝ TÀU BIỂN VŨNG TÀU</t>
+        </is>
+      </c>
+      <c r="K16" s="13" t="n">
+        <v>3900000.0</v>
+      </c>
+      <c r="L16" s="13" t="n">
+        <v>312000.0</v>
+      </c>
+      <c r="M16" s="13" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="N16" s="13"/>
+      <c r="O16" s="13" t="n">
+        <v>4212000.0</v>
+      </c>
+      <c r="P16" s="7" t="inlineStr">
+        <is>
+          <t>VND</t>
+        </is>
+      </c>
+      <c r="Q16" s="7" t="inlineStr">
+        <is>
+          <t>1.0</t>
+        </is>
+      </c>
+      <c r="R16" s="6" t="inlineStr">
+        <is>
+          <t>Hóa đơn mới</t>
+        </is>
+      </c>
+      <c r="S16" s="6" t="inlineStr">
         <is>
           <t>Đã cấp mã hóa đơn</t>
         </is>

--- a/Hoadon/HDVao/9/HDDienTuDaCapMa.xlsx
+++ b/Hoadon/HDVao/9/HDDienTuDaCapMa.xlsx
@@ -325,56 +325,56 @@
       </c>
       <c r="C7" s="6" t="inlineStr">
         <is>
-          <t>C25TNT</t>
+          <t>C25TBT</t>
         </is>
       </c>
       <c r="D7" s="7" t="inlineStr">
         <is>
-          <t>1638</t>
+          <t>1726</t>
         </is>
       </c>
       <c r="E7" s="7" t="inlineStr">
         <is>
-          <t>18/09/2025</t>
+          <t>30/09/2025</t>
         </is>
       </c>
       <c r="F7" s="7" t="inlineStr">
         <is>
-          <t>3500408138</t>
+          <t>3501772161</t>
         </is>
       </c>
       <c r="G7" s="6" t="inlineStr">
         <is>
-          <t>CÔNG TY TNHH NGHĨA THÀNH</t>
+          <t>CÔNG TY CỔ PHẦN BÊ TÔNG VÀ XÂY LẮP HODECO</t>
         </is>
       </c>
       <c r="H7" s="6" t="inlineStr">
         <is>
-          <t>Số 100 Bình Giã, Phường Tam Thắng, Thành phố Hồ Chí Minh, Việt Nam</t>
+          <t>Thôn 9 Gò Găng, Xã Long Sơn, Thành phố Hồ Chí Minh, Việt Nam.</t>
         </is>
       </c>
       <c r="I7" s="7" t="inlineStr">
         <is>
-          <t>3500826826</t>
+          <t>3502267355</t>
         </is>
       </c>
       <c r="J7" s="6" t="inlineStr">
         <is>
-          <t>CÔNG TY TNHH NGUYÊN KHANG</t>
+          <t>CÔNG TY TNHH XÂY DỰNG NGỌC TRÂN</t>
         </is>
       </c>
       <c r="K7" s="13" t="n">
-        <v>1.6851852E7</v>
+        <v>4.1188889E7</v>
       </c>
       <c r="L7" s="13" t="n">
-        <v>1348148.0</v>
+        <v>3295111.0</v>
       </c>
       <c r="M7" s="13" t="n">
         <v>0.0</v>
       </c>
       <c r="N7" s="13"/>
       <c r="O7" s="13" t="n">
-        <v>1.82E7</v>
+        <v>4.4484E7</v>
       </c>
       <c r="P7" s="7" t="inlineStr">
         <is>
@@ -392,338 +392,6 @@
         </is>
       </c>
       <c r="S7" s="6" t="inlineStr">
-        <is>
-          <t>Đã cấp mã hóa đơn</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" s="4" t="n">
-        <v>2.0</v>
-      </c>
-      <c r="B8" s="7" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="C8" s="6" t="inlineStr">
-        <is>
-          <t>C25TNT</t>
-        </is>
-      </c>
-      <c r="D8" s="7" t="inlineStr">
-        <is>
-          <t>1690</t>
-        </is>
-      </c>
-      <c r="E8" s="7" t="inlineStr">
-        <is>
-          <t>30/09/2025</t>
-        </is>
-      </c>
-      <c r="F8" s="7" t="inlineStr">
-        <is>
-          <t>3500408138</t>
-        </is>
-      </c>
-      <c r="G8" s="6" t="inlineStr">
-        <is>
-          <t>CÔNG TY TNHH NGHĨA THÀNH</t>
-        </is>
-      </c>
-      <c r="H8" s="6" t="inlineStr">
-        <is>
-          <t>Số 100 Bình Giã, Phường Tam Thắng, Thành phố Hồ Chí Minh, Việt Nam</t>
-        </is>
-      </c>
-      <c r="I8" s="7" t="inlineStr">
-        <is>
-          <t>3500826826</t>
-        </is>
-      </c>
-      <c r="J8" s="6" t="inlineStr">
-        <is>
-          <t>CÔNG TY TNHH NGUYÊN KHANG</t>
-        </is>
-      </c>
-      <c r="K8" s="13" t="n">
-        <v>1.2037037E7</v>
-      </c>
-      <c r="L8" s="13" t="n">
-        <v>962963.0</v>
-      </c>
-      <c r="M8" s="13" t="n">
-        <v>0.0</v>
-      </c>
-      <c r="N8" s="13"/>
-      <c r="O8" s="13" t="n">
-        <v>1.3E7</v>
-      </c>
-      <c r="P8" s="7" t="inlineStr">
-        <is>
-          <t>VND</t>
-        </is>
-      </c>
-      <c r="Q8" s="7" t="inlineStr">
-        <is>
-          <t>1.0</t>
-        </is>
-      </c>
-      <c r="R8" s="6" t="inlineStr">
-        <is>
-          <t>Hóa đơn mới</t>
-        </is>
-      </c>
-      <c r="S8" s="6" t="inlineStr">
-        <is>
-          <t>Đã cấp mã hóa đơn</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" s="4" t="n">
-        <v>3.0</v>
-      </c>
-      <c r="B9" s="7" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="C9" s="6" t="inlineStr">
-        <is>
-          <t>C25TCL</t>
-        </is>
-      </c>
-      <c r="D9" s="7" t="inlineStr">
-        <is>
-          <t>7118</t>
-        </is>
-      </c>
-      <c r="E9" s="7" t="inlineStr">
-        <is>
-          <t>08/09/2025</t>
-        </is>
-      </c>
-      <c r="F9" s="7" t="inlineStr">
-        <is>
-          <t>3500442146</t>
-        </is>
-      </c>
-      <c r="G9" s="6" t="inlineStr">
-        <is>
-          <t>CÔNG TY TNHH CHẤN LONG</t>
-        </is>
-      </c>
-      <c r="H9" s="6" t="inlineStr">
-        <is>
-          <t>421 Võ Thị Sáu , Xã Long Điền, Thành Phố Hồ Chí Minh, Việt Nam</t>
-        </is>
-      </c>
-      <c r="I9" s="7" t="inlineStr">
-        <is>
-          <t>3500826826</t>
-        </is>
-      </c>
-      <c r="J9" s="6" t="inlineStr">
-        <is>
-          <t>CÔNG TY TNHH NGUYÊN KHANG</t>
-        </is>
-      </c>
-      <c r="K9" s="13" t="n">
-        <v>1.1416667E7</v>
-      </c>
-      <c r="L9" s="13" t="n">
-        <v>913333.0</v>
-      </c>
-      <c r="M9" s="13" t="n">
-        <v>0.0</v>
-      </c>
-      <c r="N9" s="13"/>
-      <c r="O9" s="13" t="n">
-        <v>1.233E7</v>
-      </c>
-      <c r="P9" s="7" t="inlineStr">
-        <is>
-          <t>VND</t>
-        </is>
-      </c>
-      <c r="Q9" s="7" t="inlineStr">
-        <is>
-          <t>1.0</t>
-        </is>
-      </c>
-      <c r="R9" s="6" t="inlineStr">
-        <is>
-          <t>Hóa đơn mới</t>
-        </is>
-      </c>
-      <c r="S9" s="6" t="inlineStr">
-        <is>
-          <t>Đã cấp mã hóa đơn</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" s="4" t="n">
-        <v>4.0</v>
-      </c>
-      <c r="B10" s="7" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="C10" s="6" t="inlineStr">
-        <is>
-          <t>C25TCL</t>
-        </is>
-      </c>
-      <c r="D10" s="7" t="inlineStr">
-        <is>
-          <t>7300</t>
-        </is>
-      </c>
-      <c r="E10" s="7" t="inlineStr">
-        <is>
-          <t>15/09/2025</t>
-        </is>
-      </c>
-      <c r="F10" s="7" t="inlineStr">
-        <is>
-          <t>3500442146</t>
-        </is>
-      </c>
-      <c r="G10" s="6" t="inlineStr">
-        <is>
-          <t>CÔNG TY TNHH CHẤN LONG</t>
-        </is>
-      </c>
-      <c r="H10" s="6" t="inlineStr">
-        <is>
-          <t>421 Võ Thị Sáu , Xã Long Điền, Thành Phố Hồ Chí Minh, Việt Nam</t>
-        </is>
-      </c>
-      <c r="I10" s="7" t="inlineStr">
-        <is>
-          <t>3500826826</t>
-        </is>
-      </c>
-      <c r="J10" s="6" t="inlineStr">
-        <is>
-          <t>CÔNG TY TNHH NGUYÊN KHANG</t>
-        </is>
-      </c>
-      <c r="K10" s="13" t="n">
-        <v>1.125E7</v>
-      </c>
-      <c r="L10" s="13" t="n">
-        <v>900000.0</v>
-      </c>
-      <c r="M10" s="13" t="n">
-        <v>0.0</v>
-      </c>
-      <c r="N10" s="13"/>
-      <c r="O10" s="13" t="n">
-        <v>1.215E7</v>
-      </c>
-      <c r="P10" s="7" t="inlineStr">
-        <is>
-          <t>VND</t>
-        </is>
-      </c>
-      <c r="Q10" s="7" t="inlineStr">
-        <is>
-          <t>1.0</t>
-        </is>
-      </c>
-      <c r="R10" s="6" t="inlineStr">
-        <is>
-          <t>Hóa đơn mới</t>
-        </is>
-      </c>
-      <c r="S10" s="6" t="inlineStr">
-        <is>
-          <t>Đã cấp mã hóa đơn</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" s="4" t="n">
-        <v>5.0</v>
-      </c>
-      <c r="B11" s="7" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="C11" s="6" t="inlineStr">
-        <is>
-          <t>C25TCL</t>
-        </is>
-      </c>
-      <c r="D11" s="7" t="inlineStr">
-        <is>
-          <t>7721</t>
-        </is>
-      </c>
-      <c r="E11" s="7" t="inlineStr">
-        <is>
-          <t>29/09/2025</t>
-        </is>
-      </c>
-      <c r="F11" s="7" t="inlineStr">
-        <is>
-          <t>3500442146</t>
-        </is>
-      </c>
-      <c r="G11" s="6" t="inlineStr">
-        <is>
-          <t>CÔNG TY TNHH CHẤN LONG</t>
-        </is>
-      </c>
-      <c r="H11" s="6" t="inlineStr">
-        <is>
-          <t>421 Võ Thị Sáu , Xã Long Điền, Thành Phố Hồ Chí Minh, Việt Nam</t>
-        </is>
-      </c>
-      <c r="I11" s="7" t="inlineStr">
-        <is>
-          <t>3500826826</t>
-        </is>
-      </c>
-      <c r="J11" s="6" t="inlineStr">
-        <is>
-          <t>CÔNG TY TNHH NGUYÊN KHANG</t>
-        </is>
-      </c>
-      <c r="K11" s="13" t="n">
-        <v>4.45E7</v>
-      </c>
-      <c r="L11" s="13" t="n">
-        <v>3560000.0</v>
-      </c>
-      <c r="M11" s="13" t="n">
-        <v>0.0</v>
-      </c>
-      <c r="N11" s="13"/>
-      <c r="O11" s="13" t="n">
-        <v>4.806E7</v>
-      </c>
-      <c r="P11" s="7" t="inlineStr">
-        <is>
-          <t>VND</t>
-        </is>
-      </c>
-      <c r="Q11" s="7" t="inlineStr">
-        <is>
-          <t>1.0</t>
-        </is>
-      </c>
-      <c r="R11" s="6" t="inlineStr">
-        <is>
-          <t>Hóa đơn mới</t>
-        </is>
-      </c>
-      <c r="S11" s="6" t="inlineStr">
         <is>
           <t>Đã cấp mã hóa đơn</t>
         </is>

--- a/Hoadon/HDVao/9/HDDienTuDaCapMa.xlsx
+++ b/Hoadon/HDVao/9/HDDienTuDaCapMa.xlsx
@@ -325,56 +325,56 @@
       </c>
       <c r="C7" s="6" t="inlineStr">
         <is>
-          <t>C25TBT</t>
+          <t>C25TMT</t>
         </is>
       </c>
       <c r="D7" s="7" t="inlineStr">
         <is>
-          <t>1726</t>
+          <t>353</t>
         </is>
       </c>
       <c r="E7" s="7" t="inlineStr">
         <is>
-          <t>30/09/2025</t>
+          <t>05/09/2025</t>
         </is>
       </c>
       <c r="F7" s="7" t="inlineStr">
         <is>
-          <t>3501772161</t>
+          <t>0106639639</t>
         </is>
       </c>
       <c r="G7" s="6" t="inlineStr">
         <is>
-          <t>CÔNG TY CỔ PHẦN BÊ TÔNG VÀ XÂY LẮP HODECO</t>
+          <t>CÔNG TY TNHH SẢN XUẤT VÀ ĐẦU TƯ MINH TÙNG</t>
         </is>
       </c>
       <c r="H7" s="6" t="inlineStr">
         <is>
-          <t>Thôn 9 Gò Găng, Xã Long Sơn, Thành phố Hồ Chí Minh, Việt Nam.</t>
+          <t>Tầng 11 tòa nhà Zen Tower, số 12 đường Khuất Duy Tiến, Phường Thanh Xuân, Thành phố Hà Nội, Việt Nam</t>
         </is>
       </c>
       <c r="I7" s="7" t="inlineStr">
         <is>
-          <t>3502267355</t>
+          <t>3500392181</t>
         </is>
       </c>
       <c r="J7" s="6" t="inlineStr">
         <is>
-          <t>CÔNG TY TNHH XÂY DỰNG NGỌC TRÂN</t>
+          <t>CÔNG TY TNHH ĐẠI PHÚ HIỆP</t>
         </is>
       </c>
       <c r="K7" s="13" t="n">
-        <v>4.1188889E7</v>
+        <v>6.5464E7</v>
       </c>
       <c r="L7" s="13" t="n">
-        <v>3295111.0</v>
+        <v>6546400.0</v>
       </c>
       <c r="M7" s="13" t="n">
         <v>0.0</v>
       </c>
       <c r="N7" s="13"/>
       <c r="O7" s="13" t="n">
-        <v>4.4484E7</v>
+        <v>7.20104E7</v>
       </c>
       <c r="P7" s="7" t="inlineStr">
         <is>
@@ -392,6 +392,4454 @@
         </is>
       </c>
       <c r="S7" s="6" t="inlineStr">
+        <is>
+          <t>Đã cấp mã hóa đơn</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="4" t="n">
+        <v>2.0</v>
+      </c>
+      <c r="B8" s="7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C8" s="6" t="inlineStr">
+        <is>
+          <t>C25TMT</t>
+        </is>
+      </c>
+      <c r="D8" s="7" t="inlineStr">
+        <is>
+          <t>354</t>
+        </is>
+      </c>
+      <c r="E8" s="7" t="inlineStr">
+        <is>
+          <t>05/09/2025</t>
+        </is>
+      </c>
+      <c r="F8" s="7" t="inlineStr">
+        <is>
+          <t>0106639639</t>
+        </is>
+      </c>
+      <c r="G8" s="6" t="inlineStr">
+        <is>
+          <t>CÔNG TY TNHH SẢN XUẤT VÀ ĐẦU TƯ MINH TÙNG</t>
+        </is>
+      </c>
+      <c r="H8" s="6" t="inlineStr">
+        <is>
+          <t>Tầng 11 tòa nhà Zen Tower, số 12 đường Khuất Duy Tiến, Phường Thanh Xuân, Thành phố Hà Nội, Việt Nam</t>
+        </is>
+      </c>
+      <c r="I8" s="7" t="inlineStr">
+        <is>
+          <t>3500392181</t>
+        </is>
+      </c>
+      <c r="J8" s="6" t="inlineStr">
+        <is>
+          <t>CÔNG TY TNHH ĐẠI PHÚ HIỆP</t>
+        </is>
+      </c>
+      <c r="K8" s="13" t="n">
+        <v>1000000.0</v>
+      </c>
+      <c r="L8" s="13" t="n">
+        <v>80000.0</v>
+      </c>
+      <c r="M8" s="13" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="N8" s="13"/>
+      <c r="O8" s="13" t="n">
+        <v>1080000.0</v>
+      </c>
+      <c r="P8" s="7" t="inlineStr">
+        <is>
+          <t>VND</t>
+        </is>
+      </c>
+      <c r="Q8" s="7" t="inlineStr">
+        <is>
+          <t>1.0</t>
+        </is>
+      </c>
+      <c r="R8" s="6" t="inlineStr">
+        <is>
+          <t>Hóa đơn mới</t>
+        </is>
+      </c>
+      <c r="S8" s="6" t="inlineStr">
+        <is>
+          <t>Đã cấp mã hóa đơn</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="4" t="n">
+        <v>3.0</v>
+      </c>
+      <c r="B9" s="7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C9" s="6" t="inlineStr">
+        <is>
+          <t>C25THL</t>
+        </is>
+      </c>
+      <c r="D9" s="7" t="inlineStr">
+        <is>
+          <t>2123</t>
+        </is>
+      </c>
+      <c r="E9" s="7" t="inlineStr">
+        <is>
+          <t>23/09/2025</t>
+        </is>
+      </c>
+      <c r="F9" s="7" t="inlineStr">
+        <is>
+          <t>0312738441</t>
+        </is>
+      </c>
+      <c r="G9" s="6" t="inlineStr">
+        <is>
+          <t>Công ty TNHH SX TM DV XD Hiệp Lực</t>
+        </is>
+      </c>
+      <c r="H9" s="6" t="inlineStr">
+        <is>
+          <t>54/31-33 Bạch Đằng 2, Phường Tân Sơn Hòa, TP Hồ Chí Minh</t>
+        </is>
+      </c>
+      <c r="I9" s="7" t="inlineStr">
+        <is>
+          <t>3500392181</t>
+        </is>
+      </c>
+      <c r="J9" s="6" t="inlineStr">
+        <is>
+          <t>CÔNG TY TNHH ĐẠI PHÚ HIỆP</t>
+        </is>
+      </c>
+      <c r="K9" s="13" t="n">
+        <v>3.3179727E7</v>
+      </c>
+      <c r="L9" s="13" t="n">
+        <v>3317973.0</v>
+      </c>
+      <c r="M9" s="13"/>
+      <c r="N9" s="13"/>
+      <c r="O9" s="13" t="n">
+        <v>3.64977E7</v>
+      </c>
+      <c r="P9" s="7" t="inlineStr">
+        <is>
+          <t>VND</t>
+        </is>
+      </c>
+      <c r="Q9" s="7" t="inlineStr">
+        <is>
+          <t>1.0</t>
+        </is>
+      </c>
+      <c r="R9" s="6" t="inlineStr">
+        <is>
+          <t>Hóa đơn mới</t>
+        </is>
+      </c>
+      <c r="S9" s="6" t="inlineStr">
+        <is>
+          <t>Đã cấp mã hóa đơn</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="4" t="n">
+        <v>4.0</v>
+      </c>
+      <c r="B10" s="7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C10" s="6" t="inlineStr">
+        <is>
+          <t>C25THL</t>
+        </is>
+      </c>
+      <c r="D10" s="7" t="inlineStr">
+        <is>
+          <t>2251</t>
+        </is>
+      </c>
+      <c r="E10" s="7" t="inlineStr">
+        <is>
+          <t>30/09/2025</t>
+        </is>
+      </c>
+      <c r="F10" s="7" t="inlineStr">
+        <is>
+          <t>0312738441</t>
+        </is>
+      </c>
+      <c r="G10" s="6" t="inlineStr">
+        <is>
+          <t>Công ty TNHH SX TM DV XD Hiệp Lực</t>
+        </is>
+      </c>
+      <c r="H10" s="6" t="inlineStr">
+        <is>
+          <t>54/31-33 Bạch Đằng 2, Phường Tân Sơn Hòa, TP Hồ Chí Minh</t>
+        </is>
+      </c>
+      <c r="I10" s="7" t="inlineStr">
+        <is>
+          <t>3500392181</t>
+        </is>
+      </c>
+      <c r="J10" s="6" t="inlineStr">
+        <is>
+          <t>CÔNG TY TNHH ĐẠI PHÚ HIỆP</t>
+        </is>
+      </c>
+      <c r="K10" s="13" t="n">
+        <v>4.6505182E7</v>
+      </c>
+      <c r="L10" s="13" t="n">
+        <v>4650518.0</v>
+      </c>
+      <c r="M10" s="13"/>
+      <c r="N10" s="13"/>
+      <c r="O10" s="13" t="n">
+        <v>5.11557E7</v>
+      </c>
+      <c r="P10" s="7" t="inlineStr">
+        <is>
+          <t>VND</t>
+        </is>
+      </c>
+      <c r="Q10" s="7" t="inlineStr">
+        <is>
+          <t>1.0</t>
+        </is>
+      </c>
+      <c r="R10" s="6" t="inlineStr">
+        <is>
+          <t>Hóa đơn mới</t>
+        </is>
+      </c>
+      <c r="S10" s="6" t="inlineStr">
+        <is>
+          <t>Đã cấp mã hóa đơn</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="4" t="n">
+        <v>5.0</v>
+      </c>
+      <c r="B11" s="7" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="C11" s="6" t="inlineStr">
+        <is>
+          <t>C25LGL</t>
+        </is>
+      </c>
+      <c r="D11" s="7" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="E11" s="7" t="inlineStr">
+        <is>
+          <t>25/09/2025</t>
+        </is>
+      </c>
+      <c r="F11" s="7" t="inlineStr">
+        <is>
+          <t>051071000556</t>
+        </is>
+      </c>
+      <c r="G11" s="6" t="inlineStr">
+        <is>
+          <t>HỘ KINH DOANH ĐOÀN VĂN HẢO (GIA LINH)</t>
+        </is>
+      </c>
+      <c r="H11" s="6" t="inlineStr">
+        <is>
+          <t>27/7A đường Phạm Văn Dinh, Phường Rạch Dừa, TP Hồ Chí Minh</t>
+        </is>
+      </c>
+      <c r="I11" s="7" t="inlineStr">
+        <is>
+          <t>3500392181</t>
+        </is>
+      </c>
+      <c r="J11" s="6" t="inlineStr">
+        <is>
+          <t>CÔNG TY TNHH ĐẠI PHÚ HIỆP</t>
+        </is>
+      </c>
+      <c r="K11" s="13"/>
+      <c r="L11" s="13"/>
+      <c r="M11" s="13" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="N11" s="13" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="O11" s="13" t="n">
+        <v>4640000.0</v>
+      </c>
+      <c r="P11" s="7" t="inlineStr">
+        <is>
+          <t>VND</t>
+        </is>
+      </c>
+      <c r="Q11" s="7" t="inlineStr">
+        <is>
+          <t>1.0</t>
+        </is>
+      </c>
+      <c r="R11" s="6" t="inlineStr">
+        <is>
+          <t>Hóa đơn mới</t>
+        </is>
+      </c>
+      <c r="S11" s="6" t="inlineStr">
+        <is>
+          <t>Đã cấp mã hóa đơn</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="4" t="n">
+        <v>6.0</v>
+      </c>
+      <c r="B12" s="7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C12" s="6" t="inlineStr">
+        <is>
+          <t>C25TAA</t>
+        </is>
+      </c>
+      <c r="D12" s="7" t="inlineStr">
+        <is>
+          <t>1303</t>
+        </is>
+      </c>
+      <c r="E12" s="7" t="inlineStr">
+        <is>
+          <t>25/09/2025</t>
+        </is>
+      </c>
+      <c r="F12" s="7" t="inlineStr">
+        <is>
+          <t>3500342374</t>
+        </is>
+      </c>
+      <c r="G12" s="6" t="inlineStr">
+        <is>
+          <t>TRUNG TÂM NƯỚC SẠCH VÀ VỆ SINH MÔI TRƯỜNG NÔNG THÔN</t>
+        </is>
+      </c>
+      <c r="H12" s="6" t="inlineStr">
+        <is>
+          <t>Số 39 đường Hoàng Diệu, Phường Long Hương, Thành phố Hồ Chí Minh</t>
+        </is>
+      </c>
+      <c r="I12" s="7" t="inlineStr">
+        <is>
+          <t>3500392181</t>
+        </is>
+      </c>
+      <c r="J12" s="6" t="inlineStr">
+        <is>
+          <t>CÔNG TY TNHH ĐẠI PHÚ HIỆP</t>
+        </is>
+      </c>
+      <c r="K12" s="13" t="n">
+        <v>2.6337037E7</v>
+      </c>
+      <c r="L12" s="13" t="n">
+        <v>2106963.0</v>
+      </c>
+      <c r="M12" s="13"/>
+      <c r="N12" s="13"/>
+      <c r="O12" s="13" t="n">
+        <v>2.8444E7</v>
+      </c>
+      <c r="P12" s="7" t="inlineStr">
+        <is>
+          <t>VND</t>
+        </is>
+      </c>
+      <c r="Q12" s="7" t="inlineStr">
+        <is>
+          <t>1.0</t>
+        </is>
+      </c>
+      <c r="R12" s="6" t="inlineStr">
+        <is>
+          <t>Hóa đơn mới</t>
+        </is>
+      </c>
+      <c r="S12" s="6" t="inlineStr">
+        <is>
+          <t>Đã cấp mã hóa đơn</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="4" t="n">
+        <v>7.0</v>
+      </c>
+      <c r="B13" s="7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C13" s="6" t="inlineStr">
+        <is>
+          <t>C25TQH</t>
+        </is>
+      </c>
+      <c r="D13" s="7" t="inlineStr">
+        <is>
+          <t>671</t>
+        </is>
+      </c>
+      <c r="E13" s="7" t="inlineStr">
+        <is>
+          <t>30/09/2025</t>
+        </is>
+      </c>
+      <c r="F13" s="7" t="inlineStr">
+        <is>
+          <t>3500522497</t>
+        </is>
+      </c>
+      <c r="G13" s="6" t="inlineStr">
+        <is>
+          <t>CÔNG TY TNHH XÂY LẮP ĐIỆN QUANG HUY</t>
+        </is>
+      </c>
+      <c r="H13" s="6" t="inlineStr">
+        <is>
+          <t>679 Võ Thị Sáu, Phường Bà Rịa, Thành Phố Hồ Chí Minh, Việt Nam</t>
+        </is>
+      </c>
+      <c r="I13" s="7" t="inlineStr">
+        <is>
+          <t>3500392181</t>
+        </is>
+      </c>
+      <c r="J13" s="6" t="inlineStr">
+        <is>
+          <t>CÔNG TY TNHH ĐẠI PHÚ HIỆP</t>
+        </is>
+      </c>
+      <c r="K13" s="13" t="n">
+        <v>1.674E8</v>
+      </c>
+      <c r="L13" s="13" t="n">
+        <v>1.3392E7</v>
+      </c>
+      <c r="M13" s="13" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="N13" s="13"/>
+      <c r="O13" s="13" t="n">
+        <v>1.80792E8</v>
+      </c>
+      <c r="P13" s="7" t="inlineStr">
+        <is>
+          <t>VND</t>
+        </is>
+      </c>
+      <c r="Q13" s="7" t="inlineStr">
+        <is>
+          <t>1.0</t>
+        </is>
+      </c>
+      <c r="R13" s="6" t="inlineStr">
+        <is>
+          <t>Hóa đơn mới</t>
+        </is>
+      </c>
+      <c r="S13" s="6" t="inlineStr">
+        <is>
+          <t>Đã cấp mã hóa đơn</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="4" t="n">
+        <v>8.0</v>
+      </c>
+      <c r="B14" s="7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C14" s="6" t="inlineStr">
+        <is>
+          <t>C25TQH</t>
+        </is>
+      </c>
+      <c r="D14" s="7" t="inlineStr">
+        <is>
+          <t>673</t>
+        </is>
+      </c>
+      <c r="E14" s="7" t="inlineStr">
+        <is>
+          <t>30/09/2025</t>
+        </is>
+      </c>
+      <c r="F14" s="7" t="inlineStr">
+        <is>
+          <t>3500522497</t>
+        </is>
+      </c>
+      <c r="G14" s="6" t="inlineStr">
+        <is>
+          <t>CÔNG TY TNHH XÂY LẮP ĐIỆN QUANG HUY</t>
+        </is>
+      </c>
+      <c r="H14" s="6" t="inlineStr">
+        <is>
+          <t>679 Võ Thị Sáu, Phường Bà Rịa, Thành Phố Hồ Chí Minh, Việt Nam</t>
+        </is>
+      </c>
+      <c r="I14" s="7" t="inlineStr">
+        <is>
+          <t>3500392181</t>
+        </is>
+      </c>
+      <c r="J14" s="6" t="inlineStr">
+        <is>
+          <t>CÔNG TY TNHH ĐẠI PHÚ HIỆP</t>
+        </is>
+      </c>
+      <c r="K14" s="13" t="n">
+        <v>1.2E7</v>
+      </c>
+      <c r="L14" s="13" t="n">
+        <v>960000.0</v>
+      </c>
+      <c r="M14" s="13" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="N14" s="13"/>
+      <c r="O14" s="13" t="n">
+        <v>1.296E7</v>
+      </c>
+      <c r="P14" s="7" t="inlineStr">
+        <is>
+          <t>VND</t>
+        </is>
+      </c>
+      <c r="Q14" s="7" t="inlineStr">
+        <is>
+          <t>1.0</t>
+        </is>
+      </c>
+      <c r="R14" s="6" t="inlineStr">
+        <is>
+          <t>Hóa đơn mới</t>
+        </is>
+      </c>
+      <c r="S14" s="6" t="inlineStr">
+        <is>
+          <t>Đã cấp mã hóa đơn</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="4" t="n">
+        <v>9.0</v>
+      </c>
+      <c r="B15" s="7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C15" s="6" t="inlineStr">
+        <is>
+          <t>C25TYY</t>
+        </is>
+      </c>
+      <c r="D15" s="7" t="inlineStr">
+        <is>
+          <t>131</t>
+        </is>
+      </c>
+      <c r="E15" s="7" t="inlineStr">
+        <is>
+          <t>30/09/2025</t>
+        </is>
+      </c>
+      <c r="F15" s="7" t="inlineStr">
+        <is>
+          <t>3500635395</t>
+        </is>
+      </c>
+      <c r="G15" s="6" t="inlineStr">
+        <is>
+          <t>CÔNG TY CỔ PHẦN GIÁM ĐỊNH HOÀNG GIA</t>
+        </is>
+      </c>
+      <c r="H15" s="6" t="inlineStr">
+        <is>
+          <t>Số 109 Nguyễn Thị Minh Khai, Phường Tam Thắng, Thành phố Hồ Chí Minh, Việt Nam</t>
+        </is>
+      </c>
+      <c r="I15" s="7" t="inlineStr">
+        <is>
+          <t>3500392181</t>
+        </is>
+      </c>
+      <c r="J15" s="6" t="inlineStr">
+        <is>
+          <t>CÔNG TY TNHH ĐẠI PHÚ HIỆP</t>
+        </is>
+      </c>
+      <c r="K15" s="13" t="n">
+        <v>1800000.0</v>
+      </c>
+      <c r="L15" s="13" t="n">
+        <v>144000.0</v>
+      </c>
+      <c r="M15" s="13" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="N15" s="13"/>
+      <c r="O15" s="13" t="n">
+        <v>1944000.0</v>
+      </c>
+      <c r="P15" s="7" t="inlineStr">
+        <is>
+          <t>VND</t>
+        </is>
+      </c>
+      <c r="Q15" s="7" t="inlineStr">
+        <is>
+          <t>1.0</t>
+        </is>
+      </c>
+      <c r="R15" s="6" t="inlineStr">
+        <is>
+          <t>Hóa đơn mới</t>
+        </is>
+      </c>
+      <c r="S15" s="6" t="inlineStr">
+        <is>
+          <t>Đã cấp mã hóa đơn</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="4" t="n">
+        <v>10.0</v>
+      </c>
+      <c r="B16" s="7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C16" s="6" t="inlineStr">
+        <is>
+          <t>C25TSV</t>
+        </is>
+      </c>
+      <c r="D16" s="7" t="inlineStr">
+        <is>
+          <t>154</t>
+        </is>
+      </c>
+      <c r="E16" s="7" t="inlineStr">
+        <is>
+          <t>19/09/2025</t>
+        </is>
+      </c>
+      <c r="F16" s="7" t="inlineStr">
+        <is>
+          <t>3500898348</t>
+        </is>
+      </c>
+      <c r="G16" s="6" t="inlineStr">
+        <is>
+          <t>CÔNG TY TNHH DỊCH VỤ THUẾ SAO VIỆT</t>
+        </is>
+      </c>
+      <c r="H16" s="6" t="inlineStr">
+        <is>
+          <t>Số 640 Trương Công Định, Phường Tam Thắng, TP. Hồ Chí Minh, Việt Nam</t>
+        </is>
+      </c>
+      <c r="I16" s="7" t="inlineStr">
+        <is>
+          <t>3500392181</t>
+        </is>
+      </c>
+      <c r="J16" s="6" t="inlineStr">
+        <is>
+          <t>CÔNG TY TNHH ĐẠI PHÚ HIỆP</t>
+        </is>
+      </c>
+      <c r="K16" s="13" t="n">
+        <v>1.8E7</v>
+      </c>
+      <c r="L16" s="13" t="n">
+        <v>1440000.0</v>
+      </c>
+      <c r="M16" s="13" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="N16" s="13"/>
+      <c r="O16" s="13" t="n">
+        <v>1.944E7</v>
+      </c>
+      <c r="P16" s="7" t="inlineStr">
+        <is>
+          <t>VND</t>
+        </is>
+      </c>
+      <c r="Q16" s="7" t="inlineStr">
+        <is>
+          <t>1.0</t>
+        </is>
+      </c>
+      <c r="R16" s="6" t="inlineStr">
+        <is>
+          <t>Hóa đơn mới</t>
+        </is>
+      </c>
+      <c r="S16" s="6" t="inlineStr">
+        <is>
+          <t>Đã cấp mã hóa đơn</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="4" t="n">
+        <v>11.0</v>
+      </c>
+      <c r="B17" s="7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C17" s="6" t="inlineStr">
+        <is>
+          <t>C25TXD</t>
+        </is>
+      </c>
+      <c r="D17" s="7" t="inlineStr">
+        <is>
+          <t>734</t>
+        </is>
+      </c>
+      <c r="E17" s="7" t="inlineStr">
+        <is>
+          <t>20/09/2025</t>
+        </is>
+      </c>
+      <c r="F17" s="7" t="inlineStr">
+        <is>
+          <t>3500979808</t>
+        </is>
+      </c>
+      <c r="G17" s="6" t="inlineStr">
+        <is>
+          <t>CÔNG TY CỔ PHẦN TƯ VẤN VÀ XÂY DỰNG MIỀN NAM</t>
+        </is>
+      </c>
+      <c r="H17" s="6" t="inlineStr">
+        <is>
+          <t>E7-8, đường Trương Định, Khu đô thị mới Phú Mỹ, Phường Phú Mỹ, Thành phố Hồ Chí Minh, Việt Nam</t>
+        </is>
+      </c>
+      <c r="I17" s="7" t="inlineStr">
+        <is>
+          <t>3500392181</t>
+        </is>
+      </c>
+      <c r="J17" s="6" t="inlineStr">
+        <is>
+          <t>CÔNG TY TNHH ĐẠI PHÚ HIỆP</t>
+        </is>
+      </c>
+      <c r="K17" s="13" t="n">
+        <v>6464000.0</v>
+      </c>
+      <c r="L17" s="13" t="n">
+        <v>517120.0</v>
+      </c>
+      <c r="M17" s="13"/>
+      <c r="N17" s="13"/>
+      <c r="O17" s="13" t="n">
+        <v>6981120.0</v>
+      </c>
+      <c r="P17" s="7" t="inlineStr">
+        <is>
+          <t>VND</t>
+        </is>
+      </c>
+      <c r="Q17" s="7" t="inlineStr">
+        <is>
+          <t>1.0</t>
+        </is>
+      </c>
+      <c r="R17" s="6" t="inlineStr">
+        <is>
+          <t>Hóa đơn mới</t>
+        </is>
+      </c>
+      <c r="S17" s="6" t="inlineStr">
+        <is>
+          <t>Đã cấp mã hóa đơn</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="4" t="n">
+        <v>12.0</v>
+      </c>
+      <c r="B18" s="7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C18" s="6" t="inlineStr">
+        <is>
+          <t>C25TXD</t>
+        </is>
+      </c>
+      <c r="D18" s="7" t="inlineStr">
+        <is>
+          <t>750</t>
+        </is>
+      </c>
+      <c r="E18" s="7" t="inlineStr">
+        <is>
+          <t>29/09/2025</t>
+        </is>
+      </c>
+      <c r="F18" s="7" t="inlineStr">
+        <is>
+          <t>3500979808</t>
+        </is>
+      </c>
+      <c r="G18" s="6" t="inlineStr">
+        <is>
+          <t>CÔNG TY CỔ PHẦN TƯ VẤN VÀ XÂY DỰNG MIỀN NAM</t>
+        </is>
+      </c>
+      <c r="H18" s="6" t="inlineStr">
+        <is>
+          <t>E7-8, đường Trương Định, Khu đô thị mới Phú Mỹ, Phường Phú Mỹ, Thành phố Hồ Chí Minh, Việt Nam</t>
+        </is>
+      </c>
+      <c r="I18" s="7" t="inlineStr">
+        <is>
+          <t>3500392181</t>
+        </is>
+      </c>
+      <c r="J18" s="6" t="inlineStr">
+        <is>
+          <t>CÔNG TY TNHH ĐẠI PHÚ HIỆP</t>
+        </is>
+      </c>
+      <c r="K18" s="13" t="n">
+        <v>650000.0</v>
+      </c>
+      <c r="L18" s="13" t="n">
+        <v>65000.0</v>
+      </c>
+      <c r="M18" s="13"/>
+      <c r="N18" s="13"/>
+      <c r="O18" s="13" t="n">
+        <v>715000.0</v>
+      </c>
+      <c r="P18" s="7" t="inlineStr">
+        <is>
+          <t>VND</t>
+        </is>
+      </c>
+      <c r="Q18" s="7" t="inlineStr">
+        <is>
+          <t>1.0</t>
+        </is>
+      </c>
+      <c r="R18" s="6" t="inlineStr">
+        <is>
+          <t>Hóa đơn mới</t>
+        </is>
+      </c>
+      <c r="S18" s="6" t="inlineStr">
+        <is>
+          <t>Đã cấp mã hóa đơn</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="4" t="n">
+        <v>13.0</v>
+      </c>
+      <c r="B19" s="7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C19" s="6" t="inlineStr">
+        <is>
+          <t>C25TXD</t>
+        </is>
+      </c>
+      <c r="D19" s="7" t="inlineStr">
+        <is>
+          <t>751</t>
+        </is>
+      </c>
+      <c r="E19" s="7" t="inlineStr">
+        <is>
+          <t>29/09/2025</t>
+        </is>
+      </c>
+      <c r="F19" s="7" t="inlineStr">
+        <is>
+          <t>3500979808</t>
+        </is>
+      </c>
+      <c r="G19" s="6" t="inlineStr">
+        <is>
+          <t>CÔNG TY CỔ PHẦN TƯ VẤN VÀ XÂY DỰNG MIỀN NAM</t>
+        </is>
+      </c>
+      <c r="H19" s="6" t="inlineStr">
+        <is>
+          <t>E7-8, đường Trương Định, Khu đô thị mới Phú Mỹ, Phường Phú Mỹ, Thành phố Hồ Chí Minh, Việt Nam</t>
+        </is>
+      </c>
+      <c r="I19" s="7" t="inlineStr">
+        <is>
+          <t>3500392181</t>
+        </is>
+      </c>
+      <c r="J19" s="6" t="inlineStr">
+        <is>
+          <t>CÔNG TY TNHH ĐẠI PHÚ HIỆP</t>
+        </is>
+      </c>
+      <c r="K19" s="13" t="n">
+        <v>1.8666E7</v>
+      </c>
+      <c r="L19" s="13" t="n">
+        <v>1493280.0</v>
+      </c>
+      <c r="M19" s="13"/>
+      <c r="N19" s="13"/>
+      <c r="O19" s="13" t="n">
+        <v>2.015928E7</v>
+      </c>
+      <c r="P19" s="7" t="inlineStr">
+        <is>
+          <t>VND</t>
+        </is>
+      </c>
+      <c r="Q19" s="7" t="inlineStr">
+        <is>
+          <t>1.0</t>
+        </is>
+      </c>
+      <c r="R19" s="6" t="inlineStr">
+        <is>
+          <t>Hóa đơn mới</t>
+        </is>
+      </c>
+      <c r="S19" s="6" t="inlineStr">
+        <is>
+          <t>Đã cấp mã hóa đơn</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="4" t="n">
+        <v>14.0</v>
+      </c>
+      <c r="B20" s="7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C20" s="6" t="inlineStr">
+        <is>
+          <t>C25TVN</t>
+        </is>
+      </c>
+      <c r="D20" s="7" t="inlineStr">
+        <is>
+          <t>591</t>
+        </is>
+      </c>
+      <c r="E20" s="7" t="inlineStr">
+        <is>
+          <t>16/09/2025</t>
+        </is>
+      </c>
+      <c r="F20" s="7" t="inlineStr">
+        <is>
+          <t>3501371762</t>
+        </is>
+      </c>
+      <c r="G20" s="6" t="inlineStr">
+        <is>
+          <t>CÔNG TY CỔ PHẦN SẢN XUẤT - THƯƠNG MẠI VÀ XÂY DỰNG VIỆT HÀN</t>
+        </is>
+      </c>
+      <c r="H20" s="6" t="inlineStr">
+        <is>
+          <t>Đường số 3, Khu Công Nghiệp Phú Mỹ I, Phường Phú Mỹ, Thành Phố Hồ Chí Minh, Việt Nam</t>
+        </is>
+      </c>
+      <c r="I20" s="7" t="inlineStr">
+        <is>
+          <t>3500392181</t>
+        </is>
+      </c>
+      <c r="J20" s="6" t="inlineStr">
+        <is>
+          <t>CÔNG TY TNHH ĐẠI PHÚ HIỆP</t>
+        </is>
+      </c>
+      <c r="K20" s="13" t="n">
+        <v>4036111.0</v>
+      </c>
+      <c r="L20" s="13" t="n">
+        <v>322889.0</v>
+      </c>
+      <c r="M20" s="13" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="N20" s="13"/>
+      <c r="O20" s="13" t="n">
+        <v>4359000.0</v>
+      </c>
+      <c r="P20" s="7" t="inlineStr">
+        <is>
+          <t>VND</t>
+        </is>
+      </c>
+      <c r="Q20" s="7" t="inlineStr">
+        <is>
+          <t>1.0</t>
+        </is>
+      </c>
+      <c r="R20" s="6" t="inlineStr">
+        <is>
+          <t>Hóa đơn mới</t>
+        </is>
+      </c>
+      <c r="S20" s="6" t="inlineStr">
+        <is>
+          <t>Đã cấp mã hóa đơn</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="4" t="n">
+        <v>15.0</v>
+      </c>
+      <c r="B21" s="7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C21" s="6" t="inlineStr">
+        <is>
+          <t>C25TYY</t>
+        </is>
+      </c>
+      <c r="D21" s="7" t="inlineStr">
+        <is>
+          <t>640</t>
+        </is>
+      </c>
+      <c r="E21" s="7" t="inlineStr">
+        <is>
+          <t>22/09/2025</t>
+        </is>
+      </c>
+      <c r="F21" s="7" t="inlineStr">
+        <is>
+          <t>3501495711-001</t>
+        </is>
+      </c>
+      <c r="G21" s="6" t="inlineStr">
+        <is>
+          <t>CÔNG TY TRÁCH NHIỆM HỮU HẠN LÊ CHÍNH-CHI NHÁNH KHAI THÁC MỎ ĐỒI ĐẤT ĐỎ</t>
+        </is>
+      </c>
+      <c r="H21" s="6" t="inlineStr">
+        <is>
+          <t>Tổ 65, ấp Trung Thành, xã Bình Giã, Thành Phố Hồ Chí Minh</t>
+        </is>
+      </c>
+      <c r="I21" s="7" t="inlineStr">
+        <is>
+          <t>3500392181</t>
+        </is>
+      </c>
+      <c r="J21" s="6" t="inlineStr">
+        <is>
+          <t>CÔNG TY TNHH ĐẠI PHÚ HIỆP</t>
+        </is>
+      </c>
+      <c r="K21" s="13" t="n">
+        <v>1.49484764E8</v>
+      </c>
+      <c r="L21" s="13" t="n">
+        <v>1.4948476E7</v>
+      </c>
+      <c r="M21" s="13" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="N21" s="13"/>
+      <c r="O21" s="13" t="n">
+        <v>1.6443324E8</v>
+      </c>
+      <c r="P21" s="7" t="inlineStr">
+        <is>
+          <t>VND</t>
+        </is>
+      </c>
+      <c r="Q21" s="7" t="inlineStr">
+        <is>
+          <t>1.0</t>
+        </is>
+      </c>
+      <c r="R21" s="6" t="inlineStr">
+        <is>
+          <t>Hóa đơn mới</t>
+        </is>
+      </c>
+      <c r="S21" s="6" t="inlineStr">
+        <is>
+          <t>Đã cấp mã hóa đơn</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="4" t="n">
+        <v>16.0</v>
+      </c>
+      <c r="B22" s="7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C22" s="6" t="inlineStr">
+        <is>
+          <t>C25TVT</t>
+        </is>
+      </c>
+      <c r="D22" s="7" t="inlineStr">
+        <is>
+          <t>456</t>
+        </is>
+      </c>
+      <c r="E22" s="7" t="inlineStr">
+        <is>
+          <t>29/09/2025</t>
+        </is>
+      </c>
+      <c r="F22" s="7" t="inlineStr">
+        <is>
+          <t>3501617328</t>
+        </is>
+      </c>
+      <c r="G22" s="6" t="inlineStr">
+        <is>
+          <t>DOANH NGHIỆP TƯ NHÂN VÕ THỊNH</t>
+        </is>
+      </c>
+      <c r="H22" s="6" t="inlineStr">
+        <is>
+          <t>25K4 Nguyễn Thái Học, Trung Tâm Thương Mại, Phường Tam Thắng, Thành Phố Hồ Chí Minh, Việt Nam</t>
+        </is>
+      </c>
+      <c r="I22" s="7" t="inlineStr">
+        <is>
+          <t>3500392181</t>
+        </is>
+      </c>
+      <c r="J22" s="6" t="inlineStr">
+        <is>
+          <t>CÔNG TY TNHH ĐẠI PHÚ HIỆP</t>
+        </is>
+      </c>
+      <c r="K22" s="13" t="n">
+        <v>6200000.0</v>
+      </c>
+      <c r="L22" s="13" t="n">
+        <v>496000.0</v>
+      </c>
+      <c r="M22" s="13"/>
+      <c r="N22" s="13"/>
+      <c r="O22" s="13" t="n">
+        <v>6696000.0</v>
+      </c>
+      <c r="P22" s="7" t="inlineStr">
+        <is>
+          <t>VND</t>
+        </is>
+      </c>
+      <c r="Q22" s="7" t="inlineStr">
+        <is>
+          <t>1.0</t>
+        </is>
+      </c>
+      <c r="R22" s="6" t="inlineStr">
+        <is>
+          <t>Hóa đơn mới</t>
+        </is>
+      </c>
+      <c r="S22" s="6" t="inlineStr">
+        <is>
+          <t>Đã cấp mã hóa đơn</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="4" t="n">
+        <v>17.0</v>
+      </c>
+      <c r="B23" s="7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C23" s="6" t="inlineStr">
+        <is>
+          <t>C25TTK</t>
+        </is>
+      </c>
+      <c r="D23" s="7" t="inlineStr">
+        <is>
+          <t>1084</t>
+        </is>
+      </c>
+      <c r="E23" s="7" t="inlineStr">
+        <is>
+          <t>18/09/2025</t>
+        </is>
+      </c>
+      <c r="F23" s="7" t="inlineStr">
+        <is>
+          <t>3501815577</t>
+        </is>
+      </c>
+      <c r="G23" s="6" t="inlineStr">
+        <is>
+          <t>CÔNG TY TRÁCH NHIỆM HỮU HẠN KHẮC THUẬT</t>
+        </is>
+      </c>
+      <c r="H23" s="6" t="inlineStr">
+        <is>
+          <t>Quốc lộ 51, Khu Phố Hải Sơn, Phường Tân Phước, Thành Phố Hồ Chí Minh, Việt Nam</t>
+        </is>
+      </c>
+      <c r="I23" s="7" t="inlineStr">
+        <is>
+          <t>3500392181</t>
+        </is>
+      </c>
+      <c r="J23" s="6" t="inlineStr">
+        <is>
+          <t>CÔNG TY TNHH ĐẠI PHÚ HIỆP</t>
+        </is>
+      </c>
+      <c r="K23" s="13" t="n">
+        <v>600000.0</v>
+      </c>
+      <c r="L23" s="13" t="n">
+        <v>48000.0</v>
+      </c>
+      <c r="M23" s="13" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="N23" s="13"/>
+      <c r="O23" s="13" t="n">
+        <v>648000.0</v>
+      </c>
+      <c r="P23" s="7" t="inlineStr">
+        <is>
+          <t>VND</t>
+        </is>
+      </c>
+      <c r="Q23" s="7" t="inlineStr">
+        <is>
+          <t>1.0</t>
+        </is>
+      </c>
+      <c r="R23" s="6" t="inlineStr">
+        <is>
+          <t>Hóa đơn mới</t>
+        </is>
+      </c>
+      <c r="S23" s="6" t="inlineStr">
+        <is>
+          <t>Đã cấp mã hóa đơn</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="4" t="n">
+        <v>18.0</v>
+      </c>
+      <c r="B24" s="7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C24" s="6" t="inlineStr">
+        <is>
+          <t>C25TDT</t>
+        </is>
+      </c>
+      <c r="D24" s="7" t="inlineStr">
+        <is>
+          <t>462</t>
+        </is>
+      </c>
+      <c r="E24" s="7" t="inlineStr">
+        <is>
+          <t>12/09/2025</t>
+        </is>
+      </c>
+      <c r="F24" s="7" t="inlineStr">
+        <is>
+          <t>3502337796</t>
+        </is>
+      </c>
+      <c r="G24" s="6" t="inlineStr">
+        <is>
+          <t>CÔNG TY TNHH THƯƠNG MẠI XÂY DỰNG CÔNG TRÌNH ĐỒNG TÂM</t>
+        </is>
+      </c>
+      <c r="H24" s="6" t="inlineStr">
+        <is>
+          <t>Tổ 9, khu phố Hải Dinh, Phường Long Hương, Thành phố Hồ Chí Minh, Việt Nam</t>
+        </is>
+      </c>
+      <c r="I24" s="7" t="inlineStr">
+        <is>
+          <t>3500392181</t>
+        </is>
+      </c>
+      <c r="J24" s="6" t="inlineStr">
+        <is>
+          <t>CÔNG TY TNHH ĐẠI PHÚ HIỆP</t>
+        </is>
+      </c>
+      <c r="K24" s="13" t="n">
+        <v>2105000.0</v>
+      </c>
+      <c r="L24" s="13" t="n">
+        <v>168400.0</v>
+      </c>
+      <c r="M24" s="13" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="N24" s="13"/>
+      <c r="O24" s="13" t="n">
+        <v>2273400.0</v>
+      </c>
+      <c r="P24" s="7" t="inlineStr">
+        <is>
+          <t>VND</t>
+        </is>
+      </c>
+      <c r="Q24" s="7" t="inlineStr">
+        <is>
+          <t>1.0</t>
+        </is>
+      </c>
+      <c r="R24" s="6" t="inlineStr">
+        <is>
+          <t>Hóa đơn mới</t>
+        </is>
+      </c>
+      <c r="S24" s="6" t="inlineStr">
+        <is>
+          <t>Đã cấp mã hóa đơn</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="4" t="n">
+        <v>19.0</v>
+      </c>
+      <c r="B25" s="7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C25" s="6" t="inlineStr">
+        <is>
+          <t>C25TDT</t>
+        </is>
+      </c>
+      <c r="D25" s="7" t="inlineStr">
+        <is>
+          <t>463</t>
+        </is>
+      </c>
+      <c r="E25" s="7" t="inlineStr">
+        <is>
+          <t>12/09/2025</t>
+        </is>
+      </c>
+      <c r="F25" s="7" t="inlineStr">
+        <is>
+          <t>3502337796</t>
+        </is>
+      </c>
+      <c r="G25" s="6" t="inlineStr">
+        <is>
+          <t>CÔNG TY TNHH THƯƠNG MẠI XÂY DỰNG CÔNG TRÌNH ĐỒNG TÂM</t>
+        </is>
+      </c>
+      <c r="H25" s="6" t="inlineStr">
+        <is>
+          <t>Tổ 9, khu phố Hải Dinh, Phường Long Hương, Thành phố Hồ Chí Minh, Việt Nam</t>
+        </is>
+      </c>
+      <c r="I25" s="7" t="inlineStr">
+        <is>
+          <t>3500392181</t>
+        </is>
+      </c>
+      <c r="J25" s="6" t="inlineStr">
+        <is>
+          <t>CÔNG TY TNHH ĐẠI PHÚ HIỆP</t>
+        </is>
+      </c>
+      <c r="K25" s="13" t="n">
+        <v>900000.0</v>
+      </c>
+      <c r="L25" s="13" t="n">
+        <v>90000.0</v>
+      </c>
+      <c r="M25" s="13" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="N25" s="13"/>
+      <c r="O25" s="13" t="n">
+        <v>990000.0</v>
+      </c>
+      <c r="P25" s="7" t="inlineStr">
+        <is>
+          <t>VND</t>
+        </is>
+      </c>
+      <c r="Q25" s="7" t="inlineStr">
+        <is>
+          <t>1.0</t>
+        </is>
+      </c>
+      <c r="R25" s="6" t="inlineStr">
+        <is>
+          <t>Hóa đơn mới</t>
+        </is>
+      </c>
+      <c r="S25" s="6" t="inlineStr">
+        <is>
+          <t>Đã cấp mã hóa đơn</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="4" t="n">
+        <v>20.0</v>
+      </c>
+      <c r="B26" s="7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C26" s="6" t="inlineStr">
+        <is>
+          <t>C25TDP</t>
+        </is>
+      </c>
+      <c r="D26" s="7" t="inlineStr">
+        <is>
+          <t>393</t>
+        </is>
+      </c>
+      <c r="E26" s="7" t="inlineStr">
+        <is>
+          <t>03/09/2025</t>
+        </is>
+      </c>
+      <c r="F26" s="7" t="inlineStr">
+        <is>
+          <t>3502392243</t>
+        </is>
+      </c>
+      <c r="G26" s="6" t="inlineStr">
+        <is>
+          <t>CÔNG TY CỔ PHẦN BÊ TÔNG ĐÔNG PHONG</t>
+        </is>
+      </c>
+      <c r="H26" s="6" t="inlineStr">
+        <is>
+          <t>Đường Hoàng Sa, khu phố Láng Cát, Phường Tân Hải, Thành phố Hồ Chí Minh, Việt Nam</t>
+        </is>
+      </c>
+      <c r="I26" s="7" t="inlineStr">
+        <is>
+          <t>3500392181</t>
+        </is>
+      </c>
+      <c r="J26" s="6" t="inlineStr">
+        <is>
+          <t>CÔNG TY TNHH ĐẠI PHÚ HIỆP</t>
+        </is>
+      </c>
+      <c r="K26" s="13" t="n">
+        <v>9.1666667E7</v>
+      </c>
+      <c r="L26" s="13" t="n">
+        <v>7333333.0</v>
+      </c>
+      <c r="M26" s="13" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="N26" s="13"/>
+      <c r="O26" s="13" t="n">
+        <v>9.9E7</v>
+      </c>
+      <c r="P26" s="7" t="inlineStr">
+        <is>
+          <t>VND</t>
+        </is>
+      </c>
+      <c r="Q26" s="7" t="inlineStr">
+        <is>
+          <t>1.0</t>
+        </is>
+      </c>
+      <c r="R26" s="6" t="inlineStr">
+        <is>
+          <t>Hóa đơn mới</t>
+        </is>
+      </c>
+      <c r="S26" s="6" t="inlineStr">
+        <is>
+          <t>Đã cấp mã hóa đơn</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="4" t="n">
+        <v>21.0</v>
+      </c>
+      <c r="B27" s="7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C27" s="6" t="inlineStr">
+        <is>
+          <t>C25TDP</t>
+        </is>
+      </c>
+      <c r="D27" s="7" t="inlineStr">
+        <is>
+          <t>395</t>
+        </is>
+      </c>
+      <c r="E27" s="7" t="inlineStr">
+        <is>
+          <t>03/09/2025</t>
+        </is>
+      </c>
+      <c r="F27" s="7" t="inlineStr">
+        <is>
+          <t>3502392243</t>
+        </is>
+      </c>
+      <c r="G27" s="6" t="inlineStr">
+        <is>
+          <t>CÔNG TY CỔ PHẦN BÊ TÔNG ĐÔNG PHONG</t>
+        </is>
+      </c>
+      <c r="H27" s="6" t="inlineStr">
+        <is>
+          <t>Đường Hoàng Sa, khu phố Láng Cát, Phường Tân Hải, Thành phố Hồ Chí Minh, Việt Nam</t>
+        </is>
+      </c>
+      <c r="I27" s="7" t="inlineStr">
+        <is>
+          <t>3500392181</t>
+        </is>
+      </c>
+      <c r="J27" s="6" t="inlineStr">
+        <is>
+          <t>CÔNG TY TNHH ĐẠI PHÚ HIỆP</t>
+        </is>
+      </c>
+      <c r="K27" s="13" t="n">
+        <v>3.6272731E7</v>
+      </c>
+      <c r="L27" s="13" t="n">
+        <v>2901818.0</v>
+      </c>
+      <c r="M27" s="13" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="N27" s="13"/>
+      <c r="O27" s="13" t="n">
+        <v>3.9174549E7</v>
+      </c>
+      <c r="P27" s="7" t="inlineStr">
+        <is>
+          <t>VND</t>
+        </is>
+      </c>
+      <c r="Q27" s="7" t="inlineStr">
+        <is>
+          <t>1.0</t>
+        </is>
+      </c>
+      <c r="R27" s="6" t="inlineStr">
+        <is>
+          <t>Hóa đơn mới</t>
+        </is>
+      </c>
+      <c r="S27" s="6" t="inlineStr">
+        <is>
+          <t>Đã cấp mã hóa đơn</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="4" t="n">
+        <v>22.0</v>
+      </c>
+      <c r="B28" s="7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C28" s="6" t="inlineStr">
+        <is>
+          <t>C25TYY</t>
+        </is>
+      </c>
+      <c r="D28" s="7" t="inlineStr">
+        <is>
+          <t>156</t>
+        </is>
+      </c>
+      <c r="E28" s="7" t="inlineStr">
+        <is>
+          <t>27/09/2025</t>
+        </is>
+      </c>
+      <c r="F28" s="7" t="inlineStr">
+        <is>
+          <t>3502424047</t>
+        </is>
+      </c>
+      <c r="G28" s="6" t="inlineStr">
+        <is>
+          <t>CÔNG TY TNHH THƯƠNG MẠI VẬT LIỆU XÂY DỰNG QUANG CƯỜNG</t>
+        </is>
+      </c>
+      <c r="H28" s="6" t="inlineStr">
+        <is>
+          <t>313, Tổ 13, Thôn Đức Mỹ, Xã Ngãi Giao, Thành phố Hồ Chí Minh, Việt Nam</t>
+        </is>
+      </c>
+      <c r="I28" s="7" t="inlineStr">
+        <is>
+          <t>3500392181</t>
+        </is>
+      </c>
+      <c r="J28" s="6" t="inlineStr">
+        <is>
+          <t>CÔNG TY TNHH ĐẠI PHÚ HIỆP</t>
+        </is>
+      </c>
+      <c r="K28" s="13" t="n">
+        <v>6.204605E7</v>
+      </c>
+      <c r="L28" s="13" t="n">
+        <v>4963684.0</v>
+      </c>
+      <c r="M28" s="13" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="N28" s="13"/>
+      <c r="O28" s="13" t="n">
+        <v>6.7009734E7</v>
+      </c>
+      <c r="P28" s="7" t="inlineStr">
+        <is>
+          <t>VND</t>
+        </is>
+      </c>
+      <c r="Q28" s="7" t="inlineStr">
+        <is>
+          <t>1.0</t>
+        </is>
+      </c>
+      <c r="R28" s="6" t="inlineStr">
+        <is>
+          <t>Hóa đơn mới</t>
+        </is>
+      </c>
+      <c r="S28" s="6" t="inlineStr">
+        <is>
+          <t>Đã cấp mã hóa đơn</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="4" t="n">
+        <v>23.0</v>
+      </c>
+      <c r="B29" s="7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C29" s="6" t="inlineStr">
+        <is>
+          <t>C25TYY</t>
+        </is>
+      </c>
+      <c r="D29" s="7" t="inlineStr">
+        <is>
+          <t>161</t>
+        </is>
+      </c>
+      <c r="E29" s="7" t="inlineStr">
+        <is>
+          <t>29/09/2025</t>
+        </is>
+      </c>
+      <c r="F29" s="7" t="inlineStr">
+        <is>
+          <t>3502424047</t>
+        </is>
+      </c>
+      <c r="G29" s="6" t="inlineStr">
+        <is>
+          <t>CÔNG TY TNHH THƯƠNG MẠI VẬT LIỆU XÂY DỰNG QUANG CƯỜNG</t>
+        </is>
+      </c>
+      <c r="H29" s="6" t="inlineStr">
+        <is>
+          <t>313, Tổ 13, Thôn Đức Mỹ, Xã Ngãi Giao, Thành phố Hồ Chí Minh, Việt Nam</t>
+        </is>
+      </c>
+      <c r="I29" s="7" t="inlineStr">
+        <is>
+          <t>3500392181</t>
+        </is>
+      </c>
+      <c r="J29" s="6" t="inlineStr">
+        <is>
+          <t>CÔNG TY TNHH ĐẠI PHÚ HIỆP</t>
+        </is>
+      </c>
+      <c r="K29" s="13" t="n">
+        <v>6981818.0</v>
+      </c>
+      <c r="L29" s="13" t="n">
+        <v>698182.0</v>
+      </c>
+      <c r="M29" s="13" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="N29" s="13"/>
+      <c r="O29" s="13" t="n">
+        <v>7680000.0</v>
+      </c>
+      <c r="P29" s="7" t="inlineStr">
+        <is>
+          <t>VND</t>
+        </is>
+      </c>
+      <c r="Q29" s="7" t="inlineStr">
+        <is>
+          <t>1.0</t>
+        </is>
+      </c>
+      <c r="R29" s="6" t="inlineStr">
+        <is>
+          <t>Hóa đơn mới</t>
+        </is>
+      </c>
+      <c r="S29" s="6" t="inlineStr">
+        <is>
+          <t>Đã cấp mã hóa đơn</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="4" t="n">
+        <v>24.0</v>
+      </c>
+      <c r="B30" s="7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C30" s="6" t="inlineStr">
+        <is>
+          <t>C25THM</t>
+        </is>
+      </c>
+      <c r="D30" s="7" t="inlineStr">
+        <is>
+          <t>143</t>
+        </is>
+      </c>
+      <c r="E30" s="7" t="inlineStr">
+        <is>
+          <t>29/09/2025</t>
+        </is>
+      </c>
+      <c r="F30" s="7" t="inlineStr">
+        <is>
+          <t>3502429905</t>
+        </is>
+      </c>
+      <c r="G30" s="6" t="inlineStr">
+        <is>
+          <t>CÔNG TY TNHH DỊCH VỤ Ô TÔ HẢI MINH</t>
+        </is>
+      </c>
+      <c r="H30" s="6" t="inlineStr">
+        <is>
+          <t>Số 7C đường Lê Hồng Phong, Phường Tam Thắng, Thành phố Hồ Chí Minh, Việt Nam.</t>
+        </is>
+      </c>
+      <c r="I30" s="7" t="inlineStr">
+        <is>
+          <t>3500392181</t>
+        </is>
+      </c>
+      <c r="J30" s="6" t="inlineStr">
+        <is>
+          <t>CÔNG TY TNHH ĐẠI PHÚ HIỆP</t>
+        </is>
+      </c>
+      <c r="K30" s="13" t="n">
+        <v>5000000.0</v>
+      </c>
+      <c r="L30" s="13" t="n">
+        <v>400000.0</v>
+      </c>
+      <c r="M30" s="13" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="N30" s="13"/>
+      <c r="O30" s="13" t="n">
+        <v>5400000.0</v>
+      </c>
+      <c r="P30" s="7" t="inlineStr">
+        <is>
+          <t>VND</t>
+        </is>
+      </c>
+      <c r="Q30" s="7" t="inlineStr">
+        <is>
+          <t>1.0</t>
+        </is>
+      </c>
+      <c r="R30" s="6" t="inlineStr">
+        <is>
+          <t>Hóa đơn mới</t>
+        </is>
+      </c>
+      <c r="S30" s="6" t="inlineStr">
+        <is>
+          <t>Đã cấp mã hóa đơn</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="4" t="n">
+        <v>25.0</v>
+      </c>
+      <c r="B31" s="7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C31" s="6" t="inlineStr">
+        <is>
+          <t>C25THN</t>
+        </is>
+      </c>
+      <c r="D31" s="7" t="inlineStr">
+        <is>
+          <t>78</t>
+        </is>
+      </c>
+      <c r="E31" s="7" t="inlineStr">
+        <is>
+          <t>29/09/2025</t>
+        </is>
+      </c>
+      <c r="F31" s="7" t="inlineStr">
+        <is>
+          <t>3502475429</t>
+        </is>
+      </c>
+      <c r="G31" s="6" t="inlineStr">
+        <is>
+          <t>CÔNG TY TNHH THƯƠNG MẠI ĐỨC TÍN PHÚ MỸ</t>
+        </is>
+      </c>
+      <c r="H31" s="6" t="inlineStr">
+        <is>
+          <t>Tổ 7, Khu Phố Tân Lộc, Phường Tân Phước, Thành Phố Hồ Chí Minh</t>
+        </is>
+      </c>
+      <c r="I31" s="7" t="inlineStr">
+        <is>
+          <t>3500392181</t>
+        </is>
+      </c>
+      <c r="J31" s="6" t="inlineStr">
+        <is>
+          <t>CÔNG TY TNHH ĐẠI PHÚ HIỆP</t>
+        </is>
+      </c>
+      <c r="K31" s="13" t="n">
+        <v>2042000.0</v>
+      </c>
+      <c r="L31" s="13" t="n">
+        <v>163360.0</v>
+      </c>
+      <c r="M31" s="13" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="N31" s="13"/>
+      <c r="O31" s="13" t="n">
+        <v>2205360.0</v>
+      </c>
+      <c r="P31" s="7" t="inlineStr">
+        <is>
+          <t>VND</t>
+        </is>
+      </c>
+      <c r="Q31" s="7" t="inlineStr">
+        <is>
+          <t>1.0</t>
+        </is>
+      </c>
+      <c r="R31" s="6" t="inlineStr">
+        <is>
+          <t>Hóa đơn mới</t>
+        </is>
+      </c>
+      <c r="S31" s="6" t="inlineStr">
+        <is>
+          <t>Đã cấp mã hóa đơn</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="4" t="n">
+        <v>26.0</v>
+      </c>
+      <c r="B32" s="7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C32" s="6" t="inlineStr">
+        <is>
+          <t>C25TPM</t>
+        </is>
+      </c>
+      <c r="D32" s="7" t="inlineStr">
+        <is>
+          <t>328</t>
+        </is>
+      </c>
+      <c r="E32" s="7" t="inlineStr">
+        <is>
+          <t>30/09/2025</t>
+        </is>
+      </c>
+      <c r="F32" s="7" t="inlineStr">
+        <is>
+          <t>3502475764</t>
+        </is>
+      </c>
+      <c r="G32" s="6" t="inlineStr">
+        <is>
+          <t>CÔNG TY CỔ PHẦN ĐẦU TƯ GẠCH PHÚ MỸ</t>
+        </is>
+      </c>
+      <c r="H32" s="6" t="inlineStr">
+        <is>
+          <t>Thôn Tân Trung, Xã Châu Pha, Thành phố Hồ Chí Minh, Việt Nam</t>
+        </is>
+      </c>
+      <c r="I32" s="7" t="inlineStr">
+        <is>
+          <t>3500392181</t>
+        </is>
+      </c>
+      <c r="J32" s="6" t="inlineStr">
+        <is>
+          <t>CÔNG TY TNHH ĐẠI PHÚ HIỆP</t>
+        </is>
+      </c>
+      <c r="K32" s="13" t="n">
+        <v>3.128E7</v>
+      </c>
+      <c r="L32" s="13" t="n">
+        <v>2502400.0</v>
+      </c>
+      <c r="M32" s="13" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="N32" s="13"/>
+      <c r="O32" s="13" t="n">
+        <v>3.37824E7</v>
+      </c>
+      <c r="P32" s="7" t="inlineStr">
+        <is>
+          <t>VND</t>
+        </is>
+      </c>
+      <c r="Q32" s="7" t="inlineStr">
+        <is>
+          <t>1.0</t>
+        </is>
+      </c>
+      <c r="R32" s="6" t="inlineStr">
+        <is>
+          <t>Hóa đơn mới</t>
+        </is>
+      </c>
+      <c r="S32" s="6" t="inlineStr">
+        <is>
+          <t>Đã cấp mã hóa đơn</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="4" t="n">
+        <v>27.0</v>
+      </c>
+      <c r="B33" s="7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C33" s="6" t="inlineStr">
+        <is>
+          <t>C25TLT</t>
+        </is>
+      </c>
+      <c r="D33" s="7" t="inlineStr">
+        <is>
+          <t>184</t>
+        </is>
+      </c>
+      <c r="E33" s="7" t="inlineStr">
+        <is>
+          <t>05/09/2025</t>
+        </is>
+      </c>
+      <c r="F33" s="7" t="inlineStr">
+        <is>
+          <t>3502483483</t>
+        </is>
+      </c>
+      <c r="G33" s="6" t="inlineStr">
+        <is>
+          <t>CÔNG TY TRÁCH NHIỆM HỮU HẠN THƯƠNG MẠI - DỊCH VỤ - XÂY DỰNG LÂM TIẾN</t>
+        </is>
+      </c>
+      <c r="H33" s="6" t="inlineStr">
+        <is>
+          <t>Tổ 7, Khu Phố Tân Lộc, Phường Tân Phước, Thành phố Hồ Chí Minh, Việt Nam</t>
+        </is>
+      </c>
+      <c r="I33" s="7" t="inlineStr">
+        <is>
+          <t>3500392181</t>
+        </is>
+      </c>
+      <c r="J33" s="6" t="inlineStr">
+        <is>
+          <t>CÔNG TY TNHH ĐẠI PHÚ HIỆP</t>
+        </is>
+      </c>
+      <c r="K33" s="13" t="n">
+        <v>7129630.0</v>
+      </c>
+      <c r="L33" s="13" t="n">
+        <v>570370.0</v>
+      </c>
+      <c r="M33" s="13" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="N33" s="13"/>
+      <c r="O33" s="13" t="n">
+        <v>7700000.0</v>
+      </c>
+      <c r="P33" s="7" t="inlineStr">
+        <is>
+          <t>VND</t>
+        </is>
+      </c>
+      <c r="Q33" s="7" t="inlineStr">
+        <is>
+          <t>1.0</t>
+        </is>
+      </c>
+      <c r="R33" s="6" t="inlineStr">
+        <is>
+          <t>Hóa đơn mới</t>
+        </is>
+      </c>
+      <c r="S33" s="6" t="inlineStr">
+        <is>
+          <t>Đã cấp mã hóa đơn</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="4" t="n">
+        <v>28.0</v>
+      </c>
+      <c r="B34" s="7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C34" s="6" t="inlineStr">
+        <is>
+          <t>C25TLT</t>
+        </is>
+      </c>
+      <c r="D34" s="7" t="inlineStr">
+        <is>
+          <t>185</t>
+        </is>
+      </c>
+      <c r="E34" s="7" t="inlineStr">
+        <is>
+          <t>05/09/2025</t>
+        </is>
+      </c>
+      <c r="F34" s="7" t="inlineStr">
+        <is>
+          <t>3502483483</t>
+        </is>
+      </c>
+      <c r="G34" s="6" t="inlineStr">
+        <is>
+          <t>CÔNG TY TRÁCH NHIỆM HỮU HẠN THƯƠNG MẠI - DỊCH VỤ - XÂY DỰNG LÂM TIẾN</t>
+        </is>
+      </c>
+      <c r="H34" s="6" t="inlineStr">
+        <is>
+          <t>Tổ 7, Khu Phố Tân Lộc, Phường Tân Phước, Thành phố Hồ Chí Minh, Việt Nam</t>
+        </is>
+      </c>
+      <c r="I34" s="7" t="inlineStr">
+        <is>
+          <t>3500392181</t>
+        </is>
+      </c>
+      <c r="J34" s="6" t="inlineStr">
+        <is>
+          <t>CÔNG TY TNHH ĐẠI PHÚ HIỆP</t>
+        </is>
+      </c>
+      <c r="K34" s="13" t="n">
+        <v>1863709.0</v>
+      </c>
+      <c r="L34" s="13" t="n">
+        <v>186371.0</v>
+      </c>
+      <c r="M34" s="13" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="N34" s="13"/>
+      <c r="O34" s="13" t="n">
+        <v>2050080.0</v>
+      </c>
+      <c r="P34" s="7" t="inlineStr">
+        <is>
+          <t>VND</t>
+        </is>
+      </c>
+      <c r="Q34" s="7" t="inlineStr">
+        <is>
+          <t>1.0</t>
+        </is>
+      </c>
+      <c r="R34" s="6" t="inlineStr">
+        <is>
+          <t>Hóa đơn mới</t>
+        </is>
+      </c>
+      <c r="S34" s="6" t="inlineStr">
+        <is>
+          <t>Đã cấp mã hóa đơn</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="4" t="n">
+        <v>29.0</v>
+      </c>
+      <c r="B35" s="7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C35" s="6" t="inlineStr">
+        <is>
+          <t>C25TLT</t>
+        </is>
+      </c>
+      <c r="D35" s="7" t="inlineStr">
+        <is>
+          <t>213</t>
+        </is>
+      </c>
+      <c r="E35" s="7" t="inlineStr">
+        <is>
+          <t>30/09/2025</t>
+        </is>
+      </c>
+      <c r="F35" s="7" t="inlineStr">
+        <is>
+          <t>3502483483</t>
+        </is>
+      </c>
+      <c r="G35" s="6" t="inlineStr">
+        <is>
+          <t>CÔNG TY TRÁCH NHIỆM HỮU HẠN THƯƠNG MẠI - DỊCH VỤ - XÂY DỰNG LÂM TIẾN</t>
+        </is>
+      </c>
+      <c r="H35" s="6" t="inlineStr">
+        <is>
+          <t>Tổ 7, Khu Phố Tân Lộc, Phường Tân Phước, Thành phố Hồ Chí Minh, Việt Nam</t>
+        </is>
+      </c>
+      <c r="I35" s="7" t="inlineStr">
+        <is>
+          <t>3500392181</t>
+        </is>
+      </c>
+      <c r="J35" s="6" t="inlineStr">
+        <is>
+          <t>CÔNG TY TNHH ĐẠI PHÚ HIỆP</t>
+        </is>
+      </c>
+      <c r="K35" s="13" t="n">
+        <v>8555556.0</v>
+      </c>
+      <c r="L35" s="13" t="n">
+        <v>684444.0</v>
+      </c>
+      <c r="M35" s="13" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="N35" s="13"/>
+      <c r="O35" s="13" t="n">
+        <v>9240000.0</v>
+      </c>
+      <c r="P35" s="7" t="inlineStr">
+        <is>
+          <t>VND</t>
+        </is>
+      </c>
+      <c r="Q35" s="7" t="inlineStr">
+        <is>
+          <t>1.0</t>
+        </is>
+      </c>
+      <c r="R35" s="6" t="inlineStr">
+        <is>
+          <t>Hóa đơn mới</t>
+        </is>
+      </c>
+      <c r="S35" s="6" t="inlineStr">
+        <is>
+          <t>Đã cấp mã hóa đơn</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="4" t="n">
+        <v>30.0</v>
+      </c>
+      <c r="B36" s="7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C36" s="6" t="inlineStr">
+        <is>
+          <t>C25TLG</t>
+        </is>
+      </c>
+      <c r="D36" s="7" t="inlineStr">
+        <is>
+          <t>516</t>
+        </is>
+      </c>
+      <c r="E36" s="7" t="inlineStr">
+        <is>
+          <t>16/09/2025</t>
+        </is>
+      </c>
+      <c r="F36" s="7" t="inlineStr">
+        <is>
+          <t>3502501728</t>
+        </is>
+      </c>
+      <c r="G36" s="6" t="inlineStr">
+        <is>
+          <t>CÔNG TY TNHH LÊ GIA TP</t>
+        </is>
+      </c>
+      <c r="H36" s="6" t="inlineStr">
+        <is>
+          <t>Ấp Nam, Phường Tam Long, Thành Phố Hồ Chí Minh, Việt Nam</t>
+        </is>
+      </c>
+      <c r="I36" s="7" t="inlineStr">
+        <is>
+          <t>3500392181</t>
+        </is>
+      </c>
+      <c r="J36" s="6" t="inlineStr">
+        <is>
+          <t>CÔNG TY TNHH ĐẠI PHÚ HIỆP</t>
+        </is>
+      </c>
+      <c r="K36" s="13" t="n">
+        <v>4555556.0</v>
+      </c>
+      <c r="L36" s="13" t="n">
+        <v>364444.0</v>
+      </c>
+      <c r="M36" s="13" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="N36" s="13"/>
+      <c r="O36" s="13" t="n">
+        <v>4920000.0</v>
+      </c>
+      <c r="P36" s="7" t="inlineStr">
+        <is>
+          <t>VND</t>
+        </is>
+      </c>
+      <c r="Q36" s="7" t="inlineStr">
+        <is>
+          <t>1.0</t>
+        </is>
+      </c>
+      <c r="R36" s="6" t="inlineStr">
+        <is>
+          <t>Hóa đơn mới</t>
+        </is>
+      </c>
+      <c r="S36" s="6" t="inlineStr">
+        <is>
+          <t>Đã cấp mã hóa đơn</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="4" t="n">
+        <v>31.0</v>
+      </c>
+      <c r="B37" s="7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C37" s="6" t="inlineStr">
+        <is>
+          <t>C25TLG</t>
+        </is>
+      </c>
+      <c r="D37" s="7" t="inlineStr">
+        <is>
+          <t>539</t>
+        </is>
+      </c>
+      <c r="E37" s="7" t="inlineStr">
+        <is>
+          <t>26/09/2025</t>
+        </is>
+      </c>
+      <c r="F37" s="7" t="inlineStr">
+        <is>
+          <t>3502501728</t>
+        </is>
+      </c>
+      <c r="G37" s="6" t="inlineStr">
+        <is>
+          <t>CÔNG TY TNHH LÊ GIA TP</t>
+        </is>
+      </c>
+      <c r="H37" s="6" t="inlineStr">
+        <is>
+          <t>Ấp Nam, Phường Tam Long, Thành Phố Hồ Chí Minh, Việt Nam</t>
+        </is>
+      </c>
+      <c r="I37" s="7" t="inlineStr">
+        <is>
+          <t>3500392181</t>
+        </is>
+      </c>
+      <c r="J37" s="6" t="inlineStr">
+        <is>
+          <t>CÔNG TY TNHH ĐẠI PHÚ HIỆP</t>
+        </is>
+      </c>
+      <c r="K37" s="13" t="n">
+        <v>4555556.0</v>
+      </c>
+      <c r="L37" s="13" t="n">
+        <v>364444.0</v>
+      </c>
+      <c r="M37" s="13" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="N37" s="13"/>
+      <c r="O37" s="13" t="n">
+        <v>4920000.0</v>
+      </c>
+      <c r="P37" s="7" t="inlineStr">
+        <is>
+          <t>VND</t>
+        </is>
+      </c>
+      <c r="Q37" s="7" t="inlineStr">
+        <is>
+          <t>1.0</t>
+        </is>
+      </c>
+      <c r="R37" s="6" t="inlineStr">
+        <is>
+          <t>Hóa đơn mới</t>
+        </is>
+      </c>
+      <c r="S37" s="6" t="inlineStr">
+        <is>
+          <t>Đã cấp mã hóa đơn</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="4" t="n">
+        <v>32.0</v>
+      </c>
+      <c r="B38" s="7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C38" s="6" t="inlineStr">
+        <is>
+          <t>C25TGL</t>
+        </is>
+      </c>
+      <c r="D38" s="7" t="inlineStr">
+        <is>
+          <t>105</t>
+        </is>
+      </c>
+      <c r="E38" s="7" t="inlineStr">
+        <is>
+          <t>16/09/2025</t>
+        </is>
+      </c>
+      <c r="F38" s="7" t="inlineStr">
+        <is>
+          <t>3502510747</t>
+        </is>
+      </c>
+      <c r="G38" s="6" t="inlineStr">
+        <is>
+          <t>CÔNG TY TNHH DẦU NHỚT GIANG LONG</t>
+        </is>
+      </c>
+      <c r="H38" s="6" t="inlineStr">
+        <is>
+          <t>Quốc lộ 51, Tổ 11, Khu phố Phước Lộc, Phường Tân Phước, Thành phố Hồ Chí Minh, Việt Nam</t>
+        </is>
+      </c>
+      <c r="I38" s="7" t="inlineStr">
+        <is>
+          <t>3500392181</t>
+        </is>
+      </c>
+      <c r="J38" s="6" t="inlineStr">
+        <is>
+          <t>CÔNG TY TNHH ĐẠI PHÚ HIỆP</t>
+        </is>
+      </c>
+      <c r="K38" s="13" t="n">
+        <v>1111111.0</v>
+      </c>
+      <c r="L38" s="13" t="n">
+        <v>88889.0</v>
+      </c>
+      <c r="M38" s="13" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="N38" s="13"/>
+      <c r="O38" s="13" t="n">
+        <v>1200000.0</v>
+      </c>
+      <c r="P38" s="7" t="inlineStr">
+        <is>
+          <t>VND</t>
+        </is>
+      </c>
+      <c r="Q38" s="7" t="inlineStr">
+        <is>
+          <t>1.0</t>
+        </is>
+      </c>
+      <c r="R38" s="6" t="inlineStr">
+        <is>
+          <t>Hóa đơn mới</t>
+        </is>
+      </c>
+      <c r="S38" s="6" t="inlineStr">
+        <is>
+          <t>Đã cấp mã hóa đơn</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="4" t="n">
+        <v>33.0</v>
+      </c>
+      <c r="B39" s="7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C39" s="6" t="inlineStr">
+        <is>
+          <t>C25TSS</t>
+        </is>
+      </c>
+      <c r="D39" s="7" t="inlineStr">
+        <is>
+          <t>75</t>
+        </is>
+      </c>
+      <c r="E39" s="7" t="inlineStr">
+        <is>
+          <t>20/09/2025</t>
+        </is>
+      </c>
+      <c r="F39" s="7" t="inlineStr">
+        <is>
+          <t>3502523898</t>
+        </is>
+      </c>
+      <c r="G39" s="6" t="inlineStr">
+        <is>
+          <t>CÔNG TY TNHH ĐẦU TƯ THƯƠNG MẠI DỊCH VỤ SÁNG VIỆT</t>
+        </is>
+      </c>
+      <c r="H39" s="6" t="inlineStr">
+        <is>
+          <t>38 Biệt Chính , Phường Rạch Dừa, Thành Phố Hồ Chí Minh, Việt Nam</t>
+        </is>
+      </c>
+      <c r="I39" s="7" t="inlineStr">
+        <is>
+          <t>3500392181</t>
+        </is>
+      </c>
+      <c r="J39" s="6" t="inlineStr">
+        <is>
+          <t>CÔNG TY TNHH ĐẠI PHÚ HIỆP</t>
+        </is>
+      </c>
+      <c r="K39" s="13" t="n">
+        <v>760000.0</v>
+      </c>
+      <c r="L39" s="13" t="n">
+        <v>60800.0</v>
+      </c>
+      <c r="M39" s="13" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="N39" s="13"/>
+      <c r="O39" s="13" t="n">
+        <v>820800.0</v>
+      </c>
+      <c r="P39" s="7" t="inlineStr">
+        <is>
+          <t>VND</t>
+        </is>
+      </c>
+      <c r="Q39" s="7" t="inlineStr">
+        <is>
+          <t>1.0</t>
+        </is>
+      </c>
+      <c r="R39" s="6" t="inlineStr">
+        <is>
+          <t>Hóa đơn mới</t>
+        </is>
+      </c>
+      <c r="S39" s="6" t="inlineStr">
+        <is>
+          <t>Đã cấp mã hóa đơn</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="4" t="n">
+        <v>34.0</v>
+      </c>
+      <c r="B40" s="7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C40" s="6" t="inlineStr">
+        <is>
+          <t>C25TSS</t>
+        </is>
+      </c>
+      <c r="D40" s="7" t="inlineStr">
+        <is>
+          <t>77</t>
+        </is>
+      </c>
+      <c r="E40" s="7" t="inlineStr">
+        <is>
+          <t>20/09/2025</t>
+        </is>
+      </c>
+      <c r="F40" s="7" t="inlineStr">
+        <is>
+          <t>3502523898</t>
+        </is>
+      </c>
+      <c r="G40" s="6" t="inlineStr">
+        <is>
+          <t>CÔNG TY TNHH ĐẦU TƯ THƯƠNG MẠI DỊCH VỤ SÁNG VIỆT</t>
+        </is>
+      </c>
+      <c r="H40" s="6" t="inlineStr">
+        <is>
+          <t>38 Biệt Chính , Phường Rạch Dừa, Thành Phố Hồ Chí Minh, Việt Nam</t>
+        </is>
+      </c>
+      <c r="I40" s="7" t="inlineStr">
+        <is>
+          <t>3500392181</t>
+        </is>
+      </c>
+      <c r="J40" s="6" t="inlineStr">
+        <is>
+          <t>CÔNG TY TNHH ĐẠI PHÚ HIỆP</t>
+        </is>
+      </c>
+      <c r="K40" s="13" t="n">
+        <v>1873000.0</v>
+      </c>
+      <c r="L40" s="13" t="n">
+        <v>149840.0</v>
+      </c>
+      <c r="M40" s="13" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="N40" s="13"/>
+      <c r="O40" s="13" t="n">
+        <v>2022840.0</v>
+      </c>
+      <c r="P40" s="7" t="inlineStr">
+        <is>
+          <t>VND</t>
+        </is>
+      </c>
+      <c r="Q40" s="7" t="inlineStr">
+        <is>
+          <t>1.0</t>
+        </is>
+      </c>
+      <c r="R40" s="6" t="inlineStr">
+        <is>
+          <t>Hóa đơn mới</t>
+        </is>
+      </c>
+      <c r="S40" s="6" t="inlineStr">
+        <is>
+          <t>Đã cấp mã hóa đơn</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="4" t="n">
+        <v>35.0</v>
+      </c>
+      <c r="B41" s="7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C41" s="6" t="inlineStr">
+        <is>
+          <t>C25TCK</t>
+        </is>
+      </c>
+      <c r="D41" s="7" t="inlineStr">
+        <is>
+          <t>37</t>
+        </is>
+      </c>
+      <c r="E41" s="7" t="inlineStr">
+        <is>
+          <t>19/09/2025</t>
+        </is>
+      </c>
+      <c r="F41" s="7" t="inlineStr">
+        <is>
+          <t>3502538090</t>
+        </is>
+      </c>
+      <c r="G41" s="6" t="inlineStr">
+        <is>
+          <t>CÔNG TY TNHH VẬN TẢI CƠ GIỚI CƯỜNG KHANG</t>
+        </is>
+      </c>
+      <c r="H41" s="6" t="inlineStr">
+        <is>
+          <t>Đường 11F, Khu phố Hương Sơn, Phường Long Hương, Thành phố Hồ Chí Minh, Việt Nam</t>
+        </is>
+      </c>
+      <c r="I41" s="7" t="inlineStr">
+        <is>
+          <t>3500392181</t>
+        </is>
+      </c>
+      <c r="J41" s="6" t="inlineStr">
+        <is>
+          <t>CÔNG TY TNHH ĐẠI PHÚ HIỆP</t>
+        </is>
+      </c>
+      <c r="K41" s="13" t="n">
+        <v>8600000.0</v>
+      </c>
+      <c r="L41" s="13" t="n">
+        <v>688000.0</v>
+      </c>
+      <c r="M41" s="13" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="N41" s="13"/>
+      <c r="O41" s="13" t="n">
+        <v>9288000.0</v>
+      </c>
+      <c r="P41" s="7" t="inlineStr">
+        <is>
+          <t>VND</t>
+        </is>
+      </c>
+      <c r="Q41" s="7" t="inlineStr">
+        <is>
+          <t>1.0</t>
+        </is>
+      </c>
+      <c r="R41" s="6" t="inlineStr">
+        <is>
+          <t>Hóa đơn mới</t>
+        </is>
+      </c>
+      <c r="S41" s="6" t="inlineStr">
+        <is>
+          <t>Đã cấp mã hóa đơn</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="4" t="n">
+        <v>36.0</v>
+      </c>
+      <c r="B42" s="7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C42" s="6" t="inlineStr">
+        <is>
+          <t>C25TSY</t>
+        </is>
+      </c>
+      <c r="D42" s="7" t="inlineStr">
+        <is>
+          <t>5762</t>
+        </is>
+      </c>
+      <c r="E42" s="7" t="inlineStr">
+        <is>
+          <t>08/09/2025</t>
+        </is>
+      </c>
+      <c r="F42" s="7" t="inlineStr">
+        <is>
+          <t>3600745497</t>
+        </is>
+      </c>
+      <c r="G42" s="6" t="inlineStr">
+        <is>
+          <t>CÔNG TY CỔ PHẦN VAN SHIN YI</t>
+        </is>
+      </c>
+      <c r="H42" s="6" t="inlineStr">
+        <is>
+          <t>Đường số 5, KCN Sông Mây, Xã Bình Minh, Tỉnh Đồng Nai, Việt Nam</t>
+        </is>
+      </c>
+      <c r="I42" s="7" t="inlineStr">
+        <is>
+          <t>3500392181</t>
+        </is>
+      </c>
+      <c r="J42" s="6" t="inlineStr">
+        <is>
+          <t>CÔNG TY TNHH ĐẠI PHÚ HIỆP</t>
+        </is>
+      </c>
+      <c r="K42" s="13" t="n">
+        <v>3.132922E7</v>
+      </c>
+      <c r="L42" s="13" t="n">
+        <v>3132922.0</v>
+      </c>
+      <c r="M42" s="13" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="N42" s="13"/>
+      <c r="O42" s="13" t="n">
+        <v>3.4462142E7</v>
+      </c>
+      <c r="P42" s="7" t="inlineStr">
+        <is>
+          <t>VND</t>
+        </is>
+      </c>
+      <c r="Q42" s="7" t="inlineStr">
+        <is>
+          <t>1.0</t>
+        </is>
+      </c>
+      <c r="R42" s="6" t="inlineStr">
+        <is>
+          <t>Hóa đơn mới</t>
+        </is>
+      </c>
+      <c r="S42" s="6" t="inlineStr">
+        <is>
+          <t>Đã cấp mã hóa đơn</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="4" t="n">
+        <v>37.0</v>
+      </c>
+      <c r="B43" s="7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C43" s="6" t="inlineStr">
+        <is>
+          <t>C25TSY</t>
+        </is>
+      </c>
+      <c r="D43" s="7" t="inlineStr">
+        <is>
+          <t>5763</t>
+        </is>
+      </c>
+      <c r="E43" s="7" t="inlineStr">
+        <is>
+          <t>08/09/2025</t>
+        </is>
+      </c>
+      <c r="F43" s="7" t="inlineStr">
+        <is>
+          <t>3600745497</t>
+        </is>
+      </c>
+      <c r="G43" s="6" t="inlineStr">
+        <is>
+          <t>CÔNG TY CỔ PHẦN VAN SHIN YI</t>
+        </is>
+      </c>
+      <c r="H43" s="6" t="inlineStr">
+        <is>
+          <t>Đường số 5, KCN Sông Mây, Xã Bình Minh, Tỉnh Đồng Nai, Việt Nam</t>
+        </is>
+      </c>
+      <c r="I43" s="7" t="inlineStr">
+        <is>
+          <t>3500392181</t>
+        </is>
+      </c>
+      <c r="J43" s="6" t="inlineStr">
+        <is>
+          <t>CÔNG TY TNHH ĐẠI PHÚ HIỆP</t>
+        </is>
+      </c>
+      <c r="K43" s="13" t="n">
+        <v>1.69428E7</v>
+      </c>
+      <c r="L43" s="13" t="n">
+        <v>1694280.0</v>
+      </c>
+      <c r="M43" s="13" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="N43" s="13"/>
+      <c r="O43" s="13" t="n">
+        <v>1.863708E7</v>
+      </c>
+      <c r="P43" s="7" t="inlineStr">
+        <is>
+          <t>VND</t>
+        </is>
+      </c>
+      <c r="Q43" s="7" t="inlineStr">
+        <is>
+          <t>1.0</t>
+        </is>
+      </c>
+      <c r="R43" s="6" t="inlineStr">
+        <is>
+          <t>Hóa đơn mới</t>
+        </is>
+      </c>
+      <c r="S43" s="6" t="inlineStr">
+        <is>
+          <t>Đã cấp mã hóa đơn</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" s="4" t="n">
+        <v>38.0</v>
+      </c>
+      <c r="B44" s="7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C44" s="6" t="inlineStr">
+        <is>
+          <t>C25THG</t>
+        </is>
+      </c>
+      <c r="D44" s="7" t="inlineStr">
+        <is>
+          <t>381</t>
+        </is>
+      </c>
+      <c r="E44" s="7" t="inlineStr">
+        <is>
+          <t>08/09/2025</t>
+        </is>
+      </c>
+      <c r="F44" s="7" t="inlineStr">
+        <is>
+          <t>3603158560</t>
+        </is>
+      </c>
+      <c r="G44" s="6" t="inlineStr">
+        <is>
+          <t>CÔNG TY TNHH TRẦN HUY GIA</t>
+        </is>
+      </c>
+      <c r="H44" s="6" t="inlineStr">
+        <is>
+          <t>Số 08, Lê Duẩn, Xã An Phước, Tỉnh Đồng Nai, Việt Nam</t>
+        </is>
+      </c>
+      <c r="I44" s="7" t="inlineStr">
+        <is>
+          <t>3500392181</t>
+        </is>
+      </c>
+      <c r="J44" s="6" t="inlineStr">
+        <is>
+          <t>CÔNG TY TNHH ĐẠI PHÚ HIỆP</t>
+        </is>
+      </c>
+      <c r="K44" s="13" t="n">
+        <v>4513636.0</v>
+      </c>
+      <c r="L44" s="13" t="n">
+        <v>451364.0</v>
+      </c>
+      <c r="M44" s="13" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="N44" s="13"/>
+      <c r="O44" s="13" t="n">
+        <v>4965000.0</v>
+      </c>
+      <c r="P44" s="7" t="inlineStr">
+        <is>
+          <t>VND</t>
+        </is>
+      </c>
+      <c r="Q44" s="7" t="inlineStr">
+        <is>
+          <t>1.0</t>
+        </is>
+      </c>
+      <c r="R44" s="6" t="inlineStr">
+        <is>
+          <t>Hóa đơn mới</t>
+        </is>
+      </c>
+      <c r="S44" s="6" t="inlineStr">
+        <is>
+          <t>Đã cấp mã hóa đơn</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" s="4" t="n">
+        <v>39.0</v>
+      </c>
+      <c r="B45" s="7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C45" s="6" t="inlineStr">
+        <is>
+          <t>C25THG</t>
+        </is>
+      </c>
+      <c r="D45" s="7" t="inlineStr">
+        <is>
+          <t>384</t>
+        </is>
+      </c>
+      <c r="E45" s="7" t="inlineStr">
+        <is>
+          <t>09/09/2025</t>
+        </is>
+      </c>
+      <c r="F45" s="7" t="inlineStr">
+        <is>
+          <t>3603158560</t>
+        </is>
+      </c>
+      <c r="G45" s="6" t="inlineStr">
+        <is>
+          <t>CÔNG TY TNHH TRẦN HUY GIA</t>
+        </is>
+      </c>
+      <c r="H45" s="6" t="inlineStr">
+        <is>
+          <t>Số 08, Lê Duẩn, Xã An Phước, Tỉnh Đồng Nai, Việt Nam</t>
+        </is>
+      </c>
+      <c r="I45" s="7" t="inlineStr">
+        <is>
+          <t>3500392181</t>
+        </is>
+      </c>
+      <c r="J45" s="6" t="inlineStr">
+        <is>
+          <t>CÔNG TY TNHH ĐẠI PHÚ HIỆP</t>
+        </is>
+      </c>
+      <c r="K45" s="13" t="n">
+        <v>4164545.0</v>
+      </c>
+      <c r="L45" s="13" t="n">
+        <v>416455.0</v>
+      </c>
+      <c r="M45" s="13" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="N45" s="13"/>
+      <c r="O45" s="13" t="n">
+        <v>4581000.0</v>
+      </c>
+      <c r="P45" s="7" t="inlineStr">
+        <is>
+          <t>VND</t>
+        </is>
+      </c>
+      <c r="Q45" s="7" t="inlineStr">
+        <is>
+          <t>1.0</t>
+        </is>
+      </c>
+      <c r="R45" s="6" t="inlineStr">
+        <is>
+          <t>Hóa đơn mới</t>
+        </is>
+      </c>
+      <c r="S45" s="6" t="inlineStr">
+        <is>
+          <t>Đã cấp mã hóa đơn</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" s="4" t="n">
+        <v>40.0</v>
+      </c>
+      <c r="B46" s="7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C46" s="6" t="inlineStr">
+        <is>
+          <t>C25THG</t>
+        </is>
+      </c>
+      <c r="D46" s="7" t="inlineStr">
+        <is>
+          <t>388</t>
+        </is>
+      </c>
+      <c r="E46" s="7" t="inlineStr">
+        <is>
+          <t>10/09/2025</t>
+        </is>
+      </c>
+      <c r="F46" s="7" t="inlineStr">
+        <is>
+          <t>3603158560</t>
+        </is>
+      </c>
+      <c r="G46" s="6" t="inlineStr">
+        <is>
+          <t>CÔNG TY TNHH TRẦN HUY GIA</t>
+        </is>
+      </c>
+      <c r="H46" s="6" t="inlineStr">
+        <is>
+          <t>Số 08, Lê Duẩn, Xã An Phước, Tỉnh Đồng Nai, Việt Nam</t>
+        </is>
+      </c>
+      <c r="I46" s="7" t="inlineStr">
+        <is>
+          <t>3500392181</t>
+        </is>
+      </c>
+      <c r="J46" s="6" t="inlineStr">
+        <is>
+          <t>CÔNG TY TNHH ĐẠI PHÚ HIỆP</t>
+        </is>
+      </c>
+      <c r="K46" s="13" t="n">
+        <v>4338181.0</v>
+      </c>
+      <c r="L46" s="13" t="n">
+        <v>433819.0</v>
+      </c>
+      <c r="M46" s="13" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="N46" s="13"/>
+      <c r="O46" s="13" t="n">
+        <v>4772000.0</v>
+      </c>
+      <c r="P46" s="7" t="inlineStr">
+        <is>
+          <t>VND</t>
+        </is>
+      </c>
+      <c r="Q46" s="7" t="inlineStr">
+        <is>
+          <t>1.0</t>
+        </is>
+      </c>
+      <c r="R46" s="6" t="inlineStr">
+        <is>
+          <t>Hóa đơn mới</t>
+        </is>
+      </c>
+      <c r="S46" s="6" t="inlineStr">
+        <is>
+          <t>Đã cấp mã hóa đơn</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" s="4" t="n">
+        <v>41.0</v>
+      </c>
+      <c r="B47" s="7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C47" s="6" t="inlineStr">
+        <is>
+          <t>C25THG</t>
+        </is>
+      </c>
+      <c r="D47" s="7" t="inlineStr">
+        <is>
+          <t>398</t>
+        </is>
+      </c>
+      <c r="E47" s="7" t="inlineStr">
+        <is>
+          <t>11/09/2025</t>
+        </is>
+      </c>
+      <c r="F47" s="7" t="inlineStr">
+        <is>
+          <t>3603158560</t>
+        </is>
+      </c>
+      <c r="G47" s="6" t="inlineStr">
+        <is>
+          <t>CÔNG TY TNHH TRẦN HUY GIA</t>
+        </is>
+      </c>
+      <c r="H47" s="6" t="inlineStr">
+        <is>
+          <t>Số 08, Lê Duẩn, Xã An Phước, Tỉnh Đồng Nai, Việt Nam</t>
+        </is>
+      </c>
+      <c r="I47" s="7" t="inlineStr">
+        <is>
+          <t>3500392181</t>
+        </is>
+      </c>
+      <c r="J47" s="6" t="inlineStr">
+        <is>
+          <t>CÔNG TY TNHH ĐẠI PHÚ HIỆP</t>
+        </is>
+      </c>
+      <c r="K47" s="13" t="n">
+        <v>4452728.0</v>
+      </c>
+      <c r="L47" s="13" t="n">
+        <v>445272.0</v>
+      </c>
+      <c r="M47" s="13" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="N47" s="13"/>
+      <c r="O47" s="13" t="n">
+        <v>4898000.0</v>
+      </c>
+      <c r="P47" s="7" t="inlineStr">
+        <is>
+          <t>VND</t>
+        </is>
+      </c>
+      <c r="Q47" s="7" t="inlineStr">
+        <is>
+          <t>1.0</t>
+        </is>
+      </c>
+      <c r="R47" s="6" t="inlineStr">
+        <is>
+          <t>Hóa đơn mới</t>
+        </is>
+      </c>
+      <c r="S47" s="6" t="inlineStr">
+        <is>
+          <t>Đã cấp mã hóa đơn</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" s="4" t="n">
+        <v>42.0</v>
+      </c>
+      <c r="B48" s="7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C48" s="6" t="inlineStr">
+        <is>
+          <t>C25THG</t>
+        </is>
+      </c>
+      <c r="D48" s="7" t="inlineStr">
+        <is>
+          <t>403</t>
+        </is>
+      </c>
+      <c r="E48" s="7" t="inlineStr">
+        <is>
+          <t>17/09/2025</t>
+        </is>
+      </c>
+      <c r="F48" s="7" t="inlineStr">
+        <is>
+          <t>3603158560</t>
+        </is>
+      </c>
+      <c r="G48" s="6" t="inlineStr">
+        <is>
+          <t>CÔNG TY TNHH TRẦN HUY GIA</t>
+        </is>
+      </c>
+      <c r="H48" s="6" t="inlineStr">
+        <is>
+          <t>Số 08, Lê Duẩn, Xã An Phước, Tỉnh Đồng Nai, Việt Nam</t>
+        </is>
+      </c>
+      <c r="I48" s="7" t="inlineStr">
+        <is>
+          <t>3500392181</t>
+        </is>
+      </c>
+      <c r="J48" s="6" t="inlineStr">
+        <is>
+          <t>CÔNG TY TNHH ĐẠI PHÚ HIỆP</t>
+        </is>
+      </c>
+      <c r="K48" s="13" t="n">
+        <v>4404546.0</v>
+      </c>
+      <c r="L48" s="13" t="n">
+        <v>440454.0</v>
+      </c>
+      <c r="M48" s="13" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="N48" s="13"/>
+      <c r="O48" s="13" t="n">
+        <v>4845000.0</v>
+      </c>
+      <c r="P48" s="7" t="inlineStr">
+        <is>
+          <t>VND</t>
+        </is>
+      </c>
+      <c r="Q48" s="7" t="inlineStr">
+        <is>
+          <t>1.0</t>
+        </is>
+      </c>
+      <c r="R48" s="6" t="inlineStr">
+        <is>
+          <t>Hóa đơn mới</t>
+        </is>
+      </c>
+      <c r="S48" s="6" t="inlineStr">
+        <is>
+          <t>Đã cấp mã hóa đơn</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" s="4" t="n">
+        <v>43.0</v>
+      </c>
+      <c r="B49" s="7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C49" s="6" t="inlineStr">
+        <is>
+          <t>C25THG</t>
+        </is>
+      </c>
+      <c r="D49" s="7" t="inlineStr">
+        <is>
+          <t>407</t>
+        </is>
+      </c>
+      <c r="E49" s="7" t="inlineStr">
+        <is>
+          <t>18/09/2025</t>
+        </is>
+      </c>
+      <c r="F49" s="7" t="inlineStr">
+        <is>
+          <t>3603158560</t>
+        </is>
+      </c>
+      <c r="G49" s="6" t="inlineStr">
+        <is>
+          <t>CÔNG TY TNHH TRẦN HUY GIA</t>
+        </is>
+      </c>
+      <c r="H49" s="6" t="inlineStr">
+        <is>
+          <t>Số 08, Lê Duẩn, Xã An Phước, Tỉnh Đồng Nai, Việt Nam</t>
+        </is>
+      </c>
+      <c r="I49" s="7" t="inlineStr">
+        <is>
+          <t>3500392181</t>
+        </is>
+      </c>
+      <c r="J49" s="6" t="inlineStr">
+        <is>
+          <t>CÔNG TY TNHH ĐẠI PHÚ HIỆP</t>
+        </is>
+      </c>
+      <c r="K49" s="13" t="n">
+        <v>4497272.0</v>
+      </c>
+      <c r="L49" s="13" t="n">
+        <v>449728.0</v>
+      </c>
+      <c r="M49" s="13" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="N49" s="13"/>
+      <c r="O49" s="13" t="n">
+        <v>4947000.0</v>
+      </c>
+      <c r="P49" s="7" t="inlineStr">
+        <is>
+          <t>VND</t>
+        </is>
+      </c>
+      <c r="Q49" s="7" t="inlineStr">
+        <is>
+          <t>1.0</t>
+        </is>
+      </c>
+      <c r="R49" s="6" t="inlineStr">
+        <is>
+          <t>Hóa đơn mới</t>
+        </is>
+      </c>
+      <c r="S49" s="6" t="inlineStr">
+        <is>
+          <t>Đã cấp mã hóa đơn</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" s="4" t="n">
+        <v>44.0</v>
+      </c>
+      <c r="B50" s="7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C50" s="6" t="inlineStr">
+        <is>
+          <t>C25THG</t>
+        </is>
+      </c>
+      <c r="D50" s="7" t="inlineStr">
+        <is>
+          <t>409</t>
+        </is>
+      </c>
+      <c r="E50" s="7" t="inlineStr">
+        <is>
+          <t>19/09/2025</t>
+        </is>
+      </c>
+      <c r="F50" s="7" t="inlineStr">
+        <is>
+          <t>3603158560</t>
+        </is>
+      </c>
+      <c r="G50" s="6" t="inlineStr">
+        <is>
+          <t>CÔNG TY TNHH TRẦN HUY GIA</t>
+        </is>
+      </c>
+      <c r="H50" s="6" t="inlineStr">
+        <is>
+          <t>Số 08, Lê Duẩn, Xã An Phước, Tỉnh Đồng Nai, Việt Nam</t>
+        </is>
+      </c>
+      <c r="I50" s="7" t="inlineStr">
+        <is>
+          <t>3500392181</t>
+        </is>
+      </c>
+      <c r="J50" s="6" t="inlineStr">
+        <is>
+          <t>CÔNG TY TNHH ĐẠI PHÚ HIỆP</t>
+        </is>
+      </c>
+      <c r="K50" s="13" t="n">
+        <v>4484546.0</v>
+      </c>
+      <c r="L50" s="13" t="n">
+        <v>448455.0</v>
+      </c>
+      <c r="M50" s="13" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="N50" s="13"/>
+      <c r="O50" s="13" t="n">
+        <v>4933001.0</v>
+      </c>
+      <c r="P50" s="7" t="inlineStr">
+        <is>
+          <t>VND</t>
+        </is>
+      </c>
+      <c r="Q50" s="7" t="inlineStr">
+        <is>
+          <t>1.0</t>
+        </is>
+      </c>
+      <c r="R50" s="6" t="inlineStr">
+        <is>
+          <t>Hóa đơn mới</t>
+        </is>
+      </c>
+      <c r="S50" s="6" t="inlineStr">
+        <is>
+          <t>Đã cấp mã hóa đơn</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" s="4" t="n">
+        <v>45.0</v>
+      </c>
+      <c r="B51" s="7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C51" s="6" t="inlineStr">
+        <is>
+          <t>C25THG</t>
+        </is>
+      </c>
+      <c r="D51" s="7" t="inlineStr">
+        <is>
+          <t>413</t>
+        </is>
+      </c>
+      <c r="E51" s="7" t="inlineStr">
+        <is>
+          <t>20/09/2025</t>
+        </is>
+      </c>
+      <c r="F51" s="7" t="inlineStr">
+        <is>
+          <t>3603158560</t>
+        </is>
+      </c>
+      <c r="G51" s="6" t="inlineStr">
+        <is>
+          <t>CÔNG TY TNHH TRẦN HUY GIA</t>
+        </is>
+      </c>
+      <c r="H51" s="6" t="inlineStr">
+        <is>
+          <t>Số 08, Lê Duẩn, Xã An Phước, Tỉnh Đồng Nai, Việt Nam</t>
+        </is>
+      </c>
+      <c r="I51" s="7" t="inlineStr">
+        <is>
+          <t>3500392181</t>
+        </is>
+      </c>
+      <c r="J51" s="6" t="inlineStr">
+        <is>
+          <t>CÔNG TY TNHH ĐẠI PHÚ HIỆP</t>
+        </is>
+      </c>
+      <c r="K51" s="13" t="n">
+        <v>4417273.0</v>
+      </c>
+      <c r="L51" s="13" t="n">
+        <v>441727.0</v>
+      </c>
+      <c r="M51" s="13" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="N51" s="13"/>
+      <c r="O51" s="13" t="n">
+        <v>4859000.0</v>
+      </c>
+      <c r="P51" s="7" t="inlineStr">
+        <is>
+          <t>VND</t>
+        </is>
+      </c>
+      <c r="Q51" s="7" t="inlineStr">
+        <is>
+          <t>1.0</t>
+        </is>
+      </c>
+      <c r="R51" s="6" t="inlineStr">
+        <is>
+          <t>Hóa đơn mới</t>
+        </is>
+      </c>
+      <c r="S51" s="6" t="inlineStr">
+        <is>
+          <t>Đã cấp mã hóa đơn</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" s="4" t="n">
+        <v>46.0</v>
+      </c>
+      <c r="B52" s="7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C52" s="6" t="inlineStr">
+        <is>
+          <t>C25THG</t>
+        </is>
+      </c>
+      <c r="D52" s="7" t="inlineStr">
+        <is>
+          <t>416</t>
+        </is>
+      </c>
+      <c r="E52" s="7" t="inlineStr">
+        <is>
+          <t>22/09/2025</t>
+        </is>
+      </c>
+      <c r="F52" s="7" t="inlineStr">
+        <is>
+          <t>3603158560</t>
+        </is>
+      </c>
+      <c r="G52" s="6" t="inlineStr">
+        <is>
+          <t>CÔNG TY TNHH TRẦN HUY GIA</t>
+        </is>
+      </c>
+      <c r="H52" s="6" t="inlineStr">
+        <is>
+          <t>Số 08, Lê Duẩn, Xã An Phước, Tỉnh Đồng Nai, Việt Nam</t>
+        </is>
+      </c>
+      <c r="I52" s="7" t="inlineStr">
+        <is>
+          <t>3500392181</t>
+        </is>
+      </c>
+      <c r="J52" s="6" t="inlineStr">
+        <is>
+          <t>CÔNG TY TNHH ĐẠI PHÚ HIỆP</t>
+        </is>
+      </c>
+      <c r="K52" s="13" t="n">
+        <v>4490000.0</v>
+      </c>
+      <c r="L52" s="13" t="n">
+        <v>449000.0</v>
+      </c>
+      <c r="M52" s="13" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="N52" s="13"/>
+      <c r="O52" s="13" t="n">
+        <v>4939000.0</v>
+      </c>
+      <c r="P52" s="7" t="inlineStr">
+        <is>
+          <t>VND</t>
+        </is>
+      </c>
+      <c r="Q52" s="7" t="inlineStr">
+        <is>
+          <t>1.0</t>
+        </is>
+      </c>
+      <c r="R52" s="6" t="inlineStr">
+        <is>
+          <t>Hóa đơn mới</t>
+        </is>
+      </c>
+      <c r="S52" s="6" t="inlineStr">
+        <is>
+          <t>Đã cấp mã hóa đơn</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" s="4" t="n">
+        <v>47.0</v>
+      </c>
+      <c r="B53" s="7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C53" s="6" t="inlineStr">
+        <is>
+          <t>C25THG</t>
+        </is>
+      </c>
+      <c r="D53" s="7" t="inlineStr">
+        <is>
+          <t>422</t>
+        </is>
+      </c>
+      <c r="E53" s="7" t="inlineStr">
+        <is>
+          <t>25/09/2025</t>
+        </is>
+      </c>
+      <c r="F53" s="7" t="inlineStr">
+        <is>
+          <t>3603158560</t>
+        </is>
+      </c>
+      <c r="G53" s="6" t="inlineStr">
+        <is>
+          <t>CÔNG TY TNHH TRẦN HUY GIA</t>
+        </is>
+      </c>
+      <c r="H53" s="6" t="inlineStr">
+        <is>
+          <t>Số 08, Lê Duẩn, Xã An Phước, Tỉnh Đồng Nai, Việt Nam</t>
+        </is>
+      </c>
+      <c r="I53" s="7" t="inlineStr">
+        <is>
+          <t>3500392181</t>
+        </is>
+      </c>
+      <c r="J53" s="6" t="inlineStr">
+        <is>
+          <t>CÔNG TY TNHH ĐẠI PHÚ HIỆP</t>
+        </is>
+      </c>
+      <c r="K53" s="13" t="n">
+        <v>4485454.0</v>
+      </c>
+      <c r="L53" s="13" t="n">
+        <v>448546.0</v>
+      </c>
+      <c r="M53" s="13" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="N53" s="13"/>
+      <c r="O53" s="13" t="n">
+        <v>4934000.0</v>
+      </c>
+      <c r="P53" s="7" t="inlineStr">
+        <is>
+          <t>VND</t>
+        </is>
+      </c>
+      <c r="Q53" s="7" t="inlineStr">
+        <is>
+          <t>1.0</t>
+        </is>
+      </c>
+      <c r="R53" s="6" t="inlineStr">
+        <is>
+          <t>Hóa đơn mới</t>
+        </is>
+      </c>
+      <c r="S53" s="6" t="inlineStr">
+        <is>
+          <t>Đã cấp mã hóa đơn</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" s="4" t="n">
+        <v>48.0</v>
+      </c>
+      <c r="B54" s="7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C54" s="6" t="inlineStr">
+        <is>
+          <t>C25THG</t>
+        </is>
+      </c>
+      <c r="D54" s="7" t="inlineStr">
+        <is>
+          <t>425</t>
+        </is>
+      </c>
+      <c r="E54" s="7" t="inlineStr">
+        <is>
+          <t>26/09/2025</t>
+        </is>
+      </c>
+      <c r="F54" s="7" t="inlineStr">
+        <is>
+          <t>3603158560</t>
+        </is>
+      </c>
+      <c r="G54" s="6" t="inlineStr">
+        <is>
+          <t>CÔNG TY TNHH TRẦN HUY GIA</t>
+        </is>
+      </c>
+      <c r="H54" s="6" t="inlineStr">
+        <is>
+          <t>Số 08, Lê Duẩn, Xã An Phước, Tỉnh Đồng Nai, Việt Nam</t>
+        </is>
+      </c>
+      <c r="I54" s="7" t="inlineStr">
+        <is>
+          <t>3500392181</t>
+        </is>
+      </c>
+      <c r="J54" s="6" t="inlineStr">
+        <is>
+          <t>CÔNG TY TNHH ĐẠI PHÚ HIỆP</t>
+        </is>
+      </c>
+      <c r="K54" s="13" t="n">
+        <v>4260000.0</v>
+      </c>
+      <c r="L54" s="13" t="n">
+        <v>426001.0</v>
+      </c>
+      <c r="M54" s="13" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="N54" s="13"/>
+      <c r="O54" s="13" t="n">
+        <v>4686001.0</v>
+      </c>
+      <c r="P54" s="7" t="inlineStr">
+        <is>
+          <t>VND</t>
+        </is>
+      </c>
+      <c r="Q54" s="7" t="inlineStr">
+        <is>
+          <t>1.0</t>
+        </is>
+      </c>
+      <c r="R54" s="6" t="inlineStr">
+        <is>
+          <t>Hóa đơn mới</t>
+        </is>
+      </c>
+      <c r="S54" s="6" t="inlineStr">
+        <is>
+          <t>Đã cấp mã hóa đơn</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" s="4" t="n">
+        <v>49.0</v>
+      </c>
+      <c r="B55" s="7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C55" s="6" t="inlineStr">
+        <is>
+          <t>C25THG</t>
+        </is>
+      </c>
+      <c r="D55" s="7" t="inlineStr">
+        <is>
+          <t>428</t>
+        </is>
+      </c>
+      <c r="E55" s="7" t="inlineStr">
+        <is>
+          <t>27/09/2025</t>
+        </is>
+      </c>
+      <c r="F55" s="7" t="inlineStr">
+        <is>
+          <t>3603158560</t>
+        </is>
+      </c>
+      <c r="G55" s="6" t="inlineStr">
+        <is>
+          <t>CÔNG TY TNHH TRẦN HUY GIA</t>
+        </is>
+      </c>
+      <c r="H55" s="6" t="inlineStr">
+        <is>
+          <t>Số 08, Lê Duẩn, Xã An Phước, Tỉnh Đồng Nai, Việt Nam</t>
+        </is>
+      </c>
+      <c r="I55" s="7" t="inlineStr">
+        <is>
+          <t>3500392181</t>
+        </is>
+      </c>
+      <c r="J55" s="6" t="inlineStr">
+        <is>
+          <t>CÔNG TY TNHH ĐẠI PHÚ HIỆP</t>
+        </is>
+      </c>
+      <c r="K55" s="13" t="n">
+        <v>4145455.0</v>
+      </c>
+      <c r="L55" s="13" t="n">
+        <v>414546.0</v>
+      </c>
+      <c r="M55" s="13" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="N55" s="13"/>
+      <c r="O55" s="13" t="n">
+        <v>4560001.0</v>
+      </c>
+      <c r="P55" s="7" t="inlineStr">
+        <is>
+          <t>VND</t>
+        </is>
+      </c>
+      <c r="Q55" s="7" t="inlineStr">
+        <is>
+          <t>1.0</t>
+        </is>
+      </c>
+      <c r="R55" s="6" t="inlineStr">
+        <is>
+          <t>Hóa đơn mới</t>
+        </is>
+      </c>
+      <c r="S55" s="6" t="inlineStr">
+        <is>
+          <t>Đã cấp mã hóa đơn</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" s="4" t="n">
+        <v>50.0</v>
+      </c>
+      <c r="B56" s="7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C56" s="6" t="inlineStr">
+        <is>
+          <t>C25THG</t>
+        </is>
+      </c>
+      <c r="D56" s="7" t="inlineStr">
+        <is>
+          <t>437</t>
+        </is>
+      </c>
+      <c r="E56" s="7" t="inlineStr">
+        <is>
+          <t>29/09/2025</t>
+        </is>
+      </c>
+      <c r="F56" s="7" t="inlineStr">
+        <is>
+          <t>3603158560</t>
+        </is>
+      </c>
+      <c r="G56" s="6" t="inlineStr">
+        <is>
+          <t>CÔNG TY TNHH TRẦN HUY GIA</t>
+        </is>
+      </c>
+      <c r="H56" s="6" t="inlineStr">
+        <is>
+          <t>Số 08, Lê Duẩn, Xã An Phước, Tỉnh Đồng Nai, Việt Nam</t>
+        </is>
+      </c>
+      <c r="I56" s="7" t="inlineStr">
+        <is>
+          <t>3500392181</t>
+        </is>
+      </c>
+      <c r="J56" s="6" t="inlineStr">
+        <is>
+          <t>CÔNG TY TNHH ĐẠI PHÚ HIỆP</t>
+        </is>
+      </c>
+      <c r="K56" s="13" t="n">
+        <v>4183636.0</v>
+      </c>
+      <c r="L56" s="13" t="n">
+        <v>418364.0</v>
+      </c>
+      <c r="M56" s="13" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="N56" s="13"/>
+      <c r="O56" s="13" t="n">
+        <v>4602000.0</v>
+      </c>
+      <c r="P56" s="7" t="inlineStr">
+        <is>
+          <t>VND</t>
+        </is>
+      </c>
+      <c r="Q56" s="7" t="inlineStr">
+        <is>
+          <t>1.0</t>
+        </is>
+      </c>
+      <c r="R56" s="6" t="inlineStr">
+        <is>
+          <t>Hóa đơn mới</t>
+        </is>
+      </c>
+      <c r="S56" s="6" t="inlineStr">
+        <is>
+          <t>Đã cấp mã hóa đơn</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" s="4" t="n">
+        <v>51.0</v>
+      </c>
+      <c r="B57" s="7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C57" s="6" t="inlineStr">
+        <is>
+          <t>C25TNB</t>
+        </is>
+      </c>
+      <c r="D57" s="7" t="inlineStr">
+        <is>
+          <t>269</t>
+        </is>
+      </c>
+      <c r="E57" s="7" t="inlineStr">
+        <is>
+          <t>29/09/2025</t>
+        </is>
+      </c>
+      <c r="F57" s="7" t="inlineStr">
+        <is>
+          <t>3603985137</t>
+        </is>
+      </c>
+      <c r="G57" s="6" t="inlineStr">
+        <is>
+          <t>CÔNG TY TNHH CÔNG NGHỆ NĂNG LƯỢNG NIBA</t>
+        </is>
+      </c>
+      <c r="H57" s="6" t="inlineStr">
+        <is>
+          <t>Số 41, Tổ 1, Ấp Phước Mỹ, Xã Nhơn Trạch, Tỉnh Đồng Nai, Việt Nam</t>
+        </is>
+      </c>
+      <c r="I57" s="7" t="inlineStr">
+        <is>
+          <t>3500392181</t>
+        </is>
+      </c>
+      <c r="J57" s="6" t="inlineStr">
+        <is>
+          <t>CÔNG TY TNHH ĐẠI PHÚ HIỆP</t>
+        </is>
+      </c>
+      <c r="K57" s="13" t="n">
+        <v>2728000.0</v>
+      </c>
+      <c r="L57" s="13" t="n">
+        <v>218240.0</v>
+      </c>
+      <c r="M57" s="13" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="N57" s="13"/>
+      <c r="O57" s="13" t="n">
+        <v>2946240.0</v>
+      </c>
+      <c r="P57" s="7" t="inlineStr">
+        <is>
+          <t>VND</t>
+        </is>
+      </c>
+      <c r="Q57" s="7" t="inlineStr">
+        <is>
+          <t>1.0</t>
+        </is>
+      </c>
+      <c r="R57" s="6" t="inlineStr">
+        <is>
+          <t>Hóa đơn mới</t>
+        </is>
+      </c>
+      <c r="S57" s="6" t="inlineStr">
+        <is>
+          <t>Đã cấp mã hóa đơn</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" s="4" t="n">
+        <v>52.0</v>
+      </c>
+      <c r="B58" s="7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C58" s="6" t="inlineStr">
+        <is>
+          <t>C25TYY</t>
+        </is>
+      </c>
+      <c r="D58" s="7" t="inlineStr">
+        <is>
+          <t>1037</t>
+        </is>
+      </c>
+      <c r="E58" s="7" t="inlineStr">
+        <is>
+          <t>16/09/2025</t>
+        </is>
+      </c>
+      <c r="F58" s="7" t="inlineStr">
+        <is>
+          <t>3703201058</t>
+        </is>
+      </c>
+      <c r="G58" s="6" t="inlineStr">
+        <is>
+          <t>CÔNG TY TNHH DỊCH VỤ CƠ GIỚI ĐÔNG HÒA</t>
+        </is>
+      </c>
+      <c r="H58" s="6" t="inlineStr">
+        <is>
+          <t>Số 113, khu phố Tân Lập, Phường Đông Hòa, Thành phố Hồ Chí Minh, Việt Nam</t>
+        </is>
+      </c>
+      <c r="I58" s="7" t="inlineStr">
+        <is>
+          <t>3500392181</t>
+        </is>
+      </c>
+      <c r="J58" s="6" t="inlineStr">
+        <is>
+          <t>CÔNG TY TNHH ĐẠI PHÚ HIỆP</t>
+        </is>
+      </c>
+      <c r="K58" s="13" t="n">
+        <v>1300000.0</v>
+      </c>
+      <c r="L58" s="13" t="n">
+        <v>104000.0</v>
+      </c>
+      <c r="M58" s="13" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="N58" s="13"/>
+      <c r="O58" s="13" t="n">
+        <v>1404000.0</v>
+      </c>
+      <c r="P58" s="7" t="inlineStr">
+        <is>
+          <t>VND</t>
+        </is>
+      </c>
+      <c r="Q58" s="7" t="inlineStr">
+        <is>
+          <t>1.0</t>
+        </is>
+      </c>
+      <c r="R58" s="6" t="inlineStr">
+        <is>
+          <t>Hóa đơn mới</t>
+        </is>
+      </c>
+      <c r="S58" s="6" t="inlineStr">
+        <is>
+          <t>Đã cấp mã hóa đơn</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" s="4" t="n">
+        <v>53.0</v>
+      </c>
+      <c r="B59" s="7" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="C59" s="6" t="inlineStr">
+        <is>
+          <t>C25TKC</t>
+        </is>
+      </c>
+      <c r="D59" s="7" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="E59" s="7" t="inlineStr">
+        <is>
+          <t>15/09/2025</t>
+        </is>
+      </c>
+      <c r="F59" s="7" t="inlineStr">
+        <is>
+          <t>8158543604</t>
+        </is>
+      </c>
+      <c r="G59" s="6" t="inlineStr">
+        <is>
+          <t>HỘ KINH DOANH TRẠI CÂY GIỐNG HÒA LONG</t>
+        </is>
+      </c>
+      <c r="H59" s="6" t="inlineStr">
+        <is>
+          <t>Quốc lộ 56, tổ 13, ấp Bắc 2, Xã Hoà Long, Tp Bà Rịa, Bà Rịa - Vũng Tàu</t>
+        </is>
+      </c>
+      <c r="I59" s="7" t="inlineStr">
+        <is>
+          <t>3500392181</t>
+        </is>
+      </c>
+      <c r="J59" s="6" t="inlineStr">
+        <is>
+          <t>Công Ty TNHH Đại Phú Hiệp</t>
+        </is>
+      </c>
+      <c r="K59" s="13"/>
+      <c r="L59" s="13"/>
+      <c r="M59" s="13"/>
+      <c r="N59" s="13"/>
+      <c r="O59" s="13" t="n">
+        <v>1.56E7</v>
+      </c>
+      <c r="P59" s="7" t="inlineStr">
+        <is>
+          <t>VND</t>
+        </is>
+      </c>
+      <c r="Q59" s="7" t="inlineStr">
+        <is>
+          <t>1.0</t>
+        </is>
+      </c>
+      <c r="R59" s="6" t="inlineStr">
+        <is>
+          <t>Hóa đơn mới</t>
+        </is>
+      </c>
+      <c r="S59" s="6" t="inlineStr">
+        <is>
+          <t>Đã cấp mã hóa đơn</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" s="4" t="n">
+        <v>54.0</v>
+      </c>
+      <c r="B60" s="7" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="C60" s="6" t="inlineStr">
+        <is>
+          <t>C25TKC</t>
+        </is>
+      </c>
+      <c r="D60" s="7" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="E60" s="7" t="inlineStr">
+        <is>
+          <t>25/09/2025</t>
+        </is>
+      </c>
+      <c r="F60" s="7" t="inlineStr">
+        <is>
+          <t>8158543604</t>
+        </is>
+      </c>
+      <c r="G60" s="6" t="inlineStr">
+        <is>
+          <t>HỘ KINH DOANH TRẠI CÂY GIỐNG HÒA LONG</t>
+        </is>
+      </c>
+      <c r="H60" s="6" t="inlineStr">
+        <is>
+          <t>Quốc lộ 56, tổ 13, ấp Bắc 2, Phường Tam Long, Thành phố Hồ Chí Minh, Việt Nam</t>
+        </is>
+      </c>
+      <c r="I60" s="7" t="inlineStr">
+        <is>
+          <t>3500392181</t>
+        </is>
+      </c>
+      <c r="J60" s="6" t="inlineStr">
+        <is>
+          <t>Công Ty TNHH Đại Phú Hiệp</t>
+        </is>
+      </c>
+      <c r="K60" s="13"/>
+      <c r="L60" s="13"/>
+      <c r="M60" s="13"/>
+      <c r="N60" s="13"/>
+      <c r="O60" s="13" t="n">
+        <v>1.96E8</v>
+      </c>
+      <c r="P60" s="7" t="inlineStr">
+        <is>
+          <t>VND</t>
+        </is>
+      </c>
+      <c r="Q60" s="7" t="inlineStr">
+        <is>
+          <t>1.0</t>
+        </is>
+      </c>
+      <c r="R60" s="6" t="inlineStr">
+        <is>
+          <t>Hóa đơn đã bị thay thế</t>
+        </is>
+      </c>
+      <c r="S60" s="6" t="inlineStr">
+        <is>
+          <t>Đã cấp mã hóa đơn</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" s="4" t="n">
+        <v>55.0</v>
+      </c>
+      <c r="B61" s="7" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="C61" s="6" t="inlineStr">
+        <is>
+          <t>C25TKC</t>
+        </is>
+      </c>
+      <c r="D61" s="7" t="inlineStr">
+        <is>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="E61" s="7" t="inlineStr">
+        <is>
+          <t>26/09/2025</t>
+        </is>
+      </c>
+      <c r="F61" s="7" t="inlineStr">
+        <is>
+          <t>8158543604</t>
+        </is>
+      </c>
+      <c r="G61" s="6" t="inlineStr">
+        <is>
+          <t>HỘ KINH DOANH TRẠI CÂY GIỐNG HÒA LONG</t>
+        </is>
+      </c>
+      <c r="H61" s="6" t="inlineStr">
+        <is>
+          <t>Quốc lộ 56, tổ 13, ấp Bắc 2, Phường Tam Long, Thành phố Hồ Chí Minh, Việt Nam</t>
+        </is>
+      </c>
+      <c r="I61" s="7" t="inlineStr">
+        <is>
+          <t>3500392181</t>
+        </is>
+      </c>
+      <c r="J61" s="6" t="inlineStr">
+        <is>
+          <t>Công Ty TNHH Đại Phú Hiệp</t>
+        </is>
+      </c>
+      <c r="K61" s="13"/>
+      <c r="L61" s="13"/>
+      <c r="M61" s="13"/>
+      <c r="N61" s="13"/>
+      <c r="O61" s="13" t="n">
+        <v>1.96E8</v>
+      </c>
+      <c r="P61" s="7" t="inlineStr">
+        <is>
+          <t>VND</t>
+        </is>
+      </c>
+      <c r="Q61" s="7" t="inlineStr">
+        <is>
+          <t>1.0</t>
+        </is>
+      </c>
+      <c r="R61" s="6" t="inlineStr">
+        <is>
+          <t>Hóa đơn thay thế</t>
+        </is>
+      </c>
+      <c r="S61" s="6" t="inlineStr">
         <is>
           <t>Đã cấp mã hóa đơn</t>
         </is>
